--- a/stock_review_template.xlsx
+++ b/stock_review_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12740" activeTab="4"/>
+    <workbookView windowWidth="29400" windowHeight="12740" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="1" r:id="rId1"/>
@@ -597,7 +597,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="257">
   <si>
     <t>股票复盘训练模板</t>
   </si>
@@ -812,6 +812,42 @@
     <t>属于业绩修复</t>
   </si>
   <si>
+    <t>游戏</t>
+  </si>
+  <si>
+    <t>国有大型银行</t>
+  </si>
+  <si>
+    <t>影视院线</t>
+  </si>
+  <si>
+    <t>连续两天超过大盘</t>
+  </si>
+  <si>
+    <t>跌幅小于大盘</t>
+  </si>
+  <si>
+    <t>巨星农垦</t>
+  </si>
+  <si>
+    <t>后面跌幅又超过板块，属于回调还是其实不是领涨股，领涨股要一直领涨嘛，明显高于其它股票，是要求每天都超过嘛，肯定不是，怎么理解领涨股？</t>
+  </si>
+  <si>
+    <t>油气开采及服务</t>
+  </si>
+  <si>
+    <t>旅游及酒店</t>
+  </si>
+  <si>
+    <t>IT服务</t>
+  </si>
+  <si>
+    <t>连续三天超过大盘</t>
+  </si>
+  <si>
+    <t>都涨所有的股票都涨，且都差不多，看不到什么领涨股</t>
+  </si>
+  <si>
     <t>股票</t>
   </si>
   <si>
@@ -951,6 +987,12 @@
   </si>
   <si>
     <t>大盘涨时，板块跌</t>
+  </si>
+  <si>
+    <t>贝肯能源</t>
+  </si>
+  <si>
+    <t>平量</t>
   </si>
   <si>
     <t>验证ID</t>
@@ -1201,9 +1243,6 @@
   </si>
   <si>
     <t>放量</t>
-  </si>
-  <si>
-    <t>平量</t>
   </si>
   <si>
     <t>缩量</t>
@@ -2607,7 +2646,7 @@
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="11.1538461538462" customWidth="1"/>
+    <col min="10" max="10" width="22.1923076923077" customWidth="1"/>
     <col min="11" max="11" width="6.69230769230769" customWidth="1"/>
     <col min="12" max="12" width="26" customWidth="1"/>
     <col min="13" max="13" width="14" customWidth="1"/>
@@ -3343,13 +3382,23 @@
     </row>
     <row r="16" ht="17" spans="1:26">
       <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="4"/>
+      <c r="B16" s="10">
+        <v>20260707</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="4">
+        <v>-0.0126</v>
+      </c>
       <c r="E16" s="3"/>
-      <c r="F16" s="10"/>
+      <c r="F16" s="10" t="s">
+        <v>71</v>
+      </c>
       <c r="G16" s="3"/>
-      <c r="H16" s="12"/>
+      <c r="H16" s="12">
+        <v>0.0217</v>
+      </c>
       <c r="I16" s="18"/>
       <c r="J16" s="18"/>
       <c r="K16" s="18"/>
@@ -3375,15 +3424,19 @@
       </c>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" spans="1:26">
+    <row r="17" ht="17" spans="1:26">
       <c r="A17" s="10"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
       <c r="D17" s="4"/>
       <c r="E17" s="3"/>
-      <c r="F17" s="10"/>
+      <c r="F17" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="G17" s="3"/>
-      <c r="H17" s="12"/>
+      <c r="H17" s="12">
+        <v>0.0177</v>
+      </c>
       <c r="I17" s="18"/>
       <c r="J17" s="18"/>
       <c r="K17" s="18"/>
@@ -3409,15 +3462,19 @@
       </c>
       <c r="Z17" s="3"/>
     </row>
-    <row r="18" spans="1:26">
+    <row r="18" ht="17" spans="1:26">
       <c r="A18" s="10"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
       <c r="D18" s="4"/>
       <c r="E18" s="3"/>
-      <c r="F18" s="10"/>
+      <c r="F18" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="G18" s="3"/>
-      <c r="H18" s="12"/>
+      <c r="H18" s="12">
+        <v>0.0122</v>
+      </c>
       <c r="I18" s="18"/>
       <c r="J18" s="18"/>
       <c r="K18" s="18"/>
@@ -3443,17 +3500,23 @@
       </c>
       <c r="Z18" s="3"/>
     </row>
-    <row r="19" spans="1:26">
+    <row r="19" ht="34" spans="1:26">
       <c r="A19" s="10"/>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="4"/>
       <c r="E19" s="3"/>
-      <c r="F19" s="10"/>
+      <c r="F19" s="10" t="s">
+        <v>63</v>
+      </c>
       <c r="G19" s="3"/>
-      <c r="H19" s="12"/>
+      <c r="H19" s="12">
+        <v>0.0091</v>
+      </c>
       <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
+      <c r="J19" s="18" t="s">
+        <v>74</v>
+      </c>
       <c r="K19" s="18"/>
       <c r="L19" s="18"/>
       <c r="M19" s="18"/>
@@ -3477,17 +3540,23 @@
       </c>
       <c r="Z19" s="3"/>
     </row>
-    <row r="20" spans="1:26">
+    <row r="20" ht="118" spans="1:26">
       <c r="A20" s="10"/>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
       <c r="D20" s="4"/>
       <c r="E20" s="3"/>
-      <c r="F20" s="10"/>
+      <c r="F20" s="10" t="s">
+        <v>51</v>
+      </c>
       <c r="G20" s="3"/>
-      <c r="H20" s="12"/>
+      <c r="H20" s="12">
+        <v>-0.0112</v>
+      </c>
       <c r="I20" s="18"/>
-      <c r="J20" s="18"/>
+      <c r="J20" s="18" t="s">
+        <v>75</v>
+      </c>
       <c r="K20" s="18"/>
       <c r="L20" s="18"/>
       <c r="M20" s="18"/>
@@ -3501,7 +3570,9 @@
         <v/>
       </c>
       <c r="T20" s="10"/>
-      <c r="U20" s="10"/>
+      <c r="U20" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
       <c r="X20" s="10"/>
@@ -3509,17 +3580,31 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Z20" s="3"/>
-    </row>
-    <row r="21" spans="1:26">
+      <c r="Z20" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" ht="17" spans="1:26">
       <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="4"/>
+      <c r="B21" s="10">
+        <v>20260708</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="4">
+        <v>-0.0049</v>
+      </c>
       <c r="E21" s="3"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="12"/>
+      <c r="F21" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H21" s="12">
+        <v>0.0352</v>
+      </c>
       <c r="I21" s="18"/>
       <c r="J21" s="18"/>
       <c r="K21" s="18"/>
@@ -3545,15 +3630,21 @@
       </c>
       <c r="Z21" s="3"/>
     </row>
-    <row r="22" spans="1:26">
+    <row r="22" ht="17" spans="1:26">
       <c r="A22" s="10"/>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
       <c r="D22" s="4"/>
       <c r="E22" s="3"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="12"/>
+      <c r="F22" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H22" s="12">
+        <v>0.0168</v>
+      </c>
       <c r="I22" s="18"/>
       <c r="J22" s="18"/>
       <c r="K22" s="18"/>
@@ -3579,15 +3670,21 @@
       </c>
       <c r="Z22" s="3"/>
     </row>
-    <row r="23" spans="1:26">
+    <row r="23" ht="17" spans="1:26">
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
       <c r="D23" s="4"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="12"/>
+      <c r="F23" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" s="12">
+        <v>0.0161</v>
+      </c>
       <c r="I23" s="18"/>
       <c r="J23" s="18"/>
       <c r="K23" s="18"/>
@@ -3613,17 +3710,23 @@
       </c>
       <c r="Z23" s="3"/>
     </row>
-    <row r="24" spans="1:26">
+    <row r="24" ht="51" spans="1:26">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="10"/>
       <c r="D24" s="4"/>
       <c r="E24" s="3"/>
-      <c r="F24" s="10"/>
+      <c r="F24" s="10" t="s">
+        <v>63</v>
+      </c>
       <c r="G24" s="3"/>
-      <c r="H24" s="12"/>
+      <c r="H24" s="12">
+        <v>0.0072</v>
+      </c>
       <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
+      <c r="J24" s="18" t="s">
+        <v>81</v>
+      </c>
       <c r="K24" s="18"/>
       <c r="L24" s="18"/>
       <c r="M24" s="18"/>
@@ -3645,7 +3748,9 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Z24" s="3"/>
+      <c r="Z24" s="3" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="25" spans="1:26">
       <c r="A25" s="10"/>
@@ -19927,7 +20032,8 @@
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="4" width="12" customWidth="1"/>
-    <col min="5" max="6" width="14" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="15.2307692307692" customWidth="1"/>
     <col min="7" max="7" width="24" customWidth="1"/>
     <col min="8" max="19" width="12" customWidth="1"/>
     <col min="20" max="23" width="24" customWidth="1"/>
@@ -19949,79 +20055,79 @@
         <v>24</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>40</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="S1" s="9" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="U1" s="9" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="V1" s="9" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="W1" s="9" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="X1" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="Y1" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="Z1" s="2" t="s">
         <v>45</v>
       </c>
       <c r="AA1" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="AC1" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="AD1" s="2" t="s">
         <v>46</v>
@@ -20056,10 +20162,10 @@
         <v>0</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="L2" s="10">
         <v>9.41</v>
@@ -20068,16 +20174,16 @@
         <v>0.1</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="R2" s="10">
         <v>9</v>
@@ -20086,17 +20192,17 @@
         <v>11</v>
       </c>
       <c r="T2" s="10" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="U2" s="10" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="V2" s="10" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="W2" s="10"/>
       <c r="X2" s="10" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="Y2" s="3"/>
       <c r="Z2" s="13" t="str">
@@ -20146,10 +20252,10 @@
         <v>待二次确认</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="L3" s="10">
         <v>31.23</v>
@@ -20158,16 +20264,16 @@
         <v>0.1</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="R3" s="10">
         <v>26</v>
@@ -20176,17 +20282,17 @@
         <v>32</v>
       </c>
       <c r="T3" s="10" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="U3" s="10" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="V3" s="10" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="W3" s="10"/>
       <c r="X3" s="10" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="Y3" s="3"/>
       <c r="Z3" s="13" t="str">
@@ -20236,10 +20342,10 @@
         <v>0</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="L4" s="10">
         <v>9.06</v>
@@ -20251,13 +20357,13 @@
         <v>53</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="R4" s="10">
         <v>9</v>
@@ -20268,11 +20374,11 @@
       <c r="T4" s="10"/>
       <c r="U4" s="10"/>
       <c r="V4" s="10" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="W4" s="10"/>
       <c r="X4" s="10" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="Y4" s="3"/>
       <c r="Z4" s="13" t="str">
@@ -20322,10 +20428,10 @@
         <v>0</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="L5" s="10">
         <v>9.45</v>
@@ -20334,16 +20440,16 @@
         <v>0.043</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="R5" s="10">
         <v>9</v>
@@ -20352,16 +20458,16 @@
         <v>9.84</v>
       </c>
       <c r="T5" s="10" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="U5" s="10" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="V5" s="10" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="W5" s="10" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="X5" s="10"/>
       <c r="Y5" s="3"/>
@@ -20383,13 +20489,23 @@
       </c>
       <c r="AD5" s="3"/>
     </row>
-    <row r="6" ht="17" spans="1:30">
+    <row r="6" ht="34" spans="1:30">
       <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="3"/>
+      <c r="B6" s="10">
+        <v>20260707</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="4">
+        <v>-0.0049</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="G6" s="10"/>
       <c r="H6" s="3" t="str">
         <f>IF(G6="","",IFERROR(VLOOKUP(G6,板块观察!A:Z,19,FALSE),""))</f>
@@ -20399,16 +20515,36 @@
         <f>IF(G6="","",IFERROR(VLOOKUP(G6,板块观察!A:Z,20,FALSE),""))</f>
         <v/>
       </c>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="10"/>
-      <c r="S6" s="10"/>
+      <c r="J6" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="L6" s="10">
+        <v>12.42</v>
+      </c>
+      <c r="M6" s="12">
+        <v>0.0463</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="R6" s="10">
+        <v>9</v>
+      </c>
+      <c r="S6" s="10">
+        <v>14</v>
+      </c>
       <c r="T6" s="10"/>
       <c r="U6" s="10"/>
       <c r="V6" s="10"/>
@@ -20419,21 +20555,21 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AA6" s="3" t="str">
+      <c r="AA6" s="3" t="e">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB6" s="3" t="str">
+        <v>#NUM!</v>
+      </c>
+      <c r="AB6" s="3" t="e">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="AC6" s="3" t="str">
+        <v>#NUM!</v>
+      </c>
+      <c r="AC6" s="3" t="e">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NUM!</v>
       </c>
       <c r="AD6" s="3"/>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" ht="17" spans="1:30">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="3"/>
@@ -45243,7 +45379,7 @@
     <dataValidation type="list" allowBlank="1" sqref="C4 C5 C2:C3 C6:C501">
       <formula1>选项!$B$1:$F$1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J4 J2:J3 J5:J501">
+    <dataValidation type="list" allowBlank="1" sqref="J4 J5 J6 J2:J3 J7:J501">
       <formula1>选项!$B$6:$G$6</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="K4 K2:K3 K5:K501">
@@ -45291,46 +45427,46 @@
   <sheetData>
     <row r="1" ht="34" spans="1:14">
       <c r="A1" s="9" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -54888,52 +55024,52 @@
   <sheetData>
     <row r="1" ht="17" spans="1:17">
       <c r="A1" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>46</v>
@@ -54943,13 +55079,13 @@
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="22" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="D2" s="3">
         <v>20260706</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="F2" s="3">
         <v>9.45</v>
@@ -54976,7 +55112,7 @@
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
       <c r="Q2" s="3" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -68998,10 +69134,10 @@
   <sheetData>
     <row r="1" ht="17" spans="1:5">
       <c r="A1" s="2" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
@@ -69009,7 +69145,7 @@
     </row>
     <row r="2" ht="34" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(板块观察!A2:A501)</f>
@@ -69021,7 +69157,7 @@
     </row>
     <row r="3" ht="17" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="B3" s="4">
         <f>IFERROR(AVERAGEIF(板块观察!N2:S501,"&gt;0"),"")</f>
@@ -69033,7 +69169,7 @@
     </row>
     <row r="4" ht="34" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="B4" s="3">
         <f>COUNTIF(板块观察!N2:S501,"&gt;=7")</f>
@@ -69045,7 +69181,7 @@
     </row>
     <row r="5" ht="17" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="B5" s="3">
         <f>COUNTA(每日复盘!A2:A501)</f>
@@ -69057,7 +69193,7 @@
     </row>
     <row r="6" ht="34" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="B6" s="4" t="str">
         <f>IFERROR(AVERAGEIF(每日复盘!Z2:Z501,"&gt;0"),"")</f>
@@ -69069,7 +69205,7 @@
     </row>
     <row r="7" ht="17" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="B7" s="3">
         <f>COUNTA(事后验证!A2:A501)</f>
@@ -69081,7 +69217,7 @@
     </row>
     <row r="8" ht="17" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="B8" s="3">
         <f>COUNTIF(事后验证!K2:K501,"正确")</f>
@@ -69093,7 +69229,7 @@
     </row>
     <row r="9" ht="17" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="B9" s="3">
         <f>COUNTIF(事后验证!K2:K501,"部分正确")</f>
@@ -69105,7 +69241,7 @@
     </row>
     <row r="10" ht="17" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B10" s="3">
         <f>COUNTIF(事后验证!K2:K501,"错误")</f>
@@ -69117,7 +69253,7 @@
     </row>
     <row r="11" ht="34" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="B11" s="3">
         <f>COUNTA(模拟交易!A2:A501)</f>
@@ -69129,7 +69265,7 @@
     </row>
     <row r="12" ht="17" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="B12" s="3">
         <f>COUNTIF(模拟交易!O2:O501,"成功")</f>
@@ -69141,7 +69277,7 @@
     </row>
     <row r="13" ht="17" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="B13" s="3">
         <f>COUNTIF(模拟交易!O2:O501,"失败")</f>
@@ -69153,7 +69289,7 @@
     </row>
     <row r="14" ht="17" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="B14" s="4" t="str">
         <f>IFERROR(B12/(B12+B13),"")</f>
@@ -69165,7 +69301,7 @@
     </row>
     <row r="15" ht="17" spans="1:5">
       <c r="A15" s="5" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="B15" s="6" t="str">
         <f>IFERROR(AVERAGEIF(模拟交易!L2:L501,"&lt;&gt;"),"")</f>
@@ -69177,7 +69313,7 @@
     </row>
     <row r="16" ht="17" spans="1:5">
       <c r="A16" s="3" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="B16" s="4">
         <f>IFERROR(MIN(模拟交易!L2:L501),"")</f>
@@ -69196,10 +69332,10 @@
     </row>
     <row r="18" ht="17" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -69207,7 +69343,7 @@
     </row>
     <row r="19" ht="17" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="B19" s="3">
         <f>COUNTIF(事后验证!L2:L501,"假突破误判")+COUNTIF(模拟交易!P2:P501,"假突破误判")</f>
@@ -69219,7 +69355,7 @@
     </row>
     <row r="20" ht="34" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="B20" s="3">
         <f>COUNTIF(事后验证!L2:L501,"低位突破确认不足")+COUNTIF(模拟交易!P2:P501,"低位突破确认不足")</f>
@@ -69231,7 +69367,7 @@
     </row>
     <row r="21" ht="17" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="B21" s="3">
         <f>COUNTIF(事后验证!L2:L501,"支撑误判")+COUNTIF(模拟交易!P2:P501,"支撑误判")</f>
@@ -69243,7 +69379,7 @@
     </row>
     <row r="22" ht="17" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="B22" s="3">
         <f>COUNTIF(事后验证!L2:L501,"买入过早")+COUNTIF(模拟交易!P2:P501,"买入过早")</f>
@@ -69255,7 +69391,7 @@
     </row>
     <row r="23" ht="34" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="B23" s="3">
         <f>COUNTIF(事后验证!L2:L501,"放量滞涨后退出慢")+COUNTIF(模拟交易!P2:P501,"放量滞涨后退出慢")</f>
@@ -69267,7 +69403,7 @@
     </row>
     <row r="24" ht="34" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="B24" s="3">
         <f>COUNTIF(事后验证!L2:L501,"板块强弱误判")+COUNTIF(模拟交易!P2:P501,"板块强弱误判")</f>
@@ -69279,7 +69415,7 @@
     </row>
     <row r="25" ht="34" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="B25" s="3">
         <f>COUNTIF(事后验证!L2:L501,"成交量理解错误")+COUNTIF(模拟交易!P2:P501,"成交量理解错误")</f>
@@ -69291,7 +69427,7 @@
     </row>
     <row r="26" ht="17" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="B26" s="3">
         <f>COUNTIF(事后验证!L2:L501,"减仓偏早")+COUNTIF(模拟交易!P2:P501,"减仓偏早")</f>
@@ -69310,7 +69446,7 @@
     </row>
     <row r="28" ht="34" spans="1:5">
       <c r="A28" s="7" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -69322,17 +69458,17 @@
         <v>40</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
     </row>
     <row r="30" ht="17" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="B30" s="3">
         <f>COUNTIF(板块观察!O2:T501,"新启动")</f>
@@ -69362,7 +69498,7 @@
     </row>
     <row r="32" ht="17" spans="1:5">
       <c r="A32" s="3" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="B32" s="3">
         <f>COUNTIF(板块观察!O2:T501,"主升中段")</f>
@@ -69377,7 +69513,7 @@
     </row>
     <row r="33" ht="17" spans="1:5">
       <c r="A33" s="3" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="B33" s="3">
         <f>COUNTIF(板块观察!O2:T501,"高潮加速")</f>
@@ -69392,7 +69528,7 @@
     </row>
     <row r="34" ht="17" spans="1:5">
       <c r="A34" s="3" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="B34" s="3">
         <f>COUNTIF(板块观察!O2:T501,"高位震荡")</f>
@@ -69407,7 +69543,7 @@
     </row>
     <row r="35" ht="17" spans="1:5">
       <c r="A35" s="3" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="B35" s="3">
         <f>COUNTIF(板块观察!O2:T501,"退潮")</f>
@@ -69422,7 +69558,7 @@
     </row>
     <row r="36" ht="17" spans="1:5">
       <c r="A36" s="3" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="B36" s="3">
         <f>COUNTIF(板块观察!O2:T501,"待观察")</f>
@@ -69444,7 +69580,7 @@
     </row>
     <row r="38" ht="34" spans="1:5">
       <c r="A38" s="7" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -69453,32 +69589,32 @@
     </row>
     <row r="39" ht="17" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" ht="17" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B40" s="3">
         <f>COUNTIF(每日复盘!J2:J501,"领涨股")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C40" s="3">
         <f>COUNTIFS(每日复盘!J2:J501,"领涨股",每日复盘!K2:K501,"强于板块")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D40" s="3">
         <f>COUNTIFS(每日复盘!J2:J501,"领涨股",每日复盘!K2:K501,"同步板块")</f>
@@ -69533,7 +69669,7 @@
     </row>
     <row r="43" ht="17" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="B43" s="3">
         <f>COUNTIF(每日复盘!J2:J501,"跟风股")</f>
@@ -69554,7 +69690,7 @@
     </row>
     <row r="44" ht="17" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="B44" s="3">
         <f>COUNTIF(每日复盘!J2:J501,"弱反弹股")</f>
@@ -69575,7 +69711,7 @@
     </row>
     <row r="45" ht="17" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="B45" s="3">
         <f>COUNTIF(每日复盘!J2:J501,"未分类")</f>
@@ -69603,7 +69739,7 @@
     </row>
     <row r="47" ht="17" spans="1:5">
       <c r="A47" s="7" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -69612,28 +69748,28 @@
     </row>
     <row r="48" ht="17" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
     </row>
     <row r="49" ht="17" spans="1:5">
       <c r="A49" s="3" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B49" s="3">
         <f>COUNTIF(每日复盘!N2:N501,"上升趋势")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C49" s="3">
         <f>COUNTIFS(事后验证!E2:E501,"上升趋势",事后验证!K2:K501,"正确")</f>
@@ -69650,7 +69786,7 @@
     </row>
     <row r="50" ht="17" spans="1:5">
       <c r="A50" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="B50" s="3">
         <f>COUNTIF(每日复盘!N2:N501,"震荡")</f>
@@ -69671,7 +69807,7 @@
     </row>
     <row r="51" ht="17" spans="1:5">
       <c r="A51" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="B51" s="3">
         <f>COUNTIF(每日复盘!N2:N501,"下降逆转")</f>
@@ -69692,7 +69828,7 @@
     </row>
     <row r="52" ht="34" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="B52" s="3">
         <f>COUNTIF(每日复盘!N2:N501,"箱体突破初期")</f>
@@ -69713,7 +69849,7 @@
     </row>
     <row r="53" ht="17" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="B53" s="3">
         <f>COUNTIF(每日复盘!N2:N501,"突破后回踩")</f>
@@ -69734,7 +69870,7 @@
     </row>
     <row r="54" ht="17" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="B54" s="3">
         <f>COUNTIF(每日复盘!N2:N501,"下降趋势")</f>
@@ -69755,7 +69891,7 @@
     </row>
     <row r="55" ht="17" spans="1:5">
       <c r="A55" s="3" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="B55" s="3">
         <f>COUNTIF(每日复盘!N2:N501,"假突破")</f>
@@ -69794,13 +69930,13 @@
         <v>47</v>
       </c>
       <c r="C1" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="D1" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="E1" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="F1" t="s">
         <v>53</v>
@@ -69811,16 +69947,16 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="C2" t="s">
-        <v>201</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="E2" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -69831,7 +69967,7 @@
         <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -69839,10 +69975,10 @@
         <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="C4" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="D4" t="s">
         <v>57</v>
@@ -69851,41 +69987,41 @@
         <v>68</v>
       </c>
       <c r="F4" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="G4" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="H4" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="I4" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="J4" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="B5" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="C5" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="D5" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C6" t="s">
         <v>42</v>
@@ -69894,288 +70030,288 @@
         <v>43</v>
       </c>
       <c r="E6" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="F6" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="G6" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C7" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D7" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="E7" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C8" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="D8" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="E8" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F8" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="G8" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="H8" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="I8" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="J8" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="C9" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B10" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="C10" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
+        <v>229</v>
+      </c>
+      <c r="F10" t="s">
+        <v>230</v>
+      </c>
+      <c r="G10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H10" t="s">
+        <v>232</v>
+      </c>
+      <c r="I10" t="s">
         <v>216</v>
-      </c>
-      <c r="F10" t="s">
-        <v>217</v>
-      </c>
-      <c r="G10" t="s">
-        <v>218</v>
-      </c>
-      <c r="H10" t="s">
-        <v>219</v>
-      </c>
-      <c r="I10" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B11" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="E11" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="F11" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="G11" t="s">
-        <v>201</v>
+        <v>131</v>
       </c>
       <c r="H11" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B12" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="E12" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="F12" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="G12" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="H12" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B13" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C13" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="D13" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="E13" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="B14" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="C14" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="D14" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="1" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="E15" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="1" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="B16" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="C16" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="D16" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="E16" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="1" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="B17" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C17" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="D17" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="E17" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="F17" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="G17" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="H17" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="I17" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="J17" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="B18" t="s">
+        <v>249</v>
+      </c>
+      <c r="C18" t="s">
+        <v>250</v>
+      </c>
+      <c r="D18" t="s">
+        <v>251</v>
+      </c>
+      <c r="E18" t="s">
         <v>236</v>
-      </c>
-      <c r="C18" t="s">
-        <v>237</v>
-      </c>
-      <c r="D18" t="s">
-        <v>238</v>
-      </c>
-      <c r="E18" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="1" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="B19" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="C19" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="D19" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="E19" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>

--- a/stock_review_template.xlsx
+++ b/stock_review_template.xlsx
@@ -190,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -257,6 +257,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -638,7 +656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -772,6 +790,34 @@
       <c r="B12" s="3" t="inlineStr">
         <is>
           <t>每天不是“填满”就算完成，而是至少产出 1 条有效理由链。完整度检查有没有填，理由链质量检查有没有认真思考。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>长电科技10日样本数据说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>样本写入位置：每日观察!2:11，事后验证!2:8。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>个股数据：搜狐历史行情接口 cn_600584；大盘数据：搜狐历史行情接口 zs_000001；板块数据：东方财富半导体板块 BK1036。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>样本日期范围：2025-06-26 至 2025-07-09，共10个交易日；因当前接口未返回2026年数据，本样本按可取得的最近完整窗口填写。</t>
         </is>
       </c>
     </row>
@@ -982,511 +1028,1491 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="72" customHeight="1">
       <c r="A2" s="7">
         <f>IF(B2="","",TEXT(B2,"yyyymmdd")&amp;"-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="9" t="n"/>
-      <c r="F2" s="9" t="n"/>
-      <c r="G2" s="9" t="n"/>
-      <c r="H2" s="9" t="n"/>
-      <c r="I2" s="9" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="9" t="n"/>
-      <c r="L2" s="9" t="n"/>
-      <c r="M2" s="9" t="n"/>
-      <c r="N2" s="10" t="n"/>
-      <c r="O2" s="9" t="n"/>
-      <c r="P2" s="10" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="R2" s="9" t="n"/>
-      <c r="S2" s="10" t="n"/>
-      <c r="T2" s="10" t="n"/>
-      <c r="U2" s="11" t="n"/>
-      <c r="V2" s="11" t="n"/>
-      <c r="W2" s="12">
+      <c r="B2" s="25" t="n">
+        <v>45834</v>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>长电科技 600584.SH</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>半导体/封测</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>强于板块</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>前高</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>33.30-33.40</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>6月25日前高33.30，今日最高33.40但收32.96，说明上方第一次出现分歧。</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>接近</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>冲高回落</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>收32.96跌0.78%，盘中最高33.40触及前高区，成交量26.21万手；半导体跌1.17%，上证跌0.22%。</t>
+        </is>
+      </c>
+      <c r="O2" s="10" t="inlineStr">
+        <is>
+          <t>高位分歧</t>
+        </is>
+      </c>
+      <c r="P2" s="10" t="inlineStr">
+        <is>
+          <t>价格接近前高后没有收住，说明33.30-33.40附近存在短线抛压；但个股跌幅小于半导体，不能直接判定转弱。</t>
+        </is>
+      </c>
+      <c r="Q2" s="10" t="inlineStr">
+        <is>
+          <t>如果随后1-3日重新放量站上33.40，今天更像突破前正常分歧，而不是上攻失败。</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="S2" s="10" t="inlineStr">
+        <is>
+          <t>有明确前高和冲高回落事实，但板块当天较弱，单日不能确认失败。</t>
+        </is>
+      </c>
+      <c r="T2" s="10" t="inlineStr">
+        <is>
+          <t>后续只看是否收盘重新站上33.40。</t>
+        </is>
+      </c>
+      <c r="U2" s="11" t="inlineStr">
+        <is>
+          <t>前高区间确认、冲高回落与板块环境区分</t>
+        </is>
+      </c>
+      <c r="V2" s="11" t="inlineStr">
+        <is>
+          <t>数据源：搜狐历史行情个股；东方财富半导体板块；窗口为2025-06-26至2025-07-09。</t>
+        </is>
+      </c>
+      <c r="W2" s="26">
         <f>IF(B2="","",B2+3)</f>
         <v/>
       </c>
-      <c r="X2" s="12">
+      <c r="X2" s="26">
         <f>IF(B2="","",B2+5)</f>
         <v/>
       </c>
-      <c r="Y2" s="12">
+      <c r="Y2" s="26">
         <f>IF(B2="","",B2+10)</f>
         <v/>
       </c>
-      <c r="Z2" s="13">
+      <c r="Z2" s="27">
         <f>IF(B2="","",(--(B2&lt;&gt;"")+--(C2&lt;&gt;"")+--(D2&lt;&gt;"")+--(E2&lt;&gt;"")+--(F2&lt;&gt;"")+--(G2&lt;&gt;"")+--(H2&lt;&gt;"")+--(I2&lt;&gt;"")+--(J2&lt;&gt;"")+--(K2&lt;&gt;"")+--(L2&lt;&gt;"")+--(M2&lt;&gt;"")+--(N2&lt;&gt;"")+--(O2&lt;&gt;"")+--(P2&lt;&gt;"")+--(Q2&lt;&gt;"")+--(R2&lt;&gt;"")+--(S2&lt;&gt;"")+--(T2&lt;&gt;""))/19)</f>
         <v/>
       </c>
-      <c r="AA2" s="16" t="n"/>
-      <c r="AB2" s="16" t="n"/>
-      <c r="AC2" s="16" t="n"/>
-      <c r="AD2" s="16" t="n"/>
+      <c r="AA2" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AB2" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AC2" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AD2" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
       <c r="AE2" s="7">
         <f>IF(B2="","",IF(AND(AA2="合格",AB2="合格",AC2="合格",AD2="合格"),"有效","无效"))</f>
         <v/>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="72" customHeight="1">
       <c r="A3" s="7">
         <f>IF(B3="","",TEXT(B3,"yyyymmdd")&amp;"-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B3" s="8" t="n"/>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="9" t="n"/>
-      <c r="F3" s="9" t="n"/>
-      <c r="G3" s="9" t="n"/>
-      <c r="H3" s="9" t="n"/>
-      <c r="I3" s="9" t="n"/>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="9" t="n"/>
-      <c r="L3" s="9" t="n"/>
-      <c r="M3" s="9" t="n"/>
-      <c r="N3" s="10" t="n"/>
-      <c r="O3" s="9" t="n"/>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="9" t="n"/>
-      <c r="S3" s="10" t="n"/>
-      <c r="T3" s="10" t="n"/>
-      <c r="U3" s="11" t="n"/>
-      <c r="V3" s="11" t="n"/>
-      <c r="W3" s="12">
+      <c r="B3" s="25" t="n">
+        <v>45835</v>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>长电科技 600584.SH</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>半导体/封测</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>轮动强势</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>强于板块</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>前高</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>33.40</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>前一日最高33.40形成短线压力，今日最高34.08且收33.60。</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>突破</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>清晰</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>放量突破</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>收33.60涨1.94%，最高34.08，成交量46.41万手明显放大；半导体涨1.08%，上证跌0.70%。</t>
+        </is>
+      </c>
+      <c r="O3" s="10" t="inlineStr">
+        <is>
+          <t>真突破/启动尝试</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="inlineStr">
+        <is>
+          <t>在大盘走弱时个股放量收过33.40，且强于半导体，说明有资金主动推动突破。</t>
+        </is>
+      </c>
+      <c r="Q3" s="10" t="inlineStr">
+        <is>
+          <t>收盘离日高较远，若很快跌回33.40下方并放量，突破解释会削弱。</t>
+        </is>
+      </c>
+      <c r="R3" s="10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>量价与相对强弱都支持，但只是一日突破，还没有回踩确认。</t>
+        </is>
+      </c>
+      <c r="T3" s="10" t="inlineStr">
+        <is>
+          <t>后续只看是否守住33.30-33.40。</t>
+        </is>
+      </c>
+      <c r="U3" s="11" t="inlineStr">
+        <is>
+          <t>突破有效性、放量含义、回踩确认</t>
+        </is>
+      </c>
+      <c r="V3" s="11" t="inlineStr">
+        <is>
+          <t>这是突破尝试，不等于已经进入主升。</t>
+        </is>
+      </c>
+      <c r="W3" s="26">
         <f>IF(B3="","",B3+3)</f>
         <v/>
       </c>
-      <c r="X3" s="12">
+      <c r="X3" s="26">
         <f>IF(B3="","",B3+5)</f>
         <v/>
       </c>
-      <c r="Y3" s="12">
+      <c r="Y3" s="26">
         <f>IF(B3="","",B3+10)</f>
         <v/>
       </c>
-      <c r="Z3" s="13">
+      <c r="Z3" s="27">
         <f>IF(B3="","",(--(B3&lt;&gt;"")+--(C3&lt;&gt;"")+--(D3&lt;&gt;"")+--(E3&lt;&gt;"")+--(F3&lt;&gt;"")+--(G3&lt;&gt;"")+--(H3&lt;&gt;"")+--(I3&lt;&gt;"")+--(J3&lt;&gt;"")+--(K3&lt;&gt;"")+--(L3&lt;&gt;"")+--(M3&lt;&gt;"")+--(N3&lt;&gt;"")+--(O3&lt;&gt;"")+--(P3&lt;&gt;"")+--(Q3&lt;&gt;"")+--(R3&lt;&gt;"")+--(S3&lt;&gt;"")+--(T3&lt;&gt;""))/19)</f>
         <v/>
       </c>
-      <c r="AA3" s="16" t="n"/>
-      <c r="AB3" s="16" t="n"/>
-      <c r="AC3" s="16" t="n"/>
-      <c r="AD3" s="16" t="n"/>
+      <c r="AA3" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AB3" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AC3" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AD3" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
       <c r="AE3" s="7">
         <f>IF(B3="","",IF(AND(AA3="合格",AB3="合格",AC3="合格",AD3="合格"),"有效","无效"))</f>
         <v/>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="72" customHeight="1">
       <c r="A4" s="7">
         <f>IF(B4="","",TEXT(B4,"yyyymmdd")&amp;"-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B4" s="8" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="9" t="n"/>
-      <c r="F4" s="9" t="n"/>
-      <c r="G4" s="9" t="n"/>
-      <c r="H4" s="9" t="n"/>
-      <c r="I4" s="9" t="n"/>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" s="9" t="n"/>
-      <c r="M4" s="9" t="n"/>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="9" t="n"/>
-      <c r="P4" s="10" t="n"/>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="9" t="n"/>
-      <c r="S4" s="10" t="n"/>
-      <c r="T4" s="10" t="n"/>
-      <c r="U4" s="11" t="n"/>
-      <c r="V4" s="11" t="n"/>
-      <c r="W4" s="12">
+      <c r="B4" s="25" t="n">
+        <v>45838</v>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>长电科技 600584.SH</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>半导体/封测</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>主线强势</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>弱于板块</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>前高</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>34.08</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>6月27日突破日最高34.08是新的短线观察压力。</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>接近</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>横盘震荡</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>收33.69涨0.27%，成交量30.02万手缩小；半导体涨1.67%，上证涨0.59%。</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="inlineStr">
+        <is>
+          <t>震荡整理</t>
+        </is>
+      </c>
+      <c r="P4" s="10" t="inlineStr">
+        <is>
+          <t>突破后没有继续放量上攻，只是在33.40上方小幅整理；但弱于强势板块，说明主动性不足。</t>
+        </is>
+      </c>
+      <c r="Q4" s="10" t="inlineStr">
+        <is>
+          <t>如果次日放量站上34.08，则今天的缩量可能只是突破后的蓄势。</t>
+        </is>
+      </c>
+      <c r="R4" s="10" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>事实更多指向整理，但是否转弱还缺少跌破关键位。</t>
+        </is>
+      </c>
+      <c r="T4" s="10" t="inlineStr">
+        <is>
+          <t>后续只看是否收盘站上34.08。</t>
+        </is>
+      </c>
+      <c r="U4" s="11" t="inlineStr">
+        <is>
+          <t>突破后缩量整理、相对板块弱势识别</t>
+        </is>
+      </c>
+      <c r="V4" s="11" t="inlineStr">
+        <is>
+          <t>这一天的重点不是预测涨跌，而是识别“突破后没有立刻延续”。</t>
+        </is>
+      </c>
+      <c r="W4" s="26">
         <f>IF(B4="","",B4+3)</f>
         <v/>
       </c>
-      <c r="X4" s="12">
+      <c r="X4" s="26">
         <f>IF(B4="","",B4+5)</f>
         <v/>
       </c>
-      <c r="Y4" s="12">
+      <c r="Y4" s="26">
         <f>IF(B4="","",B4+10)</f>
         <v/>
       </c>
-      <c r="Z4" s="13">
+      <c r="Z4" s="27">
         <f>IF(B4="","",(--(B4&lt;&gt;"")+--(C4&lt;&gt;"")+--(D4&lt;&gt;"")+--(E4&lt;&gt;"")+--(F4&lt;&gt;"")+--(G4&lt;&gt;"")+--(H4&lt;&gt;"")+--(I4&lt;&gt;"")+--(J4&lt;&gt;"")+--(K4&lt;&gt;"")+--(L4&lt;&gt;"")+--(M4&lt;&gt;"")+--(N4&lt;&gt;"")+--(O4&lt;&gt;"")+--(P4&lt;&gt;"")+--(Q4&lt;&gt;"")+--(R4&lt;&gt;"")+--(S4&lt;&gt;"")+--(T4&lt;&gt;""))/19)</f>
         <v/>
       </c>
-      <c r="AA4" s="16" t="n"/>
-      <c r="AB4" s="16" t="n"/>
-      <c r="AC4" s="16" t="n"/>
-      <c r="AD4" s="16" t="n"/>
+      <c r="AA4" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AB4" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AC4" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AD4" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
       <c r="AE4" s="7">
         <f>IF(B4="","",IF(AND(AA4="合格",AB4="合格",AC4="合格",AD4="合格"),"有效","无效"))</f>
         <v/>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="72" customHeight="1">
       <c r="A5" s="7">
         <f>IF(B5="","",TEXT(B5,"yyyymmdd")&amp;"-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="9" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="9" t="n"/>
-      <c r="F5" s="9" t="n"/>
-      <c r="G5" s="9" t="n"/>
-      <c r="H5" s="9" t="n"/>
-      <c r="I5" s="9" t="n"/>
-      <c r="J5" s="10" t="n"/>
-      <c r="K5" s="9" t="n"/>
-      <c r="L5" s="9" t="n"/>
-      <c r="M5" s="9" t="n"/>
-      <c r="N5" s="10" t="n"/>
-      <c r="O5" s="9" t="n"/>
-      <c r="P5" s="10" t="n"/>
-      <c r="Q5" s="10" t="n"/>
-      <c r="R5" s="9" t="n"/>
-      <c r="S5" s="10" t="n"/>
-      <c r="T5" s="10" t="n"/>
-      <c r="U5" s="11" t="n"/>
-      <c r="V5" s="11" t="n"/>
-      <c r="W5" s="12">
+      <c r="B5" s="25" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>长电科技 600584.SH</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>半导体/封测</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>轮动强势</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>强于板块</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>前高</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>34.08</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>6月27日高点34.08被盘中突破，但收盘33.97没有站上。</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>站上未确认</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>清晰</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>高位放量震荡</t>
+        </is>
+      </c>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>收33.97涨0.83%，盘中最高34.38创短线新高，成交量39.29万手；半导体涨0.33%，上证涨0.39%。</t>
+        </is>
+      </c>
+      <c r="O5" s="10" t="inlineStr">
+        <is>
+          <t>高位分歧</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="inlineStr">
+        <is>
+          <t>盘中新高但收回34.08下方，说明新高位置有抛压；不过个股仍强于板块，不能直接判定见顶。</t>
+        </is>
+      </c>
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
+          <t>如果后续收盘站回34.08并继续放量，新高回落可能只是分歧换手。</t>
+        </is>
+      </c>
+      <c r="R5" s="10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>关键位清晰且有冲高回落，但趋势尚未破坏。</t>
+        </is>
+      </c>
+      <c r="T5" s="10" t="inlineStr">
+        <is>
+          <t>后续只看是否收盘站上34.08。</t>
+        </is>
+      </c>
+      <c r="U5" s="11" t="inlineStr">
+        <is>
+          <t>盘中新高与收盘确认、分歧换手</t>
+        </is>
+      </c>
+      <c r="V5" s="11" t="inlineStr">
+        <is>
+          <t>这是判断“真突破还是假突破”的典型样本。</t>
+        </is>
+      </c>
+      <c r="W5" s="26">
         <f>IF(B5="","",B5+3)</f>
         <v/>
       </c>
-      <c r="X5" s="12">
+      <c r="X5" s="26">
         <f>IF(B5="","",B5+5)</f>
         <v/>
       </c>
-      <c r="Y5" s="12">
+      <c r="Y5" s="26">
         <f>IF(B5="","",B5+10)</f>
         <v/>
       </c>
-      <c r="Z5" s="13">
+      <c r="Z5" s="27">
         <f>IF(B5="","",(--(B5&lt;&gt;"")+--(C5&lt;&gt;"")+--(D5&lt;&gt;"")+--(E5&lt;&gt;"")+--(F5&lt;&gt;"")+--(G5&lt;&gt;"")+--(H5&lt;&gt;"")+--(I5&lt;&gt;"")+--(J5&lt;&gt;"")+--(K5&lt;&gt;"")+--(L5&lt;&gt;"")+--(M5&lt;&gt;"")+--(N5&lt;&gt;"")+--(O5&lt;&gt;"")+--(P5&lt;&gt;"")+--(Q5&lt;&gt;"")+--(R5&lt;&gt;"")+--(S5&lt;&gt;"")+--(T5&lt;&gt;""))/19)</f>
         <v/>
       </c>
-      <c r="AA5" s="16" t="n"/>
-      <c r="AB5" s="16" t="n"/>
-      <c r="AC5" s="16" t="n"/>
-      <c r="AD5" s="16" t="n"/>
+      <c r="AA5" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AB5" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AC5" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AD5" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
       <c r="AE5" s="7">
         <f>IF(B5="","",IF(AND(AA5="合格",AB5="合格",AC5="合格",AD5="合格"),"有效","无效"))</f>
         <v/>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="72" customHeight="1">
       <c r="A6" s="7">
         <f>IF(B6="","",TEXT(B6,"yyyymmdd")&amp;"-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="9" t="n"/>
-      <c r="E6" s="9" t="n"/>
-      <c r="F6" s="9" t="n"/>
-      <c r="G6" s="9" t="n"/>
-      <c r="H6" s="9" t="n"/>
-      <c r="I6" s="9" t="n"/>
-      <c r="J6" s="10" t="n"/>
-      <c r="K6" s="9" t="n"/>
-      <c r="L6" s="9" t="n"/>
-      <c r="M6" s="9" t="n"/>
-      <c r="N6" s="10" t="n"/>
-      <c r="O6" s="9" t="n"/>
-      <c r="P6" s="10" t="n"/>
-      <c r="Q6" s="10" t="n"/>
-      <c r="R6" s="9" t="n"/>
-      <c r="S6" s="10" t="n"/>
-      <c r="T6" s="10" t="n"/>
-      <c r="U6" s="11" t="n"/>
-      <c r="V6" s="11" t="n"/>
-      <c r="W6" s="12">
+      <c r="B6" s="25" t="n">
+        <v>45840</v>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>长电科技 600584.SH</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>半导体/封测</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>退潮</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>强于板块</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>大阳线低点</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>33.00-33.30</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>6月27日放量阳线低点33.00，6月25日前高33.30附近构成回踩观察区。</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>回踩</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>缩量回调</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>收33.31跌1.94%，最低33.23，成交量26.21万手；半导体跌2.18%，上证跌0.09%。</t>
+        </is>
+      </c>
+      <c r="O6" s="10" t="inlineStr">
+        <is>
+          <t>健康回调</t>
+        </is>
+      </c>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>价格回到33.00-33.30支撑区附近但没有明显放量跌破，且跌幅小于半导体，暂时更像突破后的回踩。</t>
+        </is>
+      </c>
+      <c r="Q6" s="10" t="inlineStr">
+        <is>
+          <t>如果随后跌破33.00并收不回，健康回调解释会被证伪。</t>
+        </is>
+      </c>
+      <c r="R6" s="10" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>回踩区间是人工划出来的，不够精确，只能作为低强度假设。</t>
+        </is>
+      </c>
+      <c r="T6" s="10" t="inlineStr">
+        <is>
+          <t>后续只看是否跌破33.00。</t>
+        </is>
+      </c>
+      <c r="U6" s="11" t="inlineStr">
+        <is>
+          <t>大阳线低点、支撑区间而非单点、缩量回调</t>
+        </is>
+      </c>
+      <c r="V6" s="11" t="inlineStr">
+        <is>
+          <t>这行故意保持低判断强度，因为支撑区不是非常清晰。</t>
+        </is>
+      </c>
+      <c r="W6" s="26">
         <f>IF(B6="","",B6+3)</f>
         <v/>
       </c>
-      <c r="X6" s="12">
+      <c r="X6" s="26">
         <f>IF(B6="","",B6+5)</f>
         <v/>
       </c>
-      <c r="Y6" s="12">
+      <c r="Y6" s="26">
         <f>IF(B6="","",B6+10)</f>
         <v/>
       </c>
-      <c r="Z6" s="13">
+      <c r="Z6" s="27">
         <f>IF(B6="","",(--(B6&lt;&gt;"")+--(C6&lt;&gt;"")+--(D6&lt;&gt;"")+--(E6&lt;&gt;"")+--(F6&lt;&gt;"")+--(G6&lt;&gt;"")+--(H6&lt;&gt;"")+--(I6&lt;&gt;"")+--(J6&lt;&gt;"")+--(K6&lt;&gt;"")+--(L6&lt;&gt;"")+--(M6&lt;&gt;"")+--(N6&lt;&gt;"")+--(O6&lt;&gt;"")+--(P6&lt;&gt;"")+--(Q6&lt;&gt;"")+--(R6&lt;&gt;"")+--(S6&lt;&gt;"")+--(T6&lt;&gt;""))/19)</f>
         <v/>
       </c>
-      <c r="AA6" s="16" t="n"/>
-      <c r="AB6" s="16" t="n"/>
-      <c r="AC6" s="16" t="n"/>
-      <c r="AD6" s="16" t="n"/>
+      <c r="AA6" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AB6" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AC6" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AD6" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
       <c r="AE6" s="7">
         <f>IF(B6="","",IF(AND(AA6="合格",AB6="合格",AC6="合格",AD6="合格"),"有效","无效"))</f>
         <v/>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="72" customHeight="1">
       <c r="A7" s="7">
         <f>IF(B7="","",TEXT(B7,"yyyymmdd")&amp;"-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="9" t="n"/>
-      <c r="G7" s="9" t="n"/>
-      <c r="H7" s="9" t="n"/>
-      <c r="I7" s="9" t="n"/>
-      <c r="J7" s="10" t="n"/>
-      <c r="K7" s="9" t="n"/>
-      <c r="L7" s="9" t="n"/>
-      <c r="M7" s="9" t="n"/>
-      <c r="N7" s="10" t="n"/>
-      <c r="O7" s="9" t="n"/>
-      <c r="P7" s="10" t="n"/>
-      <c r="Q7" s="10" t="n"/>
-      <c r="R7" s="9" t="n"/>
-      <c r="S7" s="10" t="n"/>
-      <c r="T7" s="10" t="n"/>
-      <c r="U7" s="11" t="n"/>
-      <c r="V7" s="11" t="n"/>
-      <c r="W7" s="12">
+      <c r="B7" s="25" t="n">
+        <v>45841</v>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>长电科技 600584.SH</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>半导体/封测</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>强于板块</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>箱体下沿</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>33.20-33.30</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>7月2日低点33.23与7月3日低点33.23重合，形成短线震荡下沿。</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>回踩</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>回踩支撑不破</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>收33.53涨0.66%，最低33.23再次守住，成交量21.32万手继续缩小；半导体涨0.36%，上证涨0.18%。</t>
+        </is>
+      </c>
+      <c r="O7" s="10" t="inlineStr">
+        <is>
+          <t>震荡整理</t>
+        </is>
+      </c>
+      <c r="P7" s="10" t="inlineStr">
+        <is>
+          <t>同一低点附近两次守住，价格没有继续向下；但成交量缩小，说明反弹力度也不强。</t>
+        </is>
+      </c>
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
+          <t>如果后续跌破33.20，所谓箱体下沿就只是临时巧合。</t>
+        </is>
+      </c>
+      <c r="R7" s="10" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>只有两个交易日的低点，结构证据偏少。</t>
+        </is>
+      </c>
+      <c r="T7" s="10" t="inlineStr">
+        <is>
+          <t>后续只看是否跌破33.20。</t>
+        </is>
+      </c>
+      <c r="U7" s="11" t="inlineStr">
+        <is>
+          <t>箱体下沿需要多次确认、缩量反弹强弱</t>
+        </is>
+      </c>
+      <c r="V7" s="11" t="inlineStr">
+        <is>
+          <t>这是一条“暂时结构”，不是强结论。</t>
+        </is>
+      </c>
+      <c r="W7" s="26">
         <f>IF(B7="","",B7+3)</f>
         <v/>
       </c>
-      <c r="X7" s="12">
+      <c r="X7" s="26">
         <f>IF(B7="","",B7+5)</f>
         <v/>
       </c>
-      <c r="Y7" s="12">
+      <c r="Y7" s="26">
         <f>IF(B7="","",B7+10)</f>
         <v/>
       </c>
-      <c r="Z7" s="13">
+      <c r="Z7" s="27">
         <f>IF(B7="","",(--(B7&lt;&gt;"")+--(C7&lt;&gt;"")+--(D7&lt;&gt;"")+--(E7&lt;&gt;"")+--(F7&lt;&gt;"")+--(G7&lt;&gt;"")+--(H7&lt;&gt;"")+--(I7&lt;&gt;"")+--(J7&lt;&gt;"")+--(K7&lt;&gt;"")+--(L7&lt;&gt;"")+--(M7&lt;&gt;"")+--(N7&lt;&gt;"")+--(O7&lt;&gt;"")+--(P7&lt;&gt;"")+--(Q7&lt;&gt;"")+--(R7&lt;&gt;"")+--(S7&lt;&gt;"")+--(T7&lt;&gt;""))/19)</f>
         <v/>
       </c>
-      <c r="AA7" s="16" t="n"/>
-      <c r="AB7" s="16" t="n"/>
-      <c r="AC7" s="16" t="n"/>
-      <c r="AD7" s="16" t="n"/>
+      <c r="AA7" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AB7" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AC7" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AD7" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
       <c r="AE7" s="7">
         <f>IF(B7="","",IF(AND(AA7="合格",AB7="合格",AC7="合格",AD7="合格"),"有效","无效"))</f>
         <v/>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="72" customHeight="1">
       <c r="A8" s="7">
         <f>IF(B8="","",TEXT(B8,"yyyymmdd")&amp;"-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="n"/>
-      <c r="G8" s="9" t="n"/>
-      <c r="H8" s="9" t="n"/>
-      <c r="I8" s="9" t="n"/>
-      <c r="J8" s="10" t="n"/>
-      <c r="K8" s="9" t="n"/>
-      <c r="L8" s="9" t="n"/>
-      <c r="M8" s="9" t="n"/>
-      <c r="N8" s="10" t="n"/>
-      <c r="O8" s="9" t="n"/>
-      <c r="P8" s="10" t="n"/>
-      <c r="Q8" s="10" t="n"/>
-      <c r="R8" s="9" t="n"/>
-      <c r="S8" s="10" t="n"/>
-      <c r="T8" s="10" t="n"/>
-      <c r="U8" s="11" t="n"/>
-      <c r="V8" s="11" t="n"/>
-      <c r="W8" s="12">
+      <c r="B8" s="25" t="n">
+        <v>45842</v>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>长电科技 600584.SH</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>半导体/封测</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>同步板块</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>箱体下沿</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>33.20-33.30</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>前两日33.23低点形成短线下沿，今日收33.23正好回到下沿。</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>接近</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>横盘震荡</t>
+        </is>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>收33.23跌0.89%，最低33.10，成交量20.30万手；半导体跌0.93%，上证涨0.32%。</t>
+        </is>
+      </c>
+      <c r="O8" s="10" t="inlineStr">
+        <is>
+          <t>震荡整理</t>
+        </is>
+      </c>
+      <c r="P8" s="10" t="inlineStr">
+        <is>
+          <t>价格回到下沿附近但没有放量大跌，仍可能是箱体震荡；不过大盘上涨时个股不涨，主动性偏弱。</t>
+        </is>
+      </c>
+      <c r="Q8" s="10" t="inlineStr">
+        <is>
+          <t>如果下一日跌破33.00，震荡整理会转向突破失败或转弱。</t>
+        </is>
+      </c>
+      <c r="R8" s="10" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>位置接近支撑但没有明确反包或放量，结论只能低强度。</t>
+        </is>
+      </c>
+      <c r="T8" s="10" t="inlineStr">
+        <is>
+          <t>后续只看是否跌破33.00。</t>
+        </is>
+      </c>
+      <c r="U8" s="11" t="inlineStr">
+        <is>
+          <t>弱于大盘的含义、箱体下沿有效性</t>
+        </is>
+      </c>
+      <c r="V8" s="11" t="inlineStr">
+        <is>
+          <t>这里更适合观察，不适合急着下强判断。</t>
+        </is>
+      </c>
+      <c r="W8" s="26">
         <f>IF(B8="","",B8+3)</f>
         <v/>
       </c>
-      <c r="X8" s="12">
+      <c r="X8" s="26">
         <f>IF(B8="","",B8+5)</f>
         <v/>
       </c>
-      <c r="Y8" s="12">
+      <c r="Y8" s="26">
         <f>IF(B8="","",B8+10)</f>
         <v/>
       </c>
-      <c r="Z8" s="13">
+      <c r="Z8" s="27">
         <f>IF(B8="","",(--(B8&lt;&gt;"")+--(C8&lt;&gt;"")+--(D8&lt;&gt;"")+--(E8&lt;&gt;"")+--(F8&lt;&gt;"")+--(G8&lt;&gt;"")+--(H8&lt;&gt;"")+--(I8&lt;&gt;"")+--(J8&lt;&gt;"")+--(K8&lt;&gt;"")+--(L8&lt;&gt;"")+--(M8&lt;&gt;"")+--(N8&lt;&gt;"")+--(O8&lt;&gt;"")+--(P8&lt;&gt;"")+--(Q8&lt;&gt;"")+--(R8&lt;&gt;"")+--(S8&lt;&gt;"")+--(T8&lt;&gt;""))/19)</f>
         <v/>
       </c>
-      <c r="AA8" s="16" t="n"/>
-      <c r="AB8" s="16" t="n"/>
-      <c r="AC8" s="16" t="n"/>
-      <c r="AD8" s="16" t="n"/>
+      <c r="AA8" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AB8" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AC8" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AD8" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
       <c r="AE8" s="7">
         <f>IF(B8="","",IF(AND(AA8="合格",AB8="合格",AC8="合格",AD8="合格"),"有效","无效"))</f>
         <v/>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="72" customHeight="1">
       <c r="A9" s="7">
         <f>IF(B9="","",TEXT(B9,"yyyymmdd")&amp;"-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
-      <c r="G9" s="9" t="n"/>
-      <c r="H9" s="9" t="n"/>
-      <c r="I9" s="9" t="n"/>
-      <c r="J9" s="10" t="n"/>
-      <c r="K9" s="9" t="n"/>
-      <c r="L9" s="9" t="n"/>
-      <c r="M9" s="9" t="n"/>
-      <c r="N9" s="10" t="n"/>
-      <c r="O9" s="9" t="n"/>
-      <c r="P9" s="10" t="n"/>
-      <c r="Q9" s="10" t="n"/>
-      <c r="R9" s="9" t="n"/>
-      <c r="S9" s="10" t="n"/>
-      <c r="T9" s="10" t="n"/>
-      <c r="U9" s="11" t="n"/>
-      <c r="V9" s="11" t="n"/>
-      <c r="W9" s="12">
+      <c r="B9" s="25" t="n">
+        <v>45845</v>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>长电科技 600584.SH</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>半导体/封测</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>弱于板块</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>大阳线低点</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>33.00</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>6月27日放量阳线低点33.00，此前也作为回踩观察位。</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>跌破</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>清晰</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>跌破关键位</t>
+        </is>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>收32.95跌0.84%，最低32.88，跌破33.00，成交量15.46万手；半导体跌0.13%，上证微涨0.02%。</t>
+        </is>
+      </c>
+      <c r="O9" s="10" t="inlineStr">
+        <is>
+          <t>退潮转弱</t>
+        </is>
+      </c>
+      <c r="P9" s="10" t="inlineStr">
+        <is>
+          <t>在板块和大盘没有明显下跌时，个股跌破33.00关键位，说明前期突破结构被破坏。</t>
+        </is>
+      </c>
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
+          <t>如果下一两日快速收回33.30上方，今天可能是假跌破。</t>
+        </is>
+      </c>
+      <c r="R9" s="10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>关键位清晰，且相对板块转弱，但缩量下跌意味着杀跌并不充分。</t>
+        </is>
+      </c>
+      <c r="T9" s="10" t="inlineStr">
+        <is>
+          <t>后续只看是否收回33.30。</t>
+        </is>
+      </c>
+      <c r="U9" s="11" t="inlineStr">
+        <is>
+          <t>跌破关键位、假跌破识别、相对弱势</t>
+        </is>
+      </c>
+      <c r="V9" s="11" t="inlineStr">
+        <is>
+          <t>这一天是从“支撑观察”转为“结构受损观察”的分界。</t>
+        </is>
+      </c>
+      <c r="W9" s="26">
         <f>IF(B9="","",B9+3)</f>
         <v/>
       </c>
-      <c r="X9" s="12">
+      <c r="X9" s="26">
         <f>IF(B9="","",B9+5)</f>
         <v/>
       </c>
-      <c r="Y9" s="12">
+      <c r="Y9" s="26">
         <f>IF(B9="","",B9+10)</f>
         <v/>
       </c>
-      <c r="Z9" s="13">
+      <c r="Z9" s="27">
         <f>IF(B9="","",(--(B9&lt;&gt;"")+--(C9&lt;&gt;"")+--(D9&lt;&gt;"")+--(E9&lt;&gt;"")+--(F9&lt;&gt;"")+--(G9&lt;&gt;"")+--(H9&lt;&gt;"")+--(I9&lt;&gt;"")+--(J9&lt;&gt;"")+--(K9&lt;&gt;"")+--(L9&lt;&gt;"")+--(M9&lt;&gt;"")+--(N9&lt;&gt;"")+--(O9&lt;&gt;"")+--(P9&lt;&gt;"")+--(Q9&lt;&gt;"")+--(R9&lt;&gt;"")+--(S9&lt;&gt;"")+--(T9&lt;&gt;""))/19)</f>
         <v/>
       </c>
-      <c r="AA9" s="16" t="n"/>
-      <c r="AB9" s="16" t="n"/>
-      <c r="AC9" s="16" t="n"/>
-      <c r="AD9" s="16" t="n"/>
+      <c r="AA9" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AB9" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AC9" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AD9" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
       <c r="AE9" s="7">
         <f>IF(B9="","",IF(AND(AA9="合格",AB9="合格",AC9="合格",AD9="合格"),"有效","无效"))</f>
         <v/>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="72" customHeight="1">
       <c r="A10" s="7">
         <f>IF(B10="","",TEXT(B10,"yyyymmdd")&amp;"-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="9" t="n"/>
-      <c r="G10" s="9" t="n"/>
-      <c r="H10" s="9" t="n"/>
-      <c r="I10" s="9" t="n"/>
-      <c r="J10" s="10" t="n"/>
-      <c r="K10" s="9" t="n"/>
-      <c r="L10" s="9" t="n"/>
-      <c r="M10" s="9" t="n"/>
-      <c r="N10" s="10" t="n"/>
-      <c r="O10" s="9" t="n"/>
-      <c r="P10" s="10" t="n"/>
-      <c r="Q10" s="10" t="n"/>
-      <c r="R10" s="9" t="n"/>
-      <c r="S10" s="10" t="n"/>
-      <c r="T10" s="10" t="n"/>
-      <c r="U10" s="11" t="n"/>
-      <c r="V10" s="11" t="n"/>
-      <c r="W10" s="12">
+      <c r="B10" s="25" t="n">
+        <v>45846</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>长电科技 600584.SH</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>半导体/封测</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>轮动强势</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>同步板块</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>前高</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>33.30-33.40</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>跌破33.00后快速收回，33.30-33.40重新变成修复确认位。</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>跌破后收回</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>低位反弹</t>
+        </is>
+      </c>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>收33.55涨1.82%，最低33.01后收回33.30-33.40，成交量24.45万手；半导体涨1.50%，上证涨0.70%。</t>
+        </is>
+      </c>
+      <c r="O10" s="10" t="inlineStr">
+        <is>
+          <t>弱反弹</t>
+        </is>
+      </c>
+      <c r="P10" s="10" t="inlineStr">
+        <is>
+          <t>价格收回关键位说明7月7日跌破没有继续恶化，但反弹主要伴随大盘和板块转强，暂不能认定重新启动。</t>
+        </is>
+      </c>
+      <c r="Q10" s="10" t="inlineStr">
+        <is>
+          <t>如果后续不能继续站稳33.40并上攻33.80，反弹仍可能只是箱体震荡的一部分。</t>
+        </is>
+      </c>
+      <c r="R10" s="10" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>修复动作明确，但外部环境同步转强，个股独立性不足。</t>
+        </is>
+      </c>
+      <c r="T10" s="10" t="inlineStr">
+        <is>
+          <t>后续只看是否连续收在33.40上方。</t>
+        </is>
+      </c>
+      <c r="U10" s="11" t="inlineStr">
+        <is>
+          <t>跌破后收回、修复与重新启动区别</t>
+        </is>
+      </c>
+      <c r="V10" s="11" t="inlineStr">
+        <is>
+          <t>不要因为一天大涨就把它重新判成强趋势。</t>
+        </is>
+      </c>
+      <c r="W10" s="26">
         <f>IF(B10="","",B10+3)</f>
         <v/>
       </c>
-      <c r="X10" s="12">
+      <c r="X10" s="26">
         <f>IF(B10="","",B10+5)</f>
         <v/>
       </c>
-      <c r="Y10" s="12">
+      <c r="Y10" s="26">
         <f>IF(B10="","",B10+10)</f>
         <v/>
       </c>
-      <c r="Z10" s="13">
+      <c r="Z10" s="27">
         <f>IF(B10="","",(--(B10&lt;&gt;"")+--(C10&lt;&gt;"")+--(D10&lt;&gt;"")+--(E10&lt;&gt;"")+--(F10&lt;&gt;"")+--(G10&lt;&gt;"")+--(H10&lt;&gt;"")+--(I10&lt;&gt;"")+--(J10&lt;&gt;"")+--(K10&lt;&gt;"")+--(L10&lt;&gt;"")+--(M10&lt;&gt;"")+--(N10&lt;&gt;"")+--(O10&lt;&gt;"")+--(P10&lt;&gt;"")+--(Q10&lt;&gt;"")+--(R10&lt;&gt;"")+--(S10&lt;&gt;"")+--(T10&lt;&gt;""))/19)</f>
         <v/>
       </c>
-      <c r="AA10" s="16" t="n"/>
-      <c r="AB10" s="16" t="n"/>
-      <c r="AC10" s="16" t="n"/>
-      <c r="AD10" s="16" t="n"/>
+      <c r="AA10" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AB10" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AC10" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AD10" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
       <c r="AE10" s="7">
         <f>IF(B10="","",IF(AND(AA10="合格",AB10="合格",AC10="合格",AD10="合格"),"有效","无效"))</f>
         <v/>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="72" customHeight="1">
       <c r="A11" s="7">
         <f>IF(B11="","",TEXT(B11,"yyyymmdd")&amp;"-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="9" t="n"/>
-      <c r="H11" s="9" t="n"/>
-      <c r="I11" s="9" t="n"/>
-      <c r="J11" s="10" t="n"/>
-      <c r="K11" s="9" t="n"/>
-      <c r="L11" s="9" t="n"/>
-      <c r="M11" s="9" t="n"/>
-      <c r="N11" s="10" t="n"/>
-      <c r="O11" s="9" t="n"/>
-      <c r="P11" s="10" t="n"/>
-      <c r="Q11" s="10" t="n"/>
-      <c r="R11" s="9" t="n"/>
-      <c r="S11" s="10" t="n"/>
-      <c r="T11" s="10" t="n"/>
-      <c r="U11" s="11" t="n"/>
-      <c r="V11" s="11" t="n"/>
-      <c r="W11" s="12">
+      <c r="B11" s="25" t="n">
+        <v>45847</v>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>长电科技 600584.SH</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>半导体/封测</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>同步板块</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>箱体下沿</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>33.00-33.20</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>近几日低点集中在33.00-33.20，当前仍围绕这个区域反复。</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>接近</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>横盘震荡</t>
+        </is>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>收33.18跌1.10%，最低33.10，成交量19.43万手；半导体跌1.12%，上证跌0.13%。</t>
+        </is>
+      </c>
+      <c r="O11" s="10" t="inlineStr">
+        <is>
+          <t>震荡整理</t>
+        </is>
+      </c>
+      <c r="P11" s="10" t="inlineStr">
+        <is>
+          <t>价格没有继续向上确认33.40，也没有有效跌破33.00，说明短线仍在33.00-34.08之间震荡。</t>
+        </is>
+      </c>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
+          <t>如果后续放量跌破33.00，震荡整理会转为转弱；若放量站上34.08，才说明重新转强。</t>
+        </is>
+      </c>
+      <c r="R11" s="10" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>上下边界都有，但当前价格在中低位，方向信息不足。</t>
+        </is>
+      </c>
+      <c r="T11" s="10" t="inlineStr">
+        <is>
+          <t>后续只看33.00是否被有效跌破。</t>
+        </is>
+      </c>
+      <c r="U11" s="11" t="inlineStr">
+        <is>
+          <t>箱体边界、方向未明时降低判断强度</t>
+        </is>
+      </c>
+      <c r="V11" s="11" t="inlineStr">
+        <is>
+          <t>这是一个“看不清就承认看不清”的样本。</t>
+        </is>
+      </c>
+      <c r="W11" s="26">
         <f>IF(B11="","",B11+3)</f>
         <v/>
       </c>
-      <c r="X11" s="12">
+      <c r="X11" s="26">
         <f>IF(B11="","",B11+5)</f>
         <v/>
       </c>
-      <c r="Y11" s="12">
+      <c r="Y11" s="26">
         <f>IF(B11="","",B11+10)</f>
         <v/>
       </c>
-      <c r="Z11" s="13">
+      <c r="Z11" s="27">
         <f>IF(B11="","",(--(B11&lt;&gt;"")+--(C11&lt;&gt;"")+--(D11&lt;&gt;"")+--(E11&lt;&gt;"")+--(F11&lt;&gt;"")+--(G11&lt;&gt;"")+--(H11&lt;&gt;"")+--(I11&lt;&gt;"")+--(J11&lt;&gt;"")+--(K11&lt;&gt;"")+--(L11&lt;&gt;"")+--(M11&lt;&gt;"")+--(N11&lt;&gt;"")+--(O11&lt;&gt;"")+--(P11&lt;&gt;"")+--(Q11&lt;&gt;"")+--(R11&lt;&gt;"")+--(S11&lt;&gt;"")+--(T11&lt;&gt;""))/19)</f>
         <v/>
       </c>
-      <c r="AA11" s="16" t="n"/>
-      <c r="AB11" s="16" t="n"/>
-      <c r="AC11" s="16" t="n"/>
-      <c r="AD11" s="16" t="n"/>
+      <c r="AA11" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AB11" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AC11" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="AD11" s="18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
       <c r="AE11" s="7">
         <f>IF(B11="","",IF(AND(AA11="合格",AB11="合格",AC11="合格",AD11="合格"),"有效","无效"))</f>
         <v/>
@@ -27438,229 +28464,817 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="72" customHeight="1">
       <c r="A2" s="15">
         <f>IF(B2="","","V-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="17" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16" t="n"/>
-      <c r="H2" s="16" t="n"/>
-      <c r="I2" s="16" t="n"/>
-      <c r="J2" s="18" t="n"/>
-      <c r="K2" s="16" t="n"/>
-      <c r="L2" s="17" t="n"/>
-      <c r="M2" s="18" t="n"/>
-      <c r="N2" s="16" t="n"/>
-      <c r="O2" s="16" t="n"/>
-      <c r="P2" s="16" t="n"/>
-      <c r="Q2" s="16" t="n"/>
-      <c r="R2" s="16" t="n"/>
-      <c r="S2" s="16" t="n"/>
-      <c r="T2" s="18" t="n"/>
-      <c r="U2" s="18" t="n"/>
-      <c r="V2" s="7">
+      <c r="B2" s="18" t="inlineStr">
+        <is>
+          <t>20250626-001</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="n">
+        <v>45834</v>
+      </c>
+      <c r="D2" s="18" t="inlineStr">
+        <is>
+          <t>长电科技 600584.SH</t>
+        </is>
+      </c>
+      <c r="E2" s="18" t="inlineStr">
+        <is>
+          <t>前高</t>
+        </is>
+      </c>
+      <c r="F2" s="18" t="inlineStr">
+        <is>
+          <t>33.30-33.40</t>
+        </is>
+      </c>
+      <c r="G2" s="18" t="inlineStr">
+        <is>
+          <t>冲高回落</t>
+        </is>
+      </c>
+      <c r="H2" s="18" t="inlineStr">
+        <is>
+          <t>高位分歧</t>
+        </is>
+      </c>
+      <c r="I2" s="18" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J2" s="18" t="inlineStr">
+        <is>
+          <t>后续只看是否收盘重新站上33.40。</t>
+        </is>
+      </c>
+      <c r="K2" s="18" t="inlineStr">
+        <is>
+          <t>3日</t>
+        </is>
+      </c>
+      <c r="L2" s="28" t="n">
+        <v>45839</v>
+      </c>
+      <c r="M2" s="18" t="inlineStr">
+        <is>
+          <t>收33.97，盘中34.38，已重新站上33.40但没有收过34.08。</t>
+        </is>
+      </c>
+      <c r="N2" s="18" t="inlineStr">
+        <is>
+          <t>向上延续</t>
+        </is>
+      </c>
+      <c r="O2" s="18" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="P2" s="18" t="inlineStr">
+        <is>
+          <t>出现</t>
+        </is>
+      </c>
+      <c r="Q2" s="18" t="inlineStr">
+        <is>
+          <t>削弱</t>
+        </is>
+      </c>
+      <c r="R2" s="18" t="inlineStr">
+        <is>
+          <t>过程合理</t>
+        </is>
+      </c>
+      <c r="S2" s="18" t="inlineStr">
+        <is>
+          <t>概率结果失败</t>
+        </is>
+      </c>
+      <c r="T2" s="18" t="inlineStr">
+        <is>
+          <t>前高分歧不等于失败，必须等收盘确认。</t>
+        </is>
+      </c>
+      <c r="U2" s="18" t="inlineStr">
+        <is>
+          <t>收盘确认与盘中突破区别</t>
+        </is>
+      </c>
+      <c r="V2" s="29">
         <f>IF(L2="","",IF(TODAY()&gt;=L2,"到期","未到期"))</f>
         <v/>
       </c>
-      <c r="W2" s="16" t="n"/>
-      <c r="X2" s="16" t="n"/>
-    </row>
-    <row r="3">
+      <c r="W2" s="18" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="X2" s="18" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="72" customHeight="1">
       <c r="A3" s="15">
         <f>IF(B3="","","V-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="17" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="16" t="n"/>
-      <c r="H3" s="16" t="n"/>
-      <c r="I3" s="16" t="n"/>
-      <c r="J3" s="18" t="n"/>
-      <c r="K3" s="16" t="n"/>
-      <c r="L3" s="17" t="n"/>
-      <c r="M3" s="18" t="n"/>
-      <c r="N3" s="16" t="n"/>
-      <c r="O3" s="16" t="n"/>
-      <c r="P3" s="16" t="n"/>
-      <c r="Q3" s="16" t="n"/>
-      <c r="R3" s="16" t="n"/>
-      <c r="S3" s="16" t="n"/>
-      <c r="T3" s="18" t="n"/>
-      <c r="U3" s="18" t="n"/>
-      <c r="V3" s="7">
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>20250627-002</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="n">
+        <v>45835</v>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>长电科技 600584.SH</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>前高</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>33.40</t>
+        </is>
+      </c>
+      <c r="G3" s="18" t="inlineStr">
+        <is>
+          <t>放量突破</t>
+        </is>
+      </c>
+      <c r="H3" s="18" t="inlineStr">
+        <is>
+          <t>真突破/启动尝试</t>
+        </is>
+      </c>
+      <c r="I3" s="18" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J3" s="18" t="inlineStr">
+        <is>
+          <t>后续只看是否守住33.30-33.40。</t>
+        </is>
+      </c>
+      <c r="K3" s="18" t="inlineStr">
+        <is>
+          <t>3日</t>
+        </is>
+      </c>
+      <c r="L3" s="28" t="n">
+        <v>45840</v>
+      </c>
+      <c r="M3" s="18" t="inlineStr">
+        <is>
+          <t>收33.31，基本回踩到33.30附近，未明显跌破但突破延续不足。</t>
+        </is>
+      </c>
+      <c r="N3" s="18" t="inlineStr">
+        <is>
+          <t>震荡消化</t>
+        </is>
+      </c>
+      <c r="O3" s="18" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="P3" s="18" t="inlineStr">
+        <is>
+          <t>部分出现</t>
+        </is>
+      </c>
+      <c r="Q3" s="18" t="inlineStr">
+        <is>
+          <t>削弱</t>
+        </is>
+      </c>
+      <c r="R3" s="18" t="inlineStr">
+        <is>
+          <t>过程合理</t>
+        </is>
+      </c>
+      <c r="S3" s="18" t="inlineStr">
+        <is>
+          <t>无明显错误</t>
+        </is>
+      </c>
+      <c r="T3" s="18" t="inlineStr">
+        <is>
+          <t>突破后如果不能继续放量，先按震荡消化处理。</t>
+        </is>
+      </c>
+      <c r="U3" s="18" t="inlineStr">
+        <is>
+          <t>突破后的回踩确认</t>
+        </is>
+      </c>
+      <c r="V3" s="29">
         <f>IF(L3="","",IF(TODAY()&gt;=L3,"到期","未到期"))</f>
         <v/>
       </c>
-      <c r="W3" s="16" t="n"/>
-      <c r="X3" s="16" t="n"/>
-    </row>
-    <row r="4">
+      <c r="W3" s="18" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="X3" s="18" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="72" customHeight="1">
       <c r="A4" s="15">
         <f>IF(B4="","","V-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="17" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="16" t="n"/>
-      <c r="H4" s="16" t="n"/>
-      <c r="I4" s="16" t="n"/>
-      <c r="J4" s="18" t="n"/>
-      <c r="K4" s="16" t="n"/>
-      <c r="L4" s="17" t="n"/>
-      <c r="M4" s="18" t="n"/>
-      <c r="N4" s="16" t="n"/>
-      <c r="O4" s="16" t="n"/>
-      <c r="P4" s="16" t="n"/>
-      <c r="Q4" s="16" t="n"/>
-      <c r="R4" s="16" t="n"/>
-      <c r="S4" s="16" t="n"/>
-      <c r="T4" s="18" t="n"/>
-      <c r="U4" s="18" t="n"/>
-      <c r="V4" s="7">
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>20250630-003</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="n">
+        <v>45838</v>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>长电科技 600584.SH</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>前高</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>34.08</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>横盘震荡</t>
+        </is>
+      </c>
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>震荡整理</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J4" s="18" t="inlineStr">
+        <is>
+          <t>后续只看是否收盘站上34.08。</t>
+        </is>
+      </c>
+      <c r="K4" s="18" t="inlineStr">
+        <is>
+          <t>3日</t>
+        </is>
+      </c>
+      <c r="L4" s="28" t="n">
+        <v>45841</v>
+      </c>
+      <c r="M4" s="18" t="inlineStr">
+        <is>
+          <t>收33.53，未站上34.08，仍在33.20-34.08之间。</t>
+        </is>
+      </c>
+      <c r="N4" s="18" t="inlineStr">
+        <is>
+          <t>震荡消化</t>
+        </is>
+      </c>
+      <c r="O4" s="18" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="P4" s="18" t="inlineStr">
+        <is>
+          <t>未出现</t>
+        </is>
+      </c>
+      <c r="Q4" s="18" t="inlineStr">
+        <is>
+          <t>强化</t>
+        </is>
+      </c>
+      <c r="R4" s="18" t="inlineStr">
+        <is>
+          <t>过程合理</t>
+        </is>
+      </c>
+      <c r="S4" s="18" t="inlineStr">
+        <is>
+          <t>无明显错误</t>
+        </is>
+      </c>
+      <c r="T4" s="18" t="inlineStr">
+        <is>
+          <t>低强度震荡判断可以接受，不需要硬预测方向。</t>
+        </is>
+      </c>
+      <c r="U4" s="18" t="inlineStr">
+        <is>
+          <t>箱体上沿确认</t>
+        </is>
+      </c>
+      <c r="V4" s="29">
         <f>IF(L4="","",IF(TODAY()&gt;=L4,"到期","未到期"))</f>
         <v/>
       </c>
-      <c r="W4" s="16" t="n"/>
-      <c r="X4" s="16" t="n"/>
-    </row>
-    <row r="5">
+      <c r="W4" s="18" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="X4" s="18" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="72" customHeight="1">
       <c r="A5" s="15">
         <f>IF(B5="","","V-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="16" t="n"/>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="16" t="n"/>
-      <c r="H5" s="16" t="n"/>
-      <c r="I5" s="16" t="n"/>
-      <c r="J5" s="18" t="n"/>
-      <c r="K5" s="16" t="n"/>
-      <c r="L5" s="17" t="n"/>
-      <c r="M5" s="18" t="n"/>
-      <c r="N5" s="16" t="n"/>
-      <c r="O5" s="16" t="n"/>
-      <c r="P5" s="16" t="n"/>
-      <c r="Q5" s="16" t="n"/>
-      <c r="R5" s="16" t="n"/>
-      <c r="S5" s="16" t="n"/>
-      <c r="T5" s="18" t="n"/>
-      <c r="U5" s="18" t="n"/>
-      <c r="V5" s="7">
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>20250701-004</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="n">
+        <v>45839</v>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>长电科技 600584.SH</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>前高</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>34.08</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>高位放量震荡</t>
+        </is>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>高位分歧</t>
+        </is>
+      </c>
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="inlineStr">
+        <is>
+          <t>后续只看是否收盘站上34.08。</t>
+        </is>
+      </c>
+      <c r="K5" s="18" t="inlineStr">
+        <is>
+          <t>3日</t>
+        </is>
+      </c>
+      <c r="L5" s="28" t="n">
+        <v>45842</v>
+      </c>
+      <c r="M5" s="18" t="inlineStr">
+        <is>
+          <t>收33.23，没有站回34.08，反而回到短线下沿。</t>
+        </is>
+      </c>
+      <c r="N5" s="18" t="inlineStr">
+        <is>
+          <t>冲高回落</t>
+        </is>
+      </c>
+      <c r="O5" s="18" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="P5" s="18" t="inlineStr">
+        <is>
+          <t>未出现</t>
+        </is>
+      </c>
+      <c r="Q5" s="18" t="inlineStr">
+        <is>
+          <t>强化</t>
+        </is>
+      </c>
+      <c r="R5" s="18" t="inlineStr">
+        <is>
+          <t>过程合理</t>
+        </is>
+      </c>
+      <c r="S5" s="18" t="inlineStr">
+        <is>
+          <t>无明显错误</t>
+        </is>
+      </c>
+      <c r="T5" s="18" t="inlineStr">
+        <is>
+          <t>盘中新高不如收盘站稳重要。</t>
+        </is>
+      </c>
+      <c r="U5" s="18" t="inlineStr">
+        <is>
+          <t>假突破与分歧换手区分</t>
+        </is>
+      </c>
+      <c r="V5" s="29">
         <f>IF(L5="","",IF(TODAY()&gt;=L5,"到期","未到期"))</f>
         <v/>
       </c>
-      <c r="W5" s="16" t="n"/>
-      <c r="X5" s="16" t="n"/>
-    </row>
-    <row r="6">
+      <c r="W5" s="18" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="X5" s="18" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="72" customHeight="1">
       <c r="A6" s="15">
         <f>IF(B6="","","V-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="17" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
-      <c r="G6" s="16" t="n"/>
-      <c r="H6" s="16" t="n"/>
-      <c r="I6" s="16" t="n"/>
-      <c r="J6" s="18" t="n"/>
-      <c r="K6" s="16" t="n"/>
-      <c r="L6" s="17" t="n"/>
-      <c r="M6" s="18" t="n"/>
-      <c r="N6" s="16" t="n"/>
-      <c r="O6" s="16" t="n"/>
-      <c r="P6" s="16" t="n"/>
-      <c r="Q6" s="16" t="n"/>
-      <c r="R6" s="16" t="n"/>
-      <c r="S6" s="16" t="n"/>
-      <c r="T6" s="18" t="n"/>
-      <c r="U6" s="18" t="n"/>
-      <c r="V6" s="7">
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>20250702-005</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="n">
+        <v>45840</v>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>长电科技 600584.SH</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>大阳线低点</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>33.00-33.30</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>缩量回调</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>健康回调</t>
+        </is>
+      </c>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="inlineStr">
+        <is>
+          <t>后续只看是否跌破33.00。</t>
+        </is>
+      </c>
+      <c r="K6" s="18" t="inlineStr">
+        <is>
+          <t>3日</t>
+        </is>
+      </c>
+      <c r="L6" s="28" t="n">
+        <v>45845</v>
+      </c>
+      <c r="M6" s="18" t="inlineStr">
+        <is>
+          <t>收32.95，跌破33.00，但成交量继续缩小。</t>
+        </is>
+      </c>
+      <c r="N6" s="18" t="inlineStr">
+        <is>
+          <t>跌破支撑</t>
+        </is>
+      </c>
+      <c r="O6" s="18" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="P6" s="18" t="inlineStr">
+        <is>
+          <t>出现</t>
+        </is>
+      </c>
+      <c r="Q6" s="18" t="inlineStr">
+        <is>
+          <t>证伪</t>
+        </is>
+      </c>
+      <c r="R6" s="18" t="inlineStr">
+        <is>
+          <t>概率失败</t>
+        </is>
+      </c>
+      <c r="S6" s="18" t="inlineStr">
+        <is>
+          <t>概率结果失败</t>
+        </is>
+      </c>
+      <c r="T6" s="18" t="inlineStr">
+        <is>
+          <t>健康回调假设被证伪时要切换解释，不要补理由。</t>
+        </is>
+      </c>
+      <c r="U6" s="18" t="inlineStr">
+        <is>
+          <t>支撑区间有效性</t>
+        </is>
+      </c>
+      <c r="V6" s="29">
         <f>IF(L6="","",IF(TODAY()&gt;=L6,"到期","未到期"))</f>
         <v/>
       </c>
-      <c r="W6" s="16" t="n"/>
-      <c r="X6" s="16" t="n"/>
-    </row>
-    <row r="7">
+      <c r="W6" s="18" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="X6" s="18" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="72" customHeight="1">
       <c r="A7" s="15">
         <f>IF(B7="","","V-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="17" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
-      <c r="G7" s="16" t="n"/>
-      <c r="H7" s="16" t="n"/>
-      <c r="I7" s="16" t="n"/>
-      <c r="J7" s="18" t="n"/>
-      <c r="K7" s="16" t="n"/>
-      <c r="L7" s="17" t="n"/>
-      <c r="M7" s="18" t="n"/>
-      <c r="N7" s="16" t="n"/>
-      <c r="O7" s="16" t="n"/>
-      <c r="P7" s="16" t="n"/>
-      <c r="Q7" s="16" t="n"/>
-      <c r="R7" s="16" t="n"/>
-      <c r="S7" s="16" t="n"/>
-      <c r="T7" s="18" t="n"/>
-      <c r="U7" s="18" t="n"/>
-      <c r="V7" s="7">
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>20250703-006</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="n">
+        <v>45841</v>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>长电科技 600584.SH</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>箱体下沿</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>33.20-33.30</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>回踩支撑不破</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>震荡整理</t>
+        </is>
+      </c>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="inlineStr">
+        <is>
+          <t>后续只看是否跌破33.20。</t>
+        </is>
+      </c>
+      <c r="K7" s="18" t="inlineStr">
+        <is>
+          <t>3日</t>
+        </is>
+      </c>
+      <c r="L7" s="28" t="n">
+        <v>45846</v>
+      </c>
+      <c r="M7" s="18" t="inlineStr">
+        <is>
+          <t>收33.55，未跌破33.20，并重新收回33.40上方。</t>
+        </is>
+      </c>
+      <c r="N7" s="18" t="inlineStr">
+        <is>
+          <t>修复转强</t>
+        </is>
+      </c>
+      <c r="O7" s="18" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="P7" s="18" t="inlineStr">
+        <is>
+          <t>未出现</t>
+        </is>
+      </c>
+      <c r="Q7" s="18" t="inlineStr">
+        <is>
+          <t>强化</t>
+        </is>
+      </c>
+      <c r="R7" s="18" t="inlineStr">
+        <is>
+          <t>过程合理</t>
+        </is>
+      </c>
+      <c r="S7" s="18" t="inlineStr">
+        <is>
+          <t>无明显错误</t>
+        </is>
+      </c>
+      <c r="T7" s="18" t="inlineStr">
+        <is>
+          <t>两个低点形成的临时箱体可以观察，但强度要低。</t>
+        </is>
+      </c>
+      <c r="U7" s="18" t="inlineStr">
+        <is>
+          <t>临时箱体识别</t>
+        </is>
+      </c>
+      <c r="V7" s="29">
         <f>IF(L7="","",IF(TODAY()&gt;=L7,"到期","未到期"))</f>
         <v/>
       </c>
-      <c r="W7" s="16" t="n"/>
-      <c r="X7" s="16" t="n"/>
-    </row>
-    <row r="8">
+      <c r="W7" s="18" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="X7" s="18" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="72" customHeight="1">
       <c r="A8" s="15">
         <f>IF(B8="","","V-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="17" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n"/>
-      <c r="G8" s="16" t="n"/>
-      <c r="H8" s="16" t="n"/>
-      <c r="I8" s="16" t="n"/>
-      <c r="J8" s="18" t="n"/>
-      <c r="K8" s="16" t="n"/>
-      <c r="L8" s="17" t="n"/>
-      <c r="M8" s="18" t="n"/>
-      <c r="N8" s="16" t="n"/>
-      <c r="O8" s="16" t="n"/>
-      <c r="P8" s="16" t="n"/>
-      <c r="Q8" s="16" t="n"/>
-      <c r="R8" s="16" t="n"/>
-      <c r="S8" s="16" t="n"/>
-      <c r="T8" s="18" t="n"/>
-      <c r="U8" s="18" t="n"/>
-      <c r="V8" s="7">
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>20250704-007</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>45842</v>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>长电科技 600584.SH</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>箱体下沿</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>33.20-33.30</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>横盘震荡</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
+          <t>震荡整理</t>
+        </is>
+      </c>
+      <c r="I8" s="18" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J8" s="18" t="inlineStr">
+        <is>
+          <t>后续只看是否跌破33.00。</t>
+        </is>
+      </c>
+      <c r="K8" s="18" t="inlineStr">
+        <is>
+          <t>3日</t>
+        </is>
+      </c>
+      <c r="L8" s="28" t="n">
+        <v>45847</v>
+      </c>
+      <c r="M8" s="18" t="inlineStr">
+        <is>
+          <t>收33.18，未跌破33.00，但也没有向上确认。</t>
+        </is>
+      </c>
+      <c r="N8" s="18" t="inlineStr">
+        <is>
+          <t>震荡消化</t>
+        </is>
+      </c>
+      <c r="O8" s="18" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="P8" s="18" t="inlineStr">
+        <is>
+          <t>未出现</t>
+        </is>
+      </c>
+      <c r="Q8" s="18" t="inlineStr">
+        <is>
+          <t>仍不确定</t>
+        </is>
+      </c>
+      <c r="R8" s="18" t="inlineStr">
+        <is>
+          <t>过程合理</t>
+        </is>
+      </c>
+      <c r="S8" s="18" t="inlineStr">
+        <is>
+          <t>无明显错误</t>
+        </is>
+      </c>
+      <c r="T8" s="18" t="inlineStr">
+        <is>
+          <t>低强度判断允许保持不确定，不必强行改成看多或看空。</t>
+        </is>
+      </c>
+      <c r="U8" s="18" t="inlineStr">
+        <is>
+          <t>方向不明时的观察纪律</t>
+        </is>
+      </c>
+      <c r="V8" s="29">
         <f>IF(L8="","",IF(TODAY()&gt;=L8,"到期","未到期"))</f>
         <v/>
       </c>
-      <c r="W8" s="16" t="n"/>
-      <c r="X8" s="16" t="n"/>
+      <c r="W8" s="18" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="X8" s="18" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="15">
@@ -43472,6 +45086,8 @@
           <t>训练看板</t>
         </is>
       </c>
+      <c r="B1" s="22" t="n"/>
+      <c r="C1" s="23" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -43792,7 +45408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -44500,7 +46116,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stock_review_template.xlsx
+++ b/stock_review_template.xlsx
@@ -794,32 +794,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="24" t="inlineStr">
-        <is>
-          <t>长电科技10日样本数据说明</t>
-        </is>
-      </c>
+      <c r="A28" s="24" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="inlineStr">
-        <is>
-          <t>样本写入位置：每日观察!2:11，事后验证!2:8。</t>
-        </is>
-      </c>
+      <c r="A29" s="24" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="24" t="inlineStr">
-        <is>
-          <t>个股数据：搜狐历史行情接口 cn_600584；大盘数据：搜狐历史行情接口 zs_000001；板块数据：东方财富半导体板块 BK1036。</t>
-        </is>
-      </c>
+      <c r="A30" s="24" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="inlineStr">
-        <is>
-          <t>样本日期范围：2025-06-26 至 2025-07-09，共10个交易日；因当前接口未返回2026年数据，本样本按可取得的最近完整窗口填写。</t>
-        </is>
-      </c>
+      <c r="A31" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1028,114 +1012,32 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="72" customHeight="1">
+    <row r="2">
       <c r="A2" s="7">
         <f>IF(B2="","",TEXT(B2,"yyyymmdd")&amp;"-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B2" s="25" t="n">
-        <v>45834</v>
-      </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>长电科技 600584.SH</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>半导体/封测</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>震荡偏强</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>震荡</t>
-        </is>
-      </c>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
-          <t>强于板块</t>
-        </is>
-      </c>
-      <c r="H2" s="10" t="inlineStr">
-        <is>
-          <t>前高</t>
-        </is>
-      </c>
-      <c r="I2" s="10" t="inlineStr">
-        <is>
-          <t>33.30-33.40</t>
-        </is>
-      </c>
-      <c r="J2" s="10" t="inlineStr">
-        <is>
-          <t>6月25日前高33.30，今日最高33.40但收32.96，说明上方第一次出现分歧。</t>
-        </is>
-      </c>
-      <c r="K2" s="10" t="inlineStr">
-        <is>
-          <t>接近</t>
-        </is>
-      </c>
-      <c r="L2" s="10" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="M2" s="10" t="inlineStr">
-        <is>
-          <t>冲高回落</t>
-        </is>
-      </c>
-      <c r="N2" s="10" t="inlineStr">
-        <is>
-          <t>收32.96跌0.78%，盘中最高33.40触及前高区，成交量26.21万手；半导体跌1.17%，上证跌0.22%。</t>
-        </is>
-      </c>
-      <c r="O2" s="10" t="inlineStr">
-        <is>
-          <t>高位分歧</t>
-        </is>
-      </c>
-      <c r="P2" s="10" t="inlineStr">
-        <is>
-          <t>价格接近前高后没有收住，说明33.30-33.40附近存在短线抛压；但个股跌幅小于半导体，不能直接判定转弱。</t>
-        </is>
-      </c>
-      <c r="Q2" s="10" t="inlineStr">
-        <is>
-          <t>如果随后1-3日重新放量站上33.40，今天更像突破前正常分歧，而不是上攻失败。</t>
-        </is>
-      </c>
-      <c r="R2" s="10" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="S2" s="10" t="inlineStr">
-        <is>
-          <t>有明确前高和冲高回落事实，但板块当天较弱，单日不能确认失败。</t>
-        </is>
-      </c>
-      <c r="T2" s="10" t="inlineStr">
-        <is>
-          <t>后续只看是否收盘重新站上33.40。</t>
-        </is>
-      </c>
-      <c r="U2" s="11" t="inlineStr">
-        <is>
-          <t>前高区间确认、冲高回落与板块环境区分</t>
-        </is>
-      </c>
-      <c r="V2" s="11" t="inlineStr">
-        <is>
-          <t>数据源：搜狐历史行情个股；东方财富半导体板块；窗口为2025-06-26至2025-07-09。</t>
-        </is>
-      </c>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="10" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="11" t="n"/>
+      <c r="V2" s="11" t="n"/>
       <c r="W2" s="26">
         <f>IF(B2="","",B2+3)</f>
         <v/>
@@ -1152,139 +1054,41 @@
         <f>IF(B2="","",(--(B2&lt;&gt;"")+--(C2&lt;&gt;"")+--(D2&lt;&gt;"")+--(E2&lt;&gt;"")+--(F2&lt;&gt;"")+--(G2&lt;&gt;"")+--(H2&lt;&gt;"")+--(I2&lt;&gt;"")+--(J2&lt;&gt;"")+--(K2&lt;&gt;"")+--(L2&lt;&gt;"")+--(M2&lt;&gt;"")+--(N2&lt;&gt;"")+--(O2&lt;&gt;"")+--(P2&lt;&gt;"")+--(Q2&lt;&gt;"")+--(R2&lt;&gt;"")+--(S2&lt;&gt;"")+--(T2&lt;&gt;""))/19)</f>
         <v/>
       </c>
-      <c r="AA2" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AB2" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AC2" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AD2" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
+      <c r="AA2" s="18" t="n"/>
+      <c r="AB2" s="18" t="n"/>
+      <c r="AC2" s="18" t="n"/>
+      <c r="AD2" s="18" t="n"/>
       <c r="AE2" s="7">
         <f>IF(B2="","",IF(AND(AA2="合格",AB2="合格",AC2="合格",AD2="合格"),"有效","无效"))</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="72" customHeight="1">
+    <row r="3">
       <c r="A3" s="7">
         <f>IF(B3="","",TEXT(B3,"yyyymmdd")&amp;"-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B3" s="25" t="n">
-        <v>45835</v>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>长电科技 600584.SH</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>半导体/封测</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>震荡</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>轮动强势</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>强于板块</t>
-        </is>
-      </c>
-      <c r="H3" s="10" t="inlineStr">
-        <is>
-          <t>前高</t>
-        </is>
-      </c>
-      <c r="I3" s="10" t="inlineStr">
-        <is>
-          <t>33.40</t>
-        </is>
-      </c>
-      <c r="J3" s="10" t="inlineStr">
-        <is>
-          <t>前一日最高33.40形成短线压力，今日最高34.08且收33.60。</t>
-        </is>
-      </c>
-      <c r="K3" s="10" t="inlineStr">
-        <is>
-          <t>突破</t>
-        </is>
-      </c>
-      <c r="L3" s="10" t="inlineStr">
-        <is>
-          <t>清晰</t>
-        </is>
-      </c>
-      <c r="M3" s="10" t="inlineStr">
-        <is>
-          <t>放量突破</t>
-        </is>
-      </c>
-      <c r="N3" s="10" t="inlineStr">
-        <is>
-          <t>收33.60涨1.94%，最高34.08，成交量46.41万手明显放大；半导体涨1.08%，上证跌0.70%。</t>
-        </is>
-      </c>
-      <c r="O3" s="10" t="inlineStr">
-        <is>
-          <t>真突破/启动尝试</t>
-        </is>
-      </c>
-      <c r="P3" s="10" t="inlineStr">
-        <is>
-          <t>在大盘走弱时个股放量收过33.40，且强于半导体，说明有资金主动推动突破。</t>
-        </is>
-      </c>
-      <c r="Q3" s="10" t="inlineStr">
-        <is>
-          <t>收盘离日高较远，若很快跌回33.40下方并放量，突破解释会削弱。</t>
-        </is>
-      </c>
-      <c r="R3" s="10" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>量价与相对强弱都支持，但只是一日突破，还没有回踩确认。</t>
-        </is>
-      </c>
-      <c r="T3" s="10" t="inlineStr">
-        <is>
-          <t>后续只看是否守住33.30-33.40。</t>
-        </is>
-      </c>
-      <c r="U3" s="11" t="inlineStr">
-        <is>
-          <t>突破有效性、放量含义、回踩确认</t>
-        </is>
-      </c>
-      <c r="V3" s="11" t="inlineStr">
-        <is>
-          <t>这是突破尝试，不等于已经进入主升。</t>
-        </is>
-      </c>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="11" t="n"/>
+      <c r="V3" s="11" t="n"/>
       <c r="W3" s="26">
         <f>IF(B3="","",B3+3)</f>
         <v/>
@@ -1301,139 +1105,41 @@
         <f>IF(B3="","",(--(B3&lt;&gt;"")+--(C3&lt;&gt;"")+--(D3&lt;&gt;"")+--(E3&lt;&gt;"")+--(F3&lt;&gt;"")+--(G3&lt;&gt;"")+--(H3&lt;&gt;"")+--(I3&lt;&gt;"")+--(J3&lt;&gt;"")+--(K3&lt;&gt;"")+--(L3&lt;&gt;"")+--(M3&lt;&gt;"")+--(N3&lt;&gt;"")+--(O3&lt;&gt;"")+--(P3&lt;&gt;"")+--(Q3&lt;&gt;"")+--(R3&lt;&gt;"")+--(S3&lt;&gt;"")+--(T3&lt;&gt;""))/19)</f>
         <v/>
       </c>
-      <c r="AA3" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AB3" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AC3" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AD3" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
+      <c r="AA3" s="18" t="n"/>
+      <c r="AB3" s="18" t="n"/>
+      <c r="AC3" s="18" t="n"/>
+      <c r="AD3" s="18" t="n"/>
       <c r="AE3" s="7">
         <f>IF(B3="","",IF(AND(AA3="合格",AB3="合格",AC3="合格",AD3="合格"),"有效","无效"))</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="72" customHeight="1">
+    <row r="4">
       <c r="A4" s="7">
         <f>IF(B4="","",TEXT(B4,"yyyymmdd")&amp;"-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B4" s="25" t="n">
-        <v>45838</v>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>长电科技 600584.SH</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>半导体/封测</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>震荡偏强</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>主线强势</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>弱于板块</t>
-        </is>
-      </c>
-      <c r="H4" s="10" t="inlineStr">
-        <is>
-          <t>前高</t>
-        </is>
-      </c>
-      <c r="I4" s="10" t="inlineStr">
-        <is>
-          <t>34.08</t>
-        </is>
-      </c>
-      <c r="J4" s="10" t="inlineStr">
-        <is>
-          <t>6月27日突破日最高34.08是新的短线观察压力。</t>
-        </is>
-      </c>
-      <c r="K4" s="10" t="inlineStr">
-        <is>
-          <t>接近</t>
-        </is>
-      </c>
-      <c r="L4" s="10" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="M4" s="10" t="inlineStr">
-        <is>
-          <t>横盘震荡</t>
-        </is>
-      </c>
-      <c r="N4" s="10" t="inlineStr">
-        <is>
-          <t>收33.69涨0.27%，成交量30.02万手缩小；半导体涨1.67%，上证涨0.59%。</t>
-        </is>
-      </c>
-      <c r="O4" s="10" t="inlineStr">
-        <is>
-          <t>震荡整理</t>
-        </is>
-      </c>
-      <c r="P4" s="10" t="inlineStr">
-        <is>
-          <t>突破后没有继续放量上攻，只是在33.40上方小幅整理；但弱于强势板块，说明主动性不足。</t>
-        </is>
-      </c>
-      <c r="Q4" s="10" t="inlineStr">
-        <is>
-          <t>如果次日放量站上34.08，则今天的缩量可能只是突破后的蓄势。</t>
-        </is>
-      </c>
-      <c r="R4" s="10" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>事实更多指向整理，但是否转弱还缺少跌破关键位。</t>
-        </is>
-      </c>
-      <c r="T4" s="10" t="inlineStr">
-        <is>
-          <t>后续只看是否收盘站上34.08。</t>
-        </is>
-      </c>
-      <c r="U4" s="11" t="inlineStr">
-        <is>
-          <t>突破后缩量整理、相对板块弱势识别</t>
-        </is>
-      </c>
-      <c r="V4" s="11" t="inlineStr">
-        <is>
-          <t>这一天的重点不是预测涨跌，而是识别“突破后没有立刻延续”。</t>
-        </is>
-      </c>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="10" t="n"/>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="11" t="n"/>
+      <c r="V4" s="11" t="n"/>
       <c r="W4" s="26">
         <f>IF(B4="","",B4+3)</f>
         <v/>
@@ -1450,139 +1156,41 @@
         <f>IF(B4="","",(--(B4&lt;&gt;"")+--(C4&lt;&gt;"")+--(D4&lt;&gt;"")+--(E4&lt;&gt;"")+--(F4&lt;&gt;"")+--(G4&lt;&gt;"")+--(H4&lt;&gt;"")+--(I4&lt;&gt;"")+--(J4&lt;&gt;"")+--(K4&lt;&gt;"")+--(L4&lt;&gt;"")+--(M4&lt;&gt;"")+--(N4&lt;&gt;"")+--(O4&lt;&gt;"")+--(P4&lt;&gt;"")+--(Q4&lt;&gt;"")+--(R4&lt;&gt;"")+--(S4&lt;&gt;"")+--(T4&lt;&gt;""))/19)</f>
         <v/>
       </c>
-      <c r="AA4" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AB4" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AC4" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AD4" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
+      <c r="AA4" s="18" t="n"/>
+      <c r="AB4" s="18" t="n"/>
+      <c r="AC4" s="18" t="n"/>
+      <c r="AD4" s="18" t="n"/>
       <c r="AE4" s="7">
         <f>IF(B4="","",IF(AND(AA4="合格",AB4="合格",AC4="合格",AD4="合格"),"有效","无效"))</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="72" customHeight="1">
+    <row r="5">
       <c r="A5" s="7">
         <f>IF(B5="","",TEXT(B5,"yyyymmdd")&amp;"-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B5" s="25" t="n">
-        <v>45839</v>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>长电科技 600584.SH</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>半导体/封测</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>震荡偏强</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>轮动强势</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>强于板块</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>前高</t>
-        </is>
-      </c>
-      <c r="I5" s="10" t="inlineStr">
-        <is>
-          <t>34.08</t>
-        </is>
-      </c>
-      <c r="J5" s="10" t="inlineStr">
-        <is>
-          <t>6月27日高点34.08被盘中突破，但收盘33.97没有站上。</t>
-        </is>
-      </c>
-      <c r="K5" s="10" t="inlineStr">
-        <is>
-          <t>站上未确认</t>
-        </is>
-      </c>
-      <c r="L5" s="10" t="inlineStr">
-        <is>
-          <t>清晰</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>高位放量震荡</t>
-        </is>
-      </c>
-      <c r="N5" s="10" t="inlineStr">
-        <is>
-          <t>收33.97涨0.83%，盘中最高34.38创短线新高，成交量39.29万手；半导体涨0.33%，上证涨0.39%。</t>
-        </is>
-      </c>
-      <c r="O5" s="10" t="inlineStr">
-        <is>
-          <t>高位分歧</t>
-        </is>
-      </c>
-      <c r="P5" s="10" t="inlineStr">
-        <is>
-          <t>盘中新高但收回34.08下方，说明新高位置有抛压；不过个股仍强于板块，不能直接判定见顶。</t>
-        </is>
-      </c>
-      <c r="Q5" s="10" t="inlineStr">
-        <is>
-          <t>如果后续收盘站回34.08并继续放量，新高回落可能只是分歧换手。</t>
-        </is>
-      </c>
-      <c r="R5" s="10" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>关键位清晰且有冲高回落，但趋势尚未破坏。</t>
-        </is>
-      </c>
-      <c r="T5" s="10" t="inlineStr">
-        <is>
-          <t>后续只看是否收盘站上34.08。</t>
-        </is>
-      </c>
-      <c r="U5" s="11" t="inlineStr">
-        <is>
-          <t>盘中新高与收盘确认、分歧换手</t>
-        </is>
-      </c>
-      <c r="V5" s="11" t="inlineStr">
-        <is>
-          <t>这是判断“真突破还是假突破”的典型样本。</t>
-        </is>
-      </c>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="10" t="n"/>
+      <c r="J5" s="10" t="n"/>
+      <c r="K5" s="10" t="n"/>
+      <c r="L5" s="10" t="n"/>
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="10" t="n"/>
+      <c r="O5" s="10" t="n"/>
+      <c r="P5" s="10" t="n"/>
+      <c r="Q5" s="10" t="n"/>
+      <c r="R5" s="10" t="n"/>
+      <c r="S5" s="10" t="n"/>
+      <c r="T5" s="10" t="n"/>
+      <c r="U5" s="11" t="n"/>
+      <c r="V5" s="11" t="n"/>
       <c r="W5" s="26">
         <f>IF(B5="","",B5+3)</f>
         <v/>
@@ -1599,139 +1207,41 @@
         <f>IF(B5="","",(--(B5&lt;&gt;"")+--(C5&lt;&gt;"")+--(D5&lt;&gt;"")+--(E5&lt;&gt;"")+--(F5&lt;&gt;"")+--(G5&lt;&gt;"")+--(H5&lt;&gt;"")+--(I5&lt;&gt;"")+--(J5&lt;&gt;"")+--(K5&lt;&gt;"")+--(L5&lt;&gt;"")+--(M5&lt;&gt;"")+--(N5&lt;&gt;"")+--(O5&lt;&gt;"")+--(P5&lt;&gt;"")+--(Q5&lt;&gt;"")+--(R5&lt;&gt;"")+--(S5&lt;&gt;"")+--(T5&lt;&gt;""))/19)</f>
         <v/>
       </c>
-      <c r="AA5" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AB5" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AC5" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AD5" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
+      <c r="AA5" s="18" t="n"/>
+      <c r="AB5" s="18" t="n"/>
+      <c r="AC5" s="18" t="n"/>
+      <c r="AD5" s="18" t="n"/>
       <c r="AE5" s="7">
         <f>IF(B5="","",IF(AND(AA5="合格",AB5="合格",AC5="合格",AD5="合格"),"有效","无效"))</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="72" customHeight="1">
+    <row r="6">
       <c r="A6" s="7">
         <f>IF(B6="","",TEXT(B6,"yyyymmdd")&amp;"-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B6" s="25" t="n">
-        <v>45840</v>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>长电科技 600584.SH</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>半导体/封测</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>震荡</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>退潮</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>强于板块</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>大阳线低点</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>33.00-33.30</t>
-        </is>
-      </c>
-      <c r="J6" s="10" t="inlineStr">
-        <is>
-          <t>6月27日放量阳线低点33.00，6月25日前高33.30附近构成回踩观察区。</t>
-        </is>
-      </c>
-      <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t>回踩</t>
-        </is>
-      </c>
-      <c r="L6" s="10" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="M6" s="10" t="inlineStr">
-        <is>
-          <t>缩量回调</t>
-        </is>
-      </c>
-      <c r="N6" s="10" t="inlineStr">
-        <is>
-          <t>收33.31跌1.94%，最低33.23，成交量26.21万手；半导体跌2.18%，上证跌0.09%。</t>
-        </is>
-      </c>
-      <c r="O6" s="10" t="inlineStr">
-        <is>
-          <t>健康回调</t>
-        </is>
-      </c>
-      <c r="P6" s="10" t="inlineStr">
-        <is>
-          <t>价格回到33.00-33.30支撑区附近但没有明显放量跌破，且跌幅小于半导体，暂时更像突破后的回踩。</t>
-        </is>
-      </c>
-      <c r="Q6" s="10" t="inlineStr">
-        <is>
-          <t>如果随后跌破33.00并收不回，健康回调解释会被证伪。</t>
-        </is>
-      </c>
-      <c r="R6" s="10" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>回踩区间是人工划出来的，不够精确，只能作为低强度假设。</t>
-        </is>
-      </c>
-      <c r="T6" s="10" t="inlineStr">
-        <is>
-          <t>后续只看是否跌破33.00。</t>
-        </is>
-      </c>
-      <c r="U6" s="11" t="inlineStr">
-        <is>
-          <t>大阳线低点、支撑区间而非单点、缩量回调</t>
-        </is>
-      </c>
-      <c r="V6" s="11" t="inlineStr">
-        <is>
-          <t>这行故意保持低判断强度，因为支撑区不是非常清晰。</t>
-        </is>
-      </c>
+      <c r="B6" s="25" t="n"/>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n"/>
+      <c r="I6" s="10" t="n"/>
+      <c r="J6" s="10" t="n"/>
+      <c r="K6" s="10" t="n"/>
+      <c r="L6" s="10" t="n"/>
+      <c r="M6" s="10" t="n"/>
+      <c r="N6" s="10" t="n"/>
+      <c r="O6" s="10" t="n"/>
+      <c r="P6" s="10" t="n"/>
+      <c r="Q6" s="10" t="n"/>
+      <c r="R6" s="10" t="n"/>
+      <c r="S6" s="10" t="n"/>
+      <c r="T6" s="10" t="n"/>
+      <c r="U6" s="11" t="n"/>
+      <c r="V6" s="11" t="n"/>
       <c r="W6" s="26">
         <f>IF(B6="","",B6+3)</f>
         <v/>
@@ -1748,139 +1258,41 @@
         <f>IF(B6="","",(--(B6&lt;&gt;"")+--(C6&lt;&gt;"")+--(D6&lt;&gt;"")+--(E6&lt;&gt;"")+--(F6&lt;&gt;"")+--(G6&lt;&gt;"")+--(H6&lt;&gt;"")+--(I6&lt;&gt;"")+--(J6&lt;&gt;"")+--(K6&lt;&gt;"")+--(L6&lt;&gt;"")+--(M6&lt;&gt;"")+--(N6&lt;&gt;"")+--(O6&lt;&gt;"")+--(P6&lt;&gt;"")+--(Q6&lt;&gt;"")+--(R6&lt;&gt;"")+--(S6&lt;&gt;"")+--(T6&lt;&gt;""))/19)</f>
         <v/>
       </c>
-      <c r="AA6" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AB6" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AC6" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AD6" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
+      <c r="AA6" s="18" t="n"/>
+      <c r="AB6" s="18" t="n"/>
+      <c r="AC6" s="18" t="n"/>
+      <c r="AD6" s="18" t="n"/>
       <c r="AE6" s="7">
         <f>IF(B6="","",IF(AND(AA6="合格",AB6="合格",AC6="合格",AD6="合格"),"有效","无效"))</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="72" customHeight="1">
+    <row r="7">
       <c r="A7" s="7">
         <f>IF(B7="","",TEXT(B7,"yyyymmdd")&amp;"-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B7" s="25" t="n">
-        <v>45841</v>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>长电科技 600584.SH</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>半导体/封测</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>震荡偏强</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>震荡</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>强于板块</t>
-        </is>
-      </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>箱体下沿</t>
-        </is>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>33.20-33.30</t>
-        </is>
-      </c>
-      <c r="J7" s="10" t="inlineStr">
-        <is>
-          <t>7月2日低点33.23与7月3日低点33.23重合，形成短线震荡下沿。</t>
-        </is>
-      </c>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>回踩</t>
-        </is>
-      </c>
-      <c r="L7" s="10" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="M7" s="10" t="inlineStr">
-        <is>
-          <t>回踩支撑不破</t>
-        </is>
-      </c>
-      <c r="N7" s="10" t="inlineStr">
-        <is>
-          <t>收33.53涨0.66%，最低33.23再次守住，成交量21.32万手继续缩小；半导体涨0.36%，上证涨0.18%。</t>
-        </is>
-      </c>
-      <c r="O7" s="10" t="inlineStr">
-        <is>
-          <t>震荡整理</t>
-        </is>
-      </c>
-      <c r="P7" s="10" t="inlineStr">
-        <is>
-          <t>同一低点附近两次守住，价格没有继续向下；但成交量缩小，说明反弹力度也不强。</t>
-        </is>
-      </c>
-      <c r="Q7" s="10" t="inlineStr">
-        <is>
-          <t>如果后续跌破33.20，所谓箱体下沿就只是临时巧合。</t>
-        </is>
-      </c>
-      <c r="R7" s="10" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>只有两个交易日的低点，结构证据偏少。</t>
-        </is>
-      </c>
-      <c r="T7" s="10" t="inlineStr">
-        <is>
-          <t>后续只看是否跌破33.20。</t>
-        </is>
-      </c>
-      <c r="U7" s="11" t="inlineStr">
-        <is>
-          <t>箱体下沿需要多次确认、缩量反弹强弱</t>
-        </is>
-      </c>
-      <c r="V7" s="11" t="inlineStr">
-        <is>
-          <t>这是一条“暂时结构”，不是强结论。</t>
-        </is>
-      </c>
+      <c r="B7" s="25" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="10" t="n"/>
+      <c r="J7" s="10" t="n"/>
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="10" t="n"/>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="10" t="n"/>
+      <c r="P7" s="10" t="n"/>
+      <c r="Q7" s="10" t="n"/>
+      <c r="R7" s="10" t="n"/>
+      <c r="S7" s="10" t="n"/>
+      <c r="T7" s="10" t="n"/>
+      <c r="U7" s="11" t="n"/>
+      <c r="V7" s="11" t="n"/>
       <c r="W7" s="26">
         <f>IF(B7="","",B7+3)</f>
         <v/>
@@ -1897,139 +1309,41 @@
         <f>IF(B7="","",(--(B7&lt;&gt;"")+--(C7&lt;&gt;"")+--(D7&lt;&gt;"")+--(E7&lt;&gt;"")+--(F7&lt;&gt;"")+--(G7&lt;&gt;"")+--(H7&lt;&gt;"")+--(I7&lt;&gt;"")+--(J7&lt;&gt;"")+--(K7&lt;&gt;"")+--(L7&lt;&gt;"")+--(M7&lt;&gt;"")+--(N7&lt;&gt;"")+--(O7&lt;&gt;"")+--(P7&lt;&gt;"")+--(Q7&lt;&gt;"")+--(R7&lt;&gt;"")+--(S7&lt;&gt;"")+--(T7&lt;&gt;""))/19)</f>
         <v/>
       </c>
-      <c r="AA7" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AB7" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AC7" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AD7" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
+      <c r="AA7" s="18" t="n"/>
+      <c r="AB7" s="18" t="n"/>
+      <c r="AC7" s="18" t="n"/>
+      <c r="AD7" s="18" t="n"/>
       <c r="AE7" s="7">
         <f>IF(B7="","",IF(AND(AA7="合格",AB7="合格",AC7="合格",AD7="合格"),"有效","无效"))</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="72" customHeight="1">
+    <row r="8">
       <c r="A8" s="7">
         <f>IF(B8="","",TEXT(B8,"yyyymmdd")&amp;"-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B8" s="25" t="n">
-        <v>45842</v>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>长电科技 600584.SH</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>半导体/封测</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>震荡偏强</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>震荡</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>同步板块</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>箱体下沿</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>33.20-33.30</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>前两日33.23低点形成短线下沿，今日收33.23正好回到下沿。</t>
-        </is>
-      </c>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>接近</t>
-        </is>
-      </c>
-      <c r="L8" s="10" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="M8" s="10" t="inlineStr">
-        <is>
-          <t>横盘震荡</t>
-        </is>
-      </c>
-      <c r="N8" s="10" t="inlineStr">
-        <is>
-          <t>收33.23跌0.89%，最低33.10，成交量20.30万手；半导体跌0.93%，上证涨0.32%。</t>
-        </is>
-      </c>
-      <c r="O8" s="10" t="inlineStr">
-        <is>
-          <t>震荡整理</t>
-        </is>
-      </c>
-      <c r="P8" s="10" t="inlineStr">
-        <is>
-          <t>价格回到下沿附近但没有放量大跌，仍可能是箱体震荡；不过大盘上涨时个股不涨，主动性偏弱。</t>
-        </is>
-      </c>
-      <c r="Q8" s="10" t="inlineStr">
-        <is>
-          <t>如果下一日跌破33.00，震荡整理会转向突破失败或转弱。</t>
-        </is>
-      </c>
-      <c r="R8" s="10" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>位置接近支撑但没有明确反包或放量，结论只能低强度。</t>
-        </is>
-      </c>
-      <c r="T8" s="10" t="inlineStr">
-        <is>
-          <t>后续只看是否跌破33.00。</t>
-        </is>
-      </c>
-      <c r="U8" s="11" t="inlineStr">
-        <is>
-          <t>弱于大盘的含义、箱体下沿有效性</t>
-        </is>
-      </c>
-      <c r="V8" s="11" t="inlineStr">
-        <is>
-          <t>这里更适合观察，不适合急着下强判断。</t>
-        </is>
-      </c>
+      <c r="B8" s="25" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n"/>
+      <c r="I8" s="10" t="n"/>
+      <c r="J8" s="10" t="n"/>
+      <c r="K8" s="10" t="n"/>
+      <c r="L8" s="10" t="n"/>
+      <c r="M8" s="10" t="n"/>
+      <c r="N8" s="10" t="n"/>
+      <c r="O8" s="10" t="n"/>
+      <c r="P8" s="10" t="n"/>
+      <c r="Q8" s="10" t="n"/>
+      <c r="R8" s="10" t="n"/>
+      <c r="S8" s="10" t="n"/>
+      <c r="T8" s="10" t="n"/>
+      <c r="U8" s="11" t="n"/>
+      <c r="V8" s="11" t="n"/>
       <c r="W8" s="26">
         <f>IF(B8="","",B8+3)</f>
         <v/>
@@ -2046,139 +1360,41 @@
         <f>IF(B8="","",(--(B8&lt;&gt;"")+--(C8&lt;&gt;"")+--(D8&lt;&gt;"")+--(E8&lt;&gt;"")+--(F8&lt;&gt;"")+--(G8&lt;&gt;"")+--(H8&lt;&gt;"")+--(I8&lt;&gt;"")+--(J8&lt;&gt;"")+--(K8&lt;&gt;"")+--(L8&lt;&gt;"")+--(M8&lt;&gt;"")+--(N8&lt;&gt;"")+--(O8&lt;&gt;"")+--(P8&lt;&gt;"")+--(Q8&lt;&gt;"")+--(R8&lt;&gt;"")+--(S8&lt;&gt;"")+--(T8&lt;&gt;""))/19)</f>
         <v/>
       </c>
-      <c r="AA8" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AB8" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AC8" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AD8" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
+      <c r="AA8" s="18" t="n"/>
+      <c r="AB8" s="18" t="n"/>
+      <c r="AC8" s="18" t="n"/>
+      <c r="AD8" s="18" t="n"/>
       <c r="AE8" s="7">
         <f>IF(B8="","",IF(AND(AA8="合格",AB8="合格",AC8="合格",AD8="合格"),"有效","无效"))</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="72" customHeight="1">
+    <row r="9">
       <c r="A9" s="7">
         <f>IF(B9="","",TEXT(B9,"yyyymmdd")&amp;"-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B9" s="25" t="n">
-        <v>45845</v>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>长电科技 600584.SH</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>半导体/封测</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>震荡偏强</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>震荡</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>弱于板块</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>大阳线低点</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>33.00</t>
-        </is>
-      </c>
-      <c r="J9" s="10" t="inlineStr">
-        <is>
-          <t>6月27日放量阳线低点33.00，此前也作为回踩观察位。</t>
-        </is>
-      </c>
-      <c r="K9" s="10" t="inlineStr">
-        <is>
-          <t>跌破</t>
-        </is>
-      </c>
-      <c r="L9" s="10" t="inlineStr">
-        <is>
-          <t>清晰</t>
-        </is>
-      </c>
-      <c r="M9" s="10" t="inlineStr">
-        <is>
-          <t>跌破关键位</t>
-        </is>
-      </c>
-      <c r="N9" s="10" t="inlineStr">
-        <is>
-          <t>收32.95跌0.84%，最低32.88，跌破33.00，成交量15.46万手；半导体跌0.13%，上证微涨0.02%。</t>
-        </is>
-      </c>
-      <c r="O9" s="10" t="inlineStr">
-        <is>
-          <t>退潮转弱</t>
-        </is>
-      </c>
-      <c r="P9" s="10" t="inlineStr">
-        <is>
-          <t>在板块和大盘没有明显下跌时，个股跌破33.00关键位，说明前期突破结构被破坏。</t>
-        </is>
-      </c>
-      <c r="Q9" s="10" t="inlineStr">
-        <is>
-          <t>如果下一两日快速收回33.30上方，今天可能是假跌破。</t>
-        </is>
-      </c>
-      <c r="R9" s="10" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>关键位清晰，且相对板块转弱，但缩量下跌意味着杀跌并不充分。</t>
-        </is>
-      </c>
-      <c r="T9" s="10" t="inlineStr">
-        <is>
-          <t>后续只看是否收回33.30。</t>
-        </is>
-      </c>
-      <c r="U9" s="11" t="inlineStr">
-        <is>
-          <t>跌破关键位、假跌破识别、相对弱势</t>
-        </is>
-      </c>
-      <c r="V9" s="11" t="inlineStr">
-        <is>
-          <t>这一天是从“支撑观察”转为“结构受损观察”的分界。</t>
-        </is>
-      </c>
+      <c r="B9" s="25" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="10" t="n"/>
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="10" t="n"/>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="10" t="n"/>
+      <c r="P9" s="10" t="n"/>
+      <c r="Q9" s="10" t="n"/>
+      <c r="R9" s="10" t="n"/>
+      <c r="S9" s="10" t="n"/>
+      <c r="T9" s="10" t="n"/>
+      <c r="U9" s="11" t="n"/>
+      <c r="V9" s="11" t="n"/>
       <c r="W9" s="26">
         <f>IF(B9="","",B9+3)</f>
         <v/>
@@ -2195,139 +1411,41 @@
         <f>IF(B9="","",(--(B9&lt;&gt;"")+--(C9&lt;&gt;"")+--(D9&lt;&gt;"")+--(E9&lt;&gt;"")+--(F9&lt;&gt;"")+--(G9&lt;&gt;"")+--(H9&lt;&gt;"")+--(I9&lt;&gt;"")+--(J9&lt;&gt;"")+--(K9&lt;&gt;"")+--(L9&lt;&gt;"")+--(M9&lt;&gt;"")+--(N9&lt;&gt;"")+--(O9&lt;&gt;"")+--(P9&lt;&gt;"")+--(Q9&lt;&gt;"")+--(R9&lt;&gt;"")+--(S9&lt;&gt;"")+--(T9&lt;&gt;""))/19)</f>
         <v/>
       </c>
-      <c r="AA9" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AB9" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AC9" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AD9" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
+      <c r="AA9" s="18" t="n"/>
+      <c r="AB9" s="18" t="n"/>
+      <c r="AC9" s="18" t="n"/>
+      <c r="AD9" s="18" t="n"/>
       <c r="AE9" s="7">
         <f>IF(B9="","",IF(AND(AA9="合格",AB9="合格",AC9="合格",AD9="合格"),"有效","无效"))</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="72" customHeight="1">
+    <row r="10">
       <c r="A10" s="7">
         <f>IF(B10="","",TEXT(B10,"yyyymmdd")&amp;"-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B10" s="25" t="n">
-        <v>45846</v>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>长电科技 600584.SH</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>半导体/封测</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>上升</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>轮动强势</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>同步板块</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>前高</t>
-        </is>
-      </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>33.30-33.40</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="inlineStr">
-        <is>
-          <t>跌破33.00后快速收回，33.30-33.40重新变成修复确认位。</t>
-        </is>
-      </c>
-      <c r="K10" s="10" t="inlineStr">
-        <is>
-          <t>跌破后收回</t>
-        </is>
-      </c>
-      <c r="L10" s="10" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="M10" s="10" t="inlineStr">
-        <is>
-          <t>低位反弹</t>
-        </is>
-      </c>
-      <c r="N10" s="10" t="inlineStr">
-        <is>
-          <t>收33.55涨1.82%，最低33.01后收回33.30-33.40，成交量24.45万手；半导体涨1.50%，上证涨0.70%。</t>
-        </is>
-      </c>
-      <c r="O10" s="10" t="inlineStr">
-        <is>
-          <t>弱反弹</t>
-        </is>
-      </c>
-      <c r="P10" s="10" t="inlineStr">
-        <is>
-          <t>价格收回关键位说明7月7日跌破没有继续恶化，但反弹主要伴随大盘和板块转强，暂不能认定重新启动。</t>
-        </is>
-      </c>
-      <c r="Q10" s="10" t="inlineStr">
-        <is>
-          <t>如果后续不能继续站稳33.40并上攻33.80，反弹仍可能只是箱体震荡的一部分。</t>
-        </is>
-      </c>
-      <c r="R10" s="10" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>修复动作明确，但外部环境同步转强，个股独立性不足。</t>
-        </is>
-      </c>
-      <c r="T10" s="10" t="inlineStr">
-        <is>
-          <t>后续只看是否连续收在33.40上方。</t>
-        </is>
-      </c>
-      <c r="U10" s="11" t="inlineStr">
-        <is>
-          <t>跌破后收回、修复与重新启动区别</t>
-        </is>
-      </c>
-      <c r="V10" s="11" t="inlineStr">
-        <is>
-          <t>不要因为一天大涨就把它重新判成强趋势。</t>
-        </is>
-      </c>
+      <c r="B10" s="25" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="10" t="n"/>
+      <c r="J10" s="10" t="n"/>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="10" t="n"/>
+      <c r="M10" s="10" t="n"/>
+      <c r="N10" s="10" t="n"/>
+      <c r="O10" s="10" t="n"/>
+      <c r="P10" s="10" t="n"/>
+      <c r="Q10" s="10" t="n"/>
+      <c r="R10" s="10" t="n"/>
+      <c r="S10" s="10" t="n"/>
+      <c r="T10" s="10" t="n"/>
+      <c r="U10" s="11" t="n"/>
+      <c r="V10" s="11" t="n"/>
       <c r="W10" s="26">
         <f>IF(B10="","",B10+3)</f>
         <v/>
@@ -2344,139 +1462,41 @@
         <f>IF(B10="","",(--(B10&lt;&gt;"")+--(C10&lt;&gt;"")+--(D10&lt;&gt;"")+--(E10&lt;&gt;"")+--(F10&lt;&gt;"")+--(G10&lt;&gt;"")+--(H10&lt;&gt;"")+--(I10&lt;&gt;"")+--(J10&lt;&gt;"")+--(K10&lt;&gt;"")+--(L10&lt;&gt;"")+--(M10&lt;&gt;"")+--(N10&lt;&gt;"")+--(O10&lt;&gt;"")+--(P10&lt;&gt;"")+--(Q10&lt;&gt;"")+--(R10&lt;&gt;"")+--(S10&lt;&gt;"")+--(T10&lt;&gt;""))/19)</f>
         <v/>
       </c>
-      <c r="AA10" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AB10" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AC10" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AD10" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
+      <c r="AA10" s="18" t="n"/>
+      <c r="AB10" s="18" t="n"/>
+      <c r="AC10" s="18" t="n"/>
+      <c r="AD10" s="18" t="n"/>
       <c r="AE10" s="7">
         <f>IF(B10="","",IF(AND(AA10="合格",AB10="合格",AC10="合格",AD10="合格"),"有效","无效"))</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="72" customHeight="1">
+    <row r="11">
       <c r="A11" s="7">
         <f>IF(B11="","",TEXT(B11,"yyyymmdd")&amp;"-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B11" s="25" t="n">
-        <v>45847</v>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>长电科技 600584.SH</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>半导体/封测</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>震荡偏强</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>震荡</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>同步板块</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>箱体下沿</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>33.00-33.20</t>
-        </is>
-      </c>
-      <c r="J11" s="10" t="inlineStr">
-        <is>
-          <t>近几日低点集中在33.00-33.20，当前仍围绕这个区域反复。</t>
-        </is>
-      </c>
-      <c r="K11" s="10" t="inlineStr">
-        <is>
-          <t>接近</t>
-        </is>
-      </c>
-      <c r="L11" s="10" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="M11" s="10" t="inlineStr">
-        <is>
-          <t>横盘震荡</t>
-        </is>
-      </c>
-      <c r="N11" s="10" t="inlineStr">
-        <is>
-          <t>收33.18跌1.10%，最低33.10，成交量19.43万手；半导体跌1.12%，上证跌0.13%。</t>
-        </is>
-      </c>
-      <c r="O11" s="10" t="inlineStr">
-        <is>
-          <t>震荡整理</t>
-        </is>
-      </c>
-      <c r="P11" s="10" t="inlineStr">
-        <is>
-          <t>价格没有继续向上确认33.40，也没有有效跌破33.00，说明短线仍在33.00-34.08之间震荡。</t>
-        </is>
-      </c>
-      <c r="Q11" s="10" t="inlineStr">
-        <is>
-          <t>如果后续放量跌破33.00，震荡整理会转为转弱；若放量站上34.08，才说明重新转强。</t>
-        </is>
-      </c>
-      <c r="R11" s="10" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>上下边界都有，但当前价格在中低位，方向信息不足。</t>
-        </is>
-      </c>
-      <c r="T11" s="10" t="inlineStr">
-        <is>
-          <t>后续只看33.00是否被有效跌破。</t>
-        </is>
-      </c>
-      <c r="U11" s="11" t="inlineStr">
-        <is>
-          <t>箱体边界、方向未明时降低判断强度</t>
-        </is>
-      </c>
-      <c r="V11" s="11" t="inlineStr">
-        <is>
-          <t>这是一个“看不清就承认看不清”的样本。</t>
-        </is>
-      </c>
+      <c r="B11" s="25" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n"/>
+      <c r="I11" s="10" t="n"/>
+      <c r="J11" s="10" t="n"/>
+      <c r="K11" s="10" t="n"/>
+      <c r="L11" s="10" t="n"/>
+      <c r="M11" s="10" t="n"/>
+      <c r="N11" s="10" t="n"/>
+      <c r="O11" s="10" t="n"/>
+      <c r="P11" s="10" t="n"/>
+      <c r="Q11" s="10" t="n"/>
+      <c r="R11" s="10" t="n"/>
+      <c r="S11" s="10" t="n"/>
+      <c r="T11" s="10" t="n"/>
+      <c r="U11" s="11" t="n"/>
+      <c r="V11" s="11" t="n"/>
       <c r="W11" s="26">
         <f>IF(B11="","",B11+3)</f>
         <v/>
@@ -2493,26 +1513,10 @@
         <f>IF(B11="","",(--(B11&lt;&gt;"")+--(C11&lt;&gt;"")+--(D11&lt;&gt;"")+--(E11&lt;&gt;"")+--(F11&lt;&gt;"")+--(G11&lt;&gt;"")+--(H11&lt;&gt;"")+--(I11&lt;&gt;"")+--(J11&lt;&gt;"")+--(K11&lt;&gt;"")+--(L11&lt;&gt;"")+--(M11&lt;&gt;"")+--(N11&lt;&gt;"")+--(O11&lt;&gt;"")+--(P11&lt;&gt;"")+--(Q11&lt;&gt;"")+--(R11&lt;&gt;"")+--(S11&lt;&gt;"")+--(T11&lt;&gt;""))/19)</f>
         <v/>
       </c>
-      <c r="AA11" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AB11" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AC11" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-      <c r="AD11" s="18" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
+      <c r="AA11" s="18" t="n"/>
+      <c r="AB11" s="18" t="n"/>
+      <c r="AC11" s="18" t="n"/>
+      <c r="AD11" s="18" t="n"/>
       <c r="AE11" s="7">
         <f>IF(B11="","",IF(AND(AA11="合格",AB11="合格",AC11="合格",AD11="合格"),"有效","无效"))</f>
         <v/>
@@ -28464,817 +27468,229 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="72" customHeight="1">
+    <row r="2">
       <c r="A2" s="15">
         <f>IF(B2="","","V-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B2" s="18" t="inlineStr">
-        <is>
-          <t>20250626-001</t>
-        </is>
-      </c>
-      <c r="C2" s="28" t="n">
-        <v>45834</v>
-      </c>
-      <c r="D2" s="18" t="inlineStr">
-        <is>
-          <t>长电科技 600584.SH</t>
-        </is>
-      </c>
-      <c r="E2" s="18" t="inlineStr">
-        <is>
-          <t>前高</t>
-        </is>
-      </c>
-      <c r="F2" s="18" t="inlineStr">
-        <is>
-          <t>33.30-33.40</t>
-        </is>
-      </c>
-      <c r="G2" s="18" t="inlineStr">
-        <is>
-          <t>冲高回落</t>
-        </is>
-      </c>
-      <c r="H2" s="18" t="inlineStr">
-        <is>
-          <t>高位分歧</t>
-        </is>
-      </c>
-      <c r="I2" s="18" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="J2" s="18" t="inlineStr">
-        <is>
-          <t>后续只看是否收盘重新站上33.40。</t>
-        </is>
-      </c>
-      <c r="K2" s="18" t="inlineStr">
-        <is>
-          <t>3日</t>
-        </is>
-      </c>
-      <c r="L2" s="28" t="n">
-        <v>45839</v>
-      </c>
-      <c r="M2" s="18" t="inlineStr">
-        <is>
-          <t>收33.97，盘中34.38，已重新站上33.40但没有收过34.08。</t>
-        </is>
-      </c>
-      <c r="N2" s="18" t="inlineStr">
-        <is>
-          <t>向上延续</t>
-        </is>
-      </c>
-      <c r="O2" s="18" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="P2" s="18" t="inlineStr">
-        <is>
-          <t>出现</t>
-        </is>
-      </c>
-      <c r="Q2" s="18" t="inlineStr">
-        <is>
-          <t>削弱</t>
-        </is>
-      </c>
-      <c r="R2" s="18" t="inlineStr">
-        <is>
-          <t>过程合理</t>
-        </is>
-      </c>
-      <c r="S2" s="18" t="inlineStr">
-        <is>
-          <t>概率结果失败</t>
-        </is>
-      </c>
-      <c r="T2" s="18" t="inlineStr">
-        <is>
-          <t>前高分歧不等于失败，必须等收盘确认。</t>
-        </is>
-      </c>
-      <c r="U2" s="18" t="inlineStr">
-        <is>
-          <t>收盘确认与盘中突破区别</t>
-        </is>
-      </c>
+      <c r="B2" s="18" t="n"/>
+      <c r="C2" s="28" t="n"/>
+      <c r="D2" s="18" t="n"/>
+      <c r="E2" s="18" t="n"/>
+      <c r="F2" s="18" t="n"/>
+      <c r="G2" s="18" t="n"/>
+      <c r="H2" s="18" t="n"/>
+      <c r="I2" s="18" t="n"/>
+      <c r="J2" s="18" t="n"/>
+      <c r="K2" s="18" t="n"/>
+      <c r="L2" s="28" t="n"/>
+      <c r="M2" s="18" t="n"/>
+      <c r="N2" s="18" t="n"/>
+      <c r="O2" s="18" t="n"/>
+      <c r="P2" s="18" t="n"/>
+      <c r="Q2" s="18" t="n"/>
+      <c r="R2" s="18" t="n"/>
+      <c r="S2" s="18" t="n"/>
+      <c r="T2" s="18" t="n"/>
+      <c r="U2" s="18" t="n"/>
       <c r="V2" s="29">
         <f>IF(L2="","",IF(TODAY()&gt;=L2,"到期","未到期"))</f>
         <v/>
       </c>
-      <c r="W2" s="18" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="X2" s="18" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="72" customHeight="1">
+      <c r="W2" s="18" t="n"/>
+      <c r="X2" s="18" t="n"/>
+    </row>
+    <row r="3">
       <c r="A3" s="15">
         <f>IF(B3="","","V-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B3" s="18" t="inlineStr">
-        <is>
-          <t>20250627-002</t>
-        </is>
-      </c>
-      <c r="C3" s="28" t="n">
-        <v>45835</v>
-      </c>
-      <c r="D3" s="18" t="inlineStr">
-        <is>
-          <t>长电科技 600584.SH</t>
-        </is>
-      </c>
-      <c r="E3" s="18" t="inlineStr">
-        <is>
-          <t>前高</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>33.40</t>
-        </is>
-      </c>
-      <c r="G3" s="18" t="inlineStr">
-        <is>
-          <t>放量突破</t>
-        </is>
-      </c>
-      <c r="H3" s="18" t="inlineStr">
-        <is>
-          <t>真突破/启动尝试</t>
-        </is>
-      </c>
-      <c r="I3" s="18" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="J3" s="18" t="inlineStr">
-        <is>
-          <t>后续只看是否守住33.30-33.40。</t>
-        </is>
-      </c>
-      <c r="K3" s="18" t="inlineStr">
-        <is>
-          <t>3日</t>
-        </is>
-      </c>
-      <c r="L3" s="28" t="n">
-        <v>45840</v>
-      </c>
-      <c r="M3" s="18" t="inlineStr">
-        <is>
-          <t>收33.31，基本回踩到33.30附近，未明显跌破但突破延续不足。</t>
-        </is>
-      </c>
-      <c r="N3" s="18" t="inlineStr">
-        <is>
-          <t>震荡消化</t>
-        </is>
-      </c>
-      <c r="O3" s="18" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="P3" s="18" t="inlineStr">
-        <is>
-          <t>部分出现</t>
-        </is>
-      </c>
-      <c r="Q3" s="18" t="inlineStr">
-        <is>
-          <t>削弱</t>
-        </is>
-      </c>
-      <c r="R3" s="18" t="inlineStr">
-        <is>
-          <t>过程合理</t>
-        </is>
-      </c>
-      <c r="S3" s="18" t="inlineStr">
-        <is>
-          <t>无明显错误</t>
-        </is>
-      </c>
-      <c r="T3" s="18" t="inlineStr">
-        <is>
-          <t>突破后如果不能继续放量，先按震荡消化处理。</t>
-        </is>
-      </c>
-      <c r="U3" s="18" t="inlineStr">
-        <is>
-          <t>突破后的回踩确认</t>
-        </is>
-      </c>
+      <c r="B3" s="18" t="n"/>
+      <c r="C3" s="28" t="n"/>
+      <c r="D3" s="18" t="n"/>
+      <c r="E3" s="18" t="n"/>
+      <c r="F3" s="18" t="n"/>
+      <c r="G3" s="18" t="n"/>
+      <c r="H3" s="18" t="n"/>
+      <c r="I3" s="18" t="n"/>
+      <c r="J3" s="18" t="n"/>
+      <c r="K3" s="18" t="n"/>
+      <c r="L3" s="28" t="n"/>
+      <c r="M3" s="18" t="n"/>
+      <c r="N3" s="18" t="n"/>
+      <c r="O3" s="18" t="n"/>
+      <c r="P3" s="18" t="n"/>
+      <c r="Q3" s="18" t="n"/>
+      <c r="R3" s="18" t="n"/>
+      <c r="S3" s="18" t="n"/>
+      <c r="T3" s="18" t="n"/>
+      <c r="U3" s="18" t="n"/>
       <c r="V3" s="29">
         <f>IF(L3="","",IF(TODAY()&gt;=L3,"到期","未到期"))</f>
         <v/>
       </c>
-      <c r="W3" s="18" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="X3" s="18" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="72" customHeight="1">
+      <c r="W3" s="18" t="n"/>
+      <c r="X3" s="18" t="n"/>
+    </row>
+    <row r="4">
       <c r="A4" s="15">
         <f>IF(B4="","","V-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>20250630-003</t>
-        </is>
-      </c>
-      <c r="C4" s="28" t="n">
-        <v>45838</v>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>长电科技 600584.SH</t>
-        </is>
-      </c>
-      <c r="E4" s="18" t="inlineStr">
-        <is>
-          <t>前高</t>
-        </is>
-      </c>
-      <c r="F4" s="18" t="inlineStr">
-        <is>
-          <t>34.08</t>
-        </is>
-      </c>
-      <c r="G4" s="18" t="inlineStr">
-        <is>
-          <t>横盘震荡</t>
-        </is>
-      </c>
-      <c r="H4" s="18" t="inlineStr">
-        <is>
-          <t>震荡整理</t>
-        </is>
-      </c>
-      <c r="I4" s="18" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="J4" s="18" t="inlineStr">
-        <is>
-          <t>后续只看是否收盘站上34.08。</t>
-        </is>
-      </c>
-      <c r="K4" s="18" t="inlineStr">
-        <is>
-          <t>3日</t>
-        </is>
-      </c>
-      <c r="L4" s="28" t="n">
-        <v>45841</v>
-      </c>
-      <c r="M4" s="18" t="inlineStr">
-        <is>
-          <t>收33.53，未站上34.08，仍在33.20-34.08之间。</t>
-        </is>
-      </c>
-      <c r="N4" s="18" t="inlineStr">
-        <is>
-          <t>震荡消化</t>
-        </is>
-      </c>
-      <c r="O4" s="18" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="P4" s="18" t="inlineStr">
-        <is>
-          <t>未出现</t>
-        </is>
-      </c>
-      <c r="Q4" s="18" t="inlineStr">
-        <is>
-          <t>强化</t>
-        </is>
-      </c>
-      <c r="R4" s="18" t="inlineStr">
-        <is>
-          <t>过程合理</t>
-        </is>
-      </c>
-      <c r="S4" s="18" t="inlineStr">
-        <is>
-          <t>无明显错误</t>
-        </is>
-      </c>
-      <c r="T4" s="18" t="inlineStr">
-        <is>
-          <t>低强度震荡判断可以接受，不需要硬预测方向。</t>
-        </is>
-      </c>
-      <c r="U4" s="18" t="inlineStr">
-        <is>
-          <t>箱体上沿确认</t>
-        </is>
-      </c>
+      <c r="B4" s="18" t="n"/>
+      <c r="C4" s="28" t="n"/>
+      <c r="D4" s="18" t="n"/>
+      <c r="E4" s="18" t="n"/>
+      <c r="F4" s="18" t="n"/>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n"/>
+      <c r="I4" s="18" t="n"/>
+      <c r="J4" s="18" t="n"/>
+      <c r="K4" s="18" t="n"/>
+      <c r="L4" s="28" t="n"/>
+      <c r="M4" s="18" t="n"/>
+      <c r="N4" s="18" t="n"/>
+      <c r="O4" s="18" t="n"/>
+      <c r="P4" s="18" t="n"/>
+      <c r="Q4" s="18" t="n"/>
+      <c r="R4" s="18" t="n"/>
+      <c r="S4" s="18" t="n"/>
+      <c r="T4" s="18" t="n"/>
+      <c r="U4" s="18" t="n"/>
       <c r="V4" s="29">
         <f>IF(L4="","",IF(TODAY()&gt;=L4,"到期","未到期"))</f>
         <v/>
       </c>
-      <c r="W4" s="18" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="X4" s="18" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="72" customHeight="1">
+      <c r="W4" s="18" t="n"/>
+      <c r="X4" s="18" t="n"/>
+    </row>
+    <row r="5">
       <c r="A5" s="15">
         <f>IF(B5="","","V-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>20250701-004</t>
-        </is>
-      </c>
-      <c r="C5" s="28" t="n">
-        <v>45839</v>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>长电科技 600584.SH</t>
-        </is>
-      </c>
-      <c r="E5" s="18" t="inlineStr">
-        <is>
-          <t>前高</t>
-        </is>
-      </c>
-      <c r="F5" s="18" t="inlineStr">
-        <is>
-          <t>34.08</t>
-        </is>
-      </c>
-      <c r="G5" s="18" t="inlineStr">
-        <is>
-          <t>高位放量震荡</t>
-        </is>
-      </c>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t>高位分歧</t>
-        </is>
-      </c>
-      <c r="I5" s="18" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="J5" s="18" t="inlineStr">
-        <is>
-          <t>后续只看是否收盘站上34.08。</t>
-        </is>
-      </c>
-      <c r="K5" s="18" t="inlineStr">
-        <is>
-          <t>3日</t>
-        </is>
-      </c>
-      <c r="L5" s="28" t="n">
-        <v>45842</v>
-      </c>
-      <c r="M5" s="18" t="inlineStr">
-        <is>
-          <t>收33.23，没有站回34.08，反而回到短线下沿。</t>
-        </is>
-      </c>
-      <c r="N5" s="18" t="inlineStr">
-        <is>
-          <t>冲高回落</t>
-        </is>
-      </c>
-      <c r="O5" s="18" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="P5" s="18" t="inlineStr">
-        <is>
-          <t>未出现</t>
-        </is>
-      </c>
-      <c r="Q5" s="18" t="inlineStr">
-        <is>
-          <t>强化</t>
-        </is>
-      </c>
-      <c r="R5" s="18" t="inlineStr">
-        <is>
-          <t>过程合理</t>
-        </is>
-      </c>
-      <c r="S5" s="18" t="inlineStr">
-        <is>
-          <t>无明显错误</t>
-        </is>
-      </c>
-      <c r="T5" s="18" t="inlineStr">
-        <is>
-          <t>盘中新高不如收盘站稳重要。</t>
-        </is>
-      </c>
-      <c r="U5" s="18" t="inlineStr">
-        <is>
-          <t>假突破与分歧换手区分</t>
-        </is>
-      </c>
+      <c r="B5" s="18" t="n"/>
+      <c r="C5" s="28" t="n"/>
+      <c r="D5" s="18" t="n"/>
+      <c r="E5" s="18" t="n"/>
+      <c r="F5" s="18" t="n"/>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="n"/>
+      <c r="I5" s="18" t="n"/>
+      <c r="J5" s="18" t="n"/>
+      <c r="K5" s="18" t="n"/>
+      <c r="L5" s="28" t="n"/>
+      <c r="M5" s="18" t="n"/>
+      <c r="N5" s="18" t="n"/>
+      <c r="O5" s="18" t="n"/>
+      <c r="P5" s="18" t="n"/>
+      <c r="Q5" s="18" t="n"/>
+      <c r="R5" s="18" t="n"/>
+      <c r="S5" s="18" t="n"/>
+      <c r="T5" s="18" t="n"/>
+      <c r="U5" s="18" t="n"/>
       <c r="V5" s="29">
         <f>IF(L5="","",IF(TODAY()&gt;=L5,"到期","未到期"))</f>
         <v/>
       </c>
-      <c r="W5" s="18" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="X5" s="18" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="72" customHeight="1">
+      <c r="W5" s="18" t="n"/>
+      <c r="X5" s="18" t="n"/>
+    </row>
+    <row r="6">
       <c r="A6" s="15">
         <f>IF(B6="","","V-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>20250702-005</t>
-        </is>
-      </c>
-      <c r="C6" s="28" t="n">
-        <v>45840</v>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>长电科技 600584.SH</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>大阳线低点</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>33.00-33.30</t>
-        </is>
-      </c>
-      <c r="G6" s="18" t="inlineStr">
-        <is>
-          <t>缩量回调</t>
-        </is>
-      </c>
-      <c r="H6" s="18" t="inlineStr">
-        <is>
-          <t>健康回调</t>
-        </is>
-      </c>
-      <c r="I6" s="18" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="J6" s="18" t="inlineStr">
-        <is>
-          <t>后续只看是否跌破33.00。</t>
-        </is>
-      </c>
-      <c r="K6" s="18" t="inlineStr">
-        <is>
-          <t>3日</t>
-        </is>
-      </c>
-      <c r="L6" s="28" t="n">
-        <v>45845</v>
-      </c>
-      <c r="M6" s="18" t="inlineStr">
-        <is>
-          <t>收32.95，跌破33.00，但成交量继续缩小。</t>
-        </is>
-      </c>
-      <c r="N6" s="18" t="inlineStr">
-        <is>
-          <t>跌破支撑</t>
-        </is>
-      </c>
-      <c r="O6" s="18" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="P6" s="18" t="inlineStr">
-        <is>
-          <t>出现</t>
-        </is>
-      </c>
-      <c r="Q6" s="18" t="inlineStr">
-        <is>
-          <t>证伪</t>
-        </is>
-      </c>
-      <c r="R6" s="18" t="inlineStr">
-        <is>
-          <t>概率失败</t>
-        </is>
-      </c>
-      <c r="S6" s="18" t="inlineStr">
-        <is>
-          <t>概率结果失败</t>
-        </is>
-      </c>
-      <c r="T6" s="18" t="inlineStr">
-        <is>
-          <t>健康回调假设被证伪时要切换解释，不要补理由。</t>
-        </is>
-      </c>
-      <c r="U6" s="18" t="inlineStr">
-        <is>
-          <t>支撑区间有效性</t>
-        </is>
-      </c>
+      <c r="B6" s="18" t="n"/>
+      <c r="C6" s="28" t="n"/>
+      <c r="D6" s="18" t="n"/>
+      <c r="E6" s="18" t="n"/>
+      <c r="F6" s="18" t="n"/>
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="18" t="n"/>
+      <c r="I6" s="18" t="n"/>
+      <c r="J6" s="18" t="n"/>
+      <c r="K6" s="18" t="n"/>
+      <c r="L6" s="28" t="n"/>
+      <c r="M6" s="18" t="n"/>
+      <c r="N6" s="18" t="n"/>
+      <c r="O6" s="18" t="n"/>
+      <c r="P6" s="18" t="n"/>
+      <c r="Q6" s="18" t="n"/>
+      <c r="R6" s="18" t="n"/>
+      <c r="S6" s="18" t="n"/>
+      <c r="T6" s="18" t="n"/>
+      <c r="U6" s="18" t="n"/>
       <c r="V6" s="29">
         <f>IF(L6="","",IF(TODAY()&gt;=L6,"到期","未到期"))</f>
         <v/>
       </c>
-      <c r="W6" s="18" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="X6" s="18" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="72" customHeight="1">
+      <c r="W6" s="18" t="n"/>
+      <c r="X6" s="18" t="n"/>
+    </row>
+    <row r="7">
       <c r="A7" s="15">
         <f>IF(B7="","","V-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>20250703-006</t>
-        </is>
-      </c>
-      <c r="C7" s="28" t="n">
-        <v>45841</v>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>长电科技 600584.SH</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>箱体下沿</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>33.20-33.30</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>回踩支撑不破</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>震荡整理</t>
-        </is>
-      </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="J7" s="18" t="inlineStr">
-        <is>
-          <t>后续只看是否跌破33.20。</t>
-        </is>
-      </c>
-      <c r="K7" s="18" t="inlineStr">
-        <is>
-          <t>3日</t>
-        </is>
-      </c>
-      <c r="L7" s="28" t="n">
-        <v>45846</v>
-      </c>
-      <c r="M7" s="18" t="inlineStr">
-        <is>
-          <t>收33.55，未跌破33.20，并重新收回33.40上方。</t>
-        </is>
-      </c>
-      <c r="N7" s="18" t="inlineStr">
-        <is>
-          <t>修复转强</t>
-        </is>
-      </c>
-      <c r="O7" s="18" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="P7" s="18" t="inlineStr">
-        <is>
-          <t>未出现</t>
-        </is>
-      </c>
-      <c r="Q7" s="18" t="inlineStr">
-        <is>
-          <t>强化</t>
-        </is>
-      </c>
-      <c r="R7" s="18" t="inlineStr">
-        <is>
-          <t>过程合理</t>
-        </is>
-      </c>
-      <c r="S7" s="18" t="inlineStr">
-        <is>
-          <t>无明显错误</t>
-        </is>
-      </c>
-      <c r="T7" s="18" t="inlineStr">
-        <is>
-          <t>两个低点形成的临时箱体可以观察，但强度要低。</t>
-        </is>
-      </c>
-      <c r="U7" s="18" t="inlineStr">
-        <is>
-          <t>临时箱体识别</t>
-        </is>
-      </c>
+      <c r="B7" s="18" t="n"/>
+      <c r="C7" s="28" t="n"/>
+      <c r="D7" s="18" t="n"/>
+      <c r="E7" s="18" t="n"/>
+      <c r="F7" s="18" t="n"/>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="n"/>
+      <c r="I7" s="18" t="n"/>
+      <c r="J7" s="18" t="n"/>
+      <c r="K7" s="18" t="n"/>
+      <c r="L7" s="28" t="n"/>
+      <c r="M7" s="18" t="n"/>
+      <c r="N7" s="18" t="n"/>
+      <c r="O7" s="18" t="n"/>
+      <c r="P7" s="18" t="n"/>
+      <c r="Q7" s="18" t="n"/>
+      <c r="R7" s="18" t="n"/>
+      <c r="S7" s="18" t="n"/>
+      <c r="T7" s="18" t="n"/>
+      <c r="U7" s="18" t="n"/>
       <c r="V7" s="29">
         <f>IF(L7="","",IF(TODAY()&gt;=L7,"到期","未到期"))</f>
         <v/>
       </c>
-      <c r="W7" s="18" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="X7" s="18" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="72" customHeight="1">
+      <c r="W7" s="18" t="n"/>
+      <c r="X7" s="18" t="n"/>
+    </row>
+    <row r="8">
       <c r="A8" s="15">
         <f>IF(B8="","","V-"&amp;TEXT(ROW()-1,"000"))</f>
         <v/>
       </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>20250704-007</t>
-        </is>
-      </c>
-      <c r="C8" s="28" t="n">
-        <v>45842</v>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>长电科技 600584.SH</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>箱体下沿</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>33.20-33.30</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>横盘震荡</t>
-        </is>
-      </c>
-      <c r="H8" s="18" t="inlineStr">
-        <is>
-          <t>震荡整理</t>
-        </is>
-      </c>
-      <c r="I8" s="18" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="J8" s="18" t="inlineStr">
-        <is>
-          <t>后续只看是否跌破33.00。</t>
-        </is>
-      </c>
-      <c r="K8" s="18" t="inlineStr">
-        <is>
-          <t>3日</t>
-        </is>
-      </c>
-      <c r="L8" s="28" t="n">
-        <v>45847</v>
-      </c>
-      <c r="M8" s="18" t="inlineStr">
-        <is>
-          <t>收33.18，未跌破33.00，但也没有向上确认。</t>
-        </is>
-      </c>
-      <c r="N8" s="18" t="inlineStr">
-        <is>
-          <t>震荡消化</t>
-        </is>
-      </c>
-      <c r="O8" s="18" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="P8" s="18" t="inlineStr">
-        <is>
-          <t>未出现</t>
-        </is>
-      </c>
-      <c r="Q8" s="18" t="inlineStr">
-        <is>
-          <t>仍不确定</t>
-        </is>
-      </c>
-      <c r="R8" s="18" t="inlineStr">
-        <is>
-          <t>过程合理</t>
-        </is>
-      </c>
-      <c r="S8" s="18" t="inlineStr">
-        <is>
-          <t>无明显错误</t>
-        </is>
-      </c>
-      <c r="T8" s="18" t="inlineStr">
-        <is>
-          <t>低强度判断允许保持不确定，不必强行改成看多或看空。</t>
-        </is>
-      </c>
-      <c r="U8" s="18" t="inlineStr">
-        <is>
-          <t>方向不明时的观察纪律</t>
-        </is>
-      </c>
+      <c r="B8" s="18" t="n"/>
+      <c r="C8" s="28" t="n"/>
+      <c r="D8" s="18" t="n"/>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="18" t="n"/>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="n"/>
+      <c r="I8" s="18" t="n"/>
+      <c r="J8" s="18" t="n"/>
+      <c r="K8" s="18" t="n"/>
+      <c r="L8" s="28" t="n"/>
+      <c r="M8" s="18" t="n"/>
+      <c r="N8" s="18" t="n"/>
+      <c r="O8" s="18" t="n"/>
+      <c r="P8" s="18" t="n"/>
+      <c r="Q8" s="18" t="n"/>
+      <c r="R8" s="18" t="n"/>
+      <c r="S8" s="18" t="n"/>
+      <c r="T8" s="18" t="n"/>
+      <c r="U8" s="18" t="n"/>
       <c r="V8" s="29">
         <f>IF(L8="","",IF(TODAY()&gt;=L8,"到期","未到期"))</f>
         <v/>
       </c>
-      <c r="W8" s="18" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="X8" s="18" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
+      <c r="W8" s="18" t="n"/>
+      <c r="X8" s="18" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="15">

--- a/stock_review_template.xlsx
+++ b/stock_review_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12700" activeTab="1"/>
+    <workbookView windowWidth="29400" windowHeight="12740" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="368">
   <si>
     <t>股票观察训练模板</t>
   </si>
@@ -212,7 +212,7 @@
     <t>同步板块</t>
   </si>
   <si>
-    <t>前高</t>
+    <t>箱体上沿</t>
   </si>
   <si>
     <t>104～106</t>
@@ -332,6 +332,51 @@
     <t>不预测，就是分歧很中，观察分歧过后的是往上走还是往下走，向下的动能越来越大，需要消化</t>
   </si>
   <si>
+    <t>回踩支撑不破</t>
+  </si>
+  <si>
+    <t>半导体板块涨幅不大，长电的涨幅高于半导体板块位为3.69% 盘中最低点到达91.65, 节奏基本跟着板块，跌的时候超过板块，涨的时候也超过板块，</t>
+  </si>
+  <si>
+    <t>基本跟着板块律动，没有超过板块太多，板块位1.42%，</t>
+  </si>
+  <si>
+    <t>最低下跌7个多点还是拉回来了，全天高达10个点的波动，说明多方有力量，至少是超过板块的能量，</t>
+  </si>
+  <si>
+    <t>多空博弈严重，不太好判断</t>
+  </si>
+  <si>
+    <t>如果空方消耗完毕，应该是会突破压力区间，超过106并站稳，但是注意不能是跟着板块一起冲上去的</t>
+  </si>
+  <si>
+    <t>空方的力量在这一波下跌当中有没有释放完毕，分歧是不是消化完毕，准备第三轮</t>
+  </si>
+  <si>
+    <t>沪电股份</t>
+  </si>
+  <si>
+    <t>元件</t>
+  </si>
+  <si>
+    <t>箱体下沿</t>
+  </si>
+  <si>
+    <t>122～126</t>
+  </si>
+  <si>
+    <t>连续最近一个多月的箱体的下沿几乎是这个位置，到达这个位置就上去了</t>
+  </si>
+  <si>
+    <t>远离</t>
+  </si>
+  <si>
+    <t>放量突破</t>
+  </si>
+  <si>
+    <t>跟着板块一起冲高触及涨停</t>
+  </si>
+  <si>
     <t>怎么找</t>
   </si>
   <si>
@@ -342,6 +387,9 @@
   </si>
   <si>
     <t>可用句式</t>
+  </si>
+  <si>
+    <t>前高</t>
   </si>
   <si>
     <t>找最近一次冲高后回落的最高价，优先看近5-20日内明显高点。</t>
@@ -371,9 +419,6 @@
     <t>关键位置是前低__，因为这是上一轮资金防守的位置。</t>
   </si>
   <si>
-    <t>箱体上沿</t>
-  </si>
-  <si>
     <t>找一段横盘震荡中多次冲不过去的上边界。</t>
   </si>
   <si>
@@ -384,9 +429,6 @@
   </si>
   <si>
     <t>关键位置是箱体上沿__，因为多次冲高都在这里附近受阻。</t>
-  </si>
-  <si>
-    <t>箱体下沿</t>
   </si>
   <si>
     <t>找一段横盘震荡中多次跌不下去的下边界。</t>
@@ -512,9 +554,6 @@
     <t>新手提示</t>
   </si>
   <si>
-    <t>放量突破</t>
-  </si>
-  <si>
     <t>前高/箱体上沿/整数位/放量分歧位。</t>
   </si>
   <si>
@@ -612,9 +651,6 @@
   </si>
   <si>
     <t>跌破是风险信号，不是绝对结论。</t>
-  </si>
-  <si>
-    <t>回踩支撑不破</t>
   </si>
   <si>
     <t>前高突破位/前低/箱体上沿/大阳线低点/均线。</t>
@@ -1070,9 +1106,6 @@
     <t>5日线</t>
   </si>
   <si>
-    <t>远离</t>
-  </si>
-  <si>
     <t>高位分歧</t>
   </si>
   <si>
@@ -1148,7 +1181,7 @@
     <numFmt numFmtId="176" formatCode="0.0%"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1176,13 +1209,6 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1336,7 +1362,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="43">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1412,12 +1438,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1753,13 +1773,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1768,37 +1791,37 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1813,73 +1836,70 @@
     <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1953,7 +1973,7 @@
     <xf numFmtId="9" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1965,7 +1985,7 @@
     <xf numFmtId="9" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2838,47 +2858,85 @@
         <v>无效</v>
       </c>
     </row>
-    <row r="5" ht="17" spans="1:31">
+    <row r="5" ht="68" spans="1:31">
       <c r="A5" s="8" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
+        <v>20260714-004</v>
+      </c>
+      <c r="B5" s="22">
+        <v>46217</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>58</v>
+      </c>
       <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="19"/>
-      <c r="S5" s="19"/>
-      <c r="T5" s="19"/>
+      <c r="K5" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="L5" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="M5" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="N5" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="O5" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="P5" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q5" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="R5" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="S5" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="T5" s="19" t="s">
+        <v>94</v>
+      </c>
       <c r="U5" s="20"/>
-      <c r="V5" s="20"/>
-      <c r="W5" s="23" t="str">
+      <c r="V5" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="W5" s="23">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="X5" s="23" t="str">
+        <v>46220</v>
+      </c>
+      <c r="X5" s="23">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="Y5" s="23" t="str">
+        <v>46222</v>
+      </c>
+      <c r="Y5" s="23">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Z5" s="24" t="str">
+        <v>46227</v>
+      </c>
+      <c r="Z5" s="24">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.947368421052632</v>
       </c>
       <c r="AA5" s="14"/>
       <c r="AB5" s="14"/>
@@ -2886,27 +2944,53 @@
       <c r="AD5" s="14"/>
       <c r="AE5" s="8" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="17" spans="1:31">
+        <v>无效</v>
+      </c>
+    </row>
+    <row r="6" ht="51" spans="1:31">
       <c r="A6" s="8" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
+        <v>20260714-005</v>
+      </c>
+      <c r="B6" s="22">
+        <v>46217</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="J6" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="M6" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="N6" s="19" t="s">
+        <v>103</v>
+      </c>
       <c r="O6" s="19"/>
       <c r="P6" s="19"/>
       <c r="Q6" s="19"/>
@@ -2915,21 +2999,21 @@
       <c r="T6" s="19"/>
       <c r="U6" s="20"/>
       <c r="V6" s="20"/>
-      <c r="W6" s="23" t="str">
+      <c r="W6" s="23">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="X6" s="23" t="str">
+        <v>46220</v>
+      </c>
+      <c r="X6" s="23">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="Y6" s="23" t="str">
+        <v>46222</v>
+      </c>
+      <c r="Y6" s="23">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Z6" s="24" t="str">
+        <v>46227</v>
+      </c>
+      <c r="Z6" s="24">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.684210526315789</v>
       </c>
       <c r="AA6" s="14"/>
       <c r="AB6" s="14"/>
@@ -2937,7 +3021,7 @@
       <c r="AD6" s="14"/>
       <c r="AE6" s="8" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>无效</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:31">
@@ -28155,6 +28239,9 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="10">
+    <dataValidation type="list" allowBlank="1" sqref="H5 H2:H4 H6:H500">
+      <formula1>选项!$D$2:$D$15</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="E2:E500">
       <formula1>选项!$A$2:$A$7</formula1>
     </dataValidation>
@@ -28163,9 +28250,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="G2:G500">
       <formula1>选项!$C$2:$C$5</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H500">
-      <formula1>选项!$D$2:$D$15</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="K2:K500">
       <formula1>选项!$E$2:$E$10</formula1>
@@ -28206,186 +28290,186 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" ht="78" customHeight="1" spans="1:5">
       <c r="A2" s="19" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" ht="78" customHeight="1" spans="1:5">
       <c r="A3" s="19" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" ht="78" customHeight="1" spans="1:5">
       <c r="A4" s="19" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" ht="78" customHeight="1" spans="1:5">
       <c r="A5" s="19" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" ht="78" customHeight="1" spans="1:5">
       <c r="A6" s="19" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" ht="78" customHeight="1" spans="1:5">
       <c r="A7" s="19" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" ht="78" customHeight="1" spans="1:5">
       <c r="A8" s="19" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" ht="78" customHeight="1" spans="1:5">
       <c r="A9" s="19" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" ht="78" customHeight="1" spans="1:5">
       <c r="A10" s="19" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" ht="78" customHeight="1" spans="1:5">
       <c r="A11" s="19" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -28413,71 +28497,71 @@
   <sheetData>
     <row r="1" ht="17" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" ht="90" customHeight="1" spans="1:7">
       <c r="A2" s="19" t="s">
-        <v>149</v>
+        <v>102</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" ht="90" customHeight="1" spans="1:7">
       <c r="A3" s="19" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" ht="90" customHeight="1" spans="1:7">
@@ -28485,206 +28569,206 @@
         <v>73</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" ht="90" customHeight="1" spans="1:7">
       <c r="A5" s="19" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1" spans="1:7">
       <c r="A6" s="19" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" ht="90" customHeight="1" spans="1:7">
       <c r="A7" s="19" t="s">
-        <v>183</v>
+        <v>89</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1" spans="1:7">
       <c r="A8" s="19" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1" spans="1:7">
       <c r="A9" s="19" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" ht="90" customHeight="1" spans="1:7">
       <c r="A10" s="19" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" ht="90" customHeight="1" spans="1:7">
       <c r="A11" s="19" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12" ht="90" customHeight="1" spans="1:7">
       <c r="A12" s="19" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -28723,76 +28807,76 @@
   <sheetData>
     <row r="1" ht="34" spans="1:24">
       <c r="A1" s="11" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="D1" s="11" t="s">
         <v>23</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="O1" s="11" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="T1" s="11" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="U1" s="11" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="V1" s="12" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="W1" s="11" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="X1" s="11" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:24">
@@ -44822,236 +44906,236 @@
   <sheetData>
     <row r="1" ht="20.4" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="5"/>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:3">
       <c r="A3" s="7" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="B3" s="8">
         <f>COUNTA(每日观察!B2:B500)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:3">
       <c r="A4" s="7" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="B4" s="8">
         <f>COUNTIF(每日观察!Z2:Z500,1)</f>
         <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:3">
       <c r="A5" s="7" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B5" s="10">
         <f>IFERROR(B4/B3,"")</f>
-        <v>0.333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:3">
       <c r="A6" s="7" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="B6" s="8">
         <f>COUNTIF(每日观察!AE2:AE500,"有效")</f>
         <v>0</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:3">
       <c r="A7" s="7" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="B7" s="10">
         <f>IFERROR(B6/B3,"")</f>
         <v>0</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:3">
       <c r="A8" s="7" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B8" s="8">
         <f>COUNTIF(每日观察!AA2:AA500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:3">
       <c r="A9" s="7" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="B9" s="8">
         <f>COUNTIF(每日观察!AB2:AB500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:3">
       <c r="A10" s="7" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="B10" s="8">
         <f>COUNTIF(每日观察!AC2:AC500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:3">
       <c r="A11" s="7" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(每日观察!AD2:AD500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:3">
       <c r="A12" s="7" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B12" s="8">
         <f>COUNTIF(每日观察!H2:H500,"无清晰位置")</f>
         <v>0</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:3">
       <c r="A13" s="7" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="B13" s="8">
         <f>COUNTIF(每日观察!L2:L500,"不清晰")</f>
         <v>0</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:3">
       <c r="A14" s="7" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="B14" s="8">
         <f>COUNTIF(每日观察!R2:R500,"高")</f>
         <v>1</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:3">
       <c r="A15" s="7" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="B15" s="8">
         <f>COUNTA(事后验证!B2:B500)</f>
         <v>0</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:3">
       <c r="A16" s="7" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="B16" s="8">
         <f>COUNTIF(事后验证!R2:R500,"关键位置找错")</f>
         <v>0</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:3">
       <c r="A17" s="7" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B17" s="8">
         <f>COUNTIF(事后验证!R2:R500,"理由链断裂")</f>
         <v>0</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B18" s="8">
         <f>COUNTIF(事后验证!R2:R500,"漏掉反证")</f>
         <v>0</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="B19" s="8">
         <f>COUNTIF(事后验证!R2:R500,"过度确定")</f>
         <v>0</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="B20" s="8">
         <f>COUNTIF(事后验证!R2:R500,"概率失败")</f>
         <v>0</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -45095,31 +45179,31 @@
         <v>33</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>17</v>
@@ -45133,60 +45217,60 @@
         <v>54</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>149</v>
+        <v>102</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>67</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:18">
       <c r="A3" s="2" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>55</v>
@@ -45195,143 +45279,143 @@
         <v>56</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>75</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:18">
       <c r="A4" s="2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>73</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>78</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>73</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:18">
       <c r="A5" s="2" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>81</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>60</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:18">
@@ -45342,25 +45426,25 @@
         <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>335</v>
+        <v>101</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:18">
@@ -45371,115 +45455,115 @@
         <v>81</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>183</v>
+        <v>89</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" ht="34" spans="1:18">
       <c r="D8" s="2" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" ht="34" spans="1:18">
       <c r="D9" s="2" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>64</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:18">
       <c r="D10" s="2" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>81</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:18">
       <c r="D11" s="2" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
     </row>
     <row r="12" ht="17" spans="1:18">
       <c r="D12" s="2" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
     </row>
     <row r="13" ht="17" spans="1:18">
       <c r="D13" s="2" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>62</v>
@@ -45487,7 +45571,7 @@
     </row>
     <row r="14" ht="17" spans="1:18">
       <c r="D14" s="2" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" ht="17" spans="1:18">

--- a/stock_review_template.xlsx
+++ b/stock_review_template.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="375">
   <si>
     <t>股票观察训练模板</t>
   </si>
@@ -377,6 +377,36 @@
     <t>跟着板块一起冲高触及涨停</t>
   </si>
   <si>
+    <t>弱于板块</t>
+  </si>
+  <si>
+    <t>90～92</t>
+  </si>
+  <si>
+    <t>最近有7天基本在这个位置都会反弹</t>
+  </si>
+  <si>
+    <t>缩量回调</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 今天先进封装板块大跌-5.17%，长电科技跌停，超过板块的跌幅，但是量也没有特别大，没有很多出逃的资金</t>
+  </si>
+  <si>
+    <t>高位分歧</t>
+  </si>
+  <si>
+    <t>目前长电在一个箱体内部震荡，上不去，下不来，很尴尬，还需要等待分歧结束，才可以确认是向上还是向下，也就是多空双方其实立场并不鲜明，获利的多，然后亏的也不算多，可以持有，但是总的来说越往下空方就会越来越多</t>
+  </si>
+  <si>
+    <t>是箱体震荡，还是开始下跌，目前还看不出来，需要再观察，跌停是情绪，还是真的出逃，判断几个主要来源是压力位支撑位，相对板块的强度，还有每天的振幅</t>
+  </si>
+  <si>
+    <t>即使跌停，依然在箱体下沿，没破均线，MACD也是贴着0线，并没有很差，但是波动确实大</t>
+  </si>
+  <si>
+    <t>是否会向下冲过箱体下沿，还是一个假突破随后开始第三波，或者继续向下跌</t>
+  </si>
+  <si>
     <t>怎么找</t>
   </si>
   <si>
@@ -570,9 +600,6 @@
   </si>
   <si>
     <t>不要写“突破=要涨”，要写突破围绕哪个位置发生。</t>
-  </si>
-  <si>
-    <t>缩量回调</t>
   </si>
   <si>
     <t>前高突破位/均线/大阳线低点/箱体上沿。</t>
@@ -1049,9 +1076,6 @@
     <t>首日异动</t>
   </si>
   <si>
-    <t>弱于板块</t>
-  </si>
-  <si>
     <t>跌破</t>
   </si>
   <si>
@@ -1104,9 +1128,6 @@
   </si>
   <si>
     <t>5日线</t>
-  </si>
-  <si>
-    <t>高位分歧</t>
   </si>
   <si>
     <t>跌破支撑</t>
@@ -3024,47 +3045,85 @@
         <v>无效</v>
       </c>
     </row>
-    <row r="7" ht="17" spans="1:31">
+    <row r="7" ht="101" spans="1:31">
       <c r="A7" s="8" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="19"/>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="19"/>
+        <v>20260715-006</v>
+      </c>
+      <c r="B7" s="22">
+        <v>46218</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="M7" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="N7" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="O7" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="P7" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q7" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="R7" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="S7" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="T7" s="19" t="s">
+        <v>113</v>
+      </c>
       <c r="U7" s="20"/>
       <c r="V7" s="20"/>
-      <c r="W7" s="23" t="str">
+      <c r="W7" s="23">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="X7" s="23" t="str">
+        <v>46221</v>
+      </c>
+      <c r="X7" s="23">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="Y7" s="23" t="str">
+        <v>46223</v>
+      </c>
+      <c r="Y7" s="23">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Z7" s="24" t="str">
+        <v>46228</v>
+      </c>
+      <c r="Z7" s="24">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AA7" s="14"/>
       <c r="AB7" s="14"/>
@@ -3072,7 +3131,7 @@
       <c r="AD7" s="14"/>
       <c r="AE7" s="8" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>无效</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:31">
@@ -28290,50 +28349,50 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" ht="78" customHeight="1" spans="1:5">
       <c r="A2" s="19" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" ht="78" customHeight="1" spans="1:5">
       <c r="A3" s="19" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" ht="78" customHeight="1" spans="1:5">
@@ -28341,16 +28400,16 @@
         <v>57</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" ht="78" customHeight="1" spans="1:5">
@@ -28358,118 +28417,118 @@
         <v>98</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" ht="78" customHeight="1" spans="1:5">
       <c r="A6" s="19" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" ht="78" customHeight="1" spans="1:5">
       <c r="A7" s="19" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" ht="78" customHeight="1" spans="1:5">
       <c r="A8" s="19" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" ht="78" customHeight="1" spans="1:5">
       <c r="A9" s="19" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" ht="78" customHeight="1" spans="1:5">
       <c r="A10" s="19" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" ht="78" customHeight="1" spans="1:5">
       <c r="A11" s="19" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -28497,25 +28556,25 @@
   <sheetData>
     <row r="1" ht="17" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" ht="90" customHeight="1" spans="1:7">
@@ -28523,45 +28582,45 @@
         <v>102</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" ht="90" customHeight="1" spans="1:7">
       <c r="A3" s="19" t="s">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" ht="90" customHeight="1" spans="1:7">
@@ -28569,68 +28628,68 @@
         <v>73</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" ht="90" customHeight="1" spans="1:7">
       <c r="A5" s="19" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1" spans="1:7">
       <c r="A6" s="19" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" ht="90" customHeight="1" spans="1:7">
@@ -28638,137 +28697,137 @@
         <v>89</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1" spans="1:7">
       <c r="A8" s="19" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1" spans="1:7">
       <c r="A9" s="19" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" ht="90" customHeight="1" spans="1:7">
       <c r="A10" s="19" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" ht="90" customHeight="1" spans="1:7">
       <c r="A11" s="19" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" ht="90" customHeight="1" spans="1:7">
       <c r="A12" s="19" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -28807,76 +28866,76 @@
   <sheetData>
     <row r="1" ht="34" spans="1:24">
       <c r="A1" s="11" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="D1" s="11" t="s">
         <v>23</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="O1" s="11" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="T1" s="11" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="U1" s="11" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="V1" s="12" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="W1" s="11" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="X1" s="11" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:24">
@@ -44906,236 +44965,236 @@
   <sheetData>
     <row r="1" ht="20.4" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="5"/>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:3">
       <c r="A3" s="7" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="B3" s="8">
         <f>COUNTA(每日观察!B2:B500)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:3">
       <c r="A4" s="7" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="B4" s="8">
         <f>COUNTIF(每日观察!Z2:Z500,1)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:3">
       <c r="A5" s="7" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="B5" s="10">
         <f>IFERROR(B4/B3,"")</f>
-        <v>0.2</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:3">
       <c r="A6" s="7" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="B6" s="8">
         <f>COUNTIF(每日观察!AE2:AE500,"有效")</f>
         <v>0</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:3">
       <c r="A7" s="7" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="B7" s="10">
         <f>IFERROR(B6/B3,"")</f>
         <v>0</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:3">
       <c r="A8" s="7" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B8" s="8">
         <f>COUNTIF(每日观察!AA2:AA500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:3">
       <c r="A9" s="7" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B9" s="8">
         <f>COUNTIF(每日观察!AB2:AB500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:3">
       <c r="A10" s="7" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="B10" s="8">
         <f>COUNTIF(每日观察!AC2:AC500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:3">
       <c r="A11" s="7" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(每日观察!AD2:AD500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:3">
       <c r="A12" s="7" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="B12" s="8">
         <f>COUNTIF(每日观察!H2:H500,"无清晰位置")</f>
         <v>0</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:3">
       <c r="A13" s="7" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B13" s="8">
         <f>COUNTIF(每日观察!L2:L500,"不清晰")</f>
         <v>0</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:3">
       <c r="A14" s="7" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="B14" s="8">
         <f>COUNTIF(每日观察!R2:R500,"高")</f>
         <v>1</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:3">
       <c r="A15" s="7" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B15" s="8">
         <f>COUNTA(事后验证!B2:B500)</f>
         <v>0</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:3">
       <c r="A16" s="7" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B16" s="8">
         <f>COUNTIF(事后验证!R2:R500,"关键位置找错")</f>
         <v>0</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:3">
       <c r="A17" s="7" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B17" s="8">
         <f>COUNTIF(事后验证!R2:R500,"理由链断裂")</f>
         <v>0</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="B18" s="8">
         <f>COUNTIF(事后验证!R2:R500,"漏掉反证")</f>
         <v>0</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B19" s="8">
         <f>COUNTIF(事后验证!R2:R500,"过度确定")</f>
         <v>0</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B20" s="8">
         <f>COUNTIF(事后验证!R2:R500,"概率失败")</f>
         <v>0</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -45179,31 +45238,31 @@
         <v>33</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>17</v>
@@ -45217,16 +45276,16 @@
         <v>54</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>61</v>
@@ -45235,42 +45294,42 @@
         <v>102</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>67</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:18">
       <c r="A3" s="2" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>55</v>
@@ -45279,107 +45338,107 @@
         <v>56</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>75</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:18">
       <c r="A4" s="2" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>328</v>
+        <v>104</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>73</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>78</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>73</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:18">
       <c r="A5" s="2" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>81</v>
@@ -45391,31 +45450,31 @@
         <v>60</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:18">
@@ -45426,25 +45485,25 @@
         <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>101</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>347</v>
+        <v>109</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:18">
@@ -45455,7 +45514,7 @@
         <v>81</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>82</v>
@@ -45464,106 +45523,106 @@
         <v>89</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" ht="34" spans="1:18">
       <c r="D8" s="2" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9" ht="34" spans="1:18">
       <c r="D9" s="2" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>64</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:18">
       <c r="D10" s="2" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>81</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:18">
       <c r="D11" s="2" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12" ht="17" spans="1:18">
       <c r="D12" s="2" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" ht="17" spans="1:18">
       <c r="D13" s="2" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>62</v>
@@ -45571,7 +45630,7 @@
     </row>
     <row r="14" ht="17" spans="1:18">
       <c r="D14" s="2" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" ht="17" spans="1:18">

--- a/stock_review_template.xlsx
+++ b/stock_review_template.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="400">
   <si>
     <t>股票观察训练模板</t>
   </si>
@@ -461,6 +461,56 @@
     <t>板块可能有很大的回调，也可能是市场风格开始切换，半导体，AI依然是很好的行业，只是要先洗一下估值</t>
   </si>
   <si>
+    <t>跌破后收回</t>
+  </si>
+  <si>
+    <t>大盘大跌，板块大跌，低点到达78后反弹最后到达85，全天振幅极大13块，情绪是很重的，均线已经跌破，成交量略有提升</t>
+  </si>
+  <si>
+    <t>与大盘板块走出了完全不同的趋势，大盘板块跌幅极大，盘中跌破了80，说明80左右有支撑，触发了非常大的买盘，高点是90，一天当中同时触碰了箱体的下沿与上沿
+可能的分析，在80附近有很多的买盘，看到拉伸后开始抄底，而没有下跌回去，应该是卖方不多了</t>
+  </si>
+  <si>
+    <t>如果是进入下跌通道，应该还会继续冲击箱体下沿，如果反弹就会冲击箱体上沿被站稳板块跌幅剧烈，反弹的都又跌回去了，可能长电之前的跌幅大，反弹多觉得是机会</t>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>基于情绪的推演</t>
+  </si>
+  <si>
+    <t>如果震荡，则空方暂时没了，支撑位80附近会变得更扎实
+如果继续被冲击，甚至跌破说明空方还没有结束</t>
+  </si>
+  <si>
+    <t>前低</t>
+  </si>
+  <si>
+    <t>80~82</t>
+  </si>
+  <si>
+    <t>跌破</t>
+  </si>
+  <si>
+    <t>大盘小跌，板块大跌，一路走低，最后跌停，跌穿之前箱体下沿，成交量小幅降低，情绪几乎到了冰点，4天有3天跌停</t>
+  </si>
+  <si>
+    <t>退潮转弱</t>
+  </si>
+  <si>
+    <t>昨天的拉升，可能只是多方的一次努力，今天多方基本不努力了，从情绪层面，空方力量非常强大，越下坠，上方就有抛盘，获利也会出逃，下跌会持续，整个板块也是持续在跌，这种V走势的概率相对低的，处在跌幅逐步扩大的过程</t>
+  </si>
+  <si>
+    <t>下跌的幅度还好，跟板块基本持平30%左右，没有跌破前低，可能只是回调，只是回调的很快，之前涨的也多</t>
+  </si>
+  <si>
+    <t>基于趋势基于价格从价格分析的，所有的价格指标都是差的</t>
+  </si>
+  <si>
+    <t>是否会V型反转，冲破箱体上沿80～82</t>
+  </si>
+  <si>
     <t>怎么找</t>
   </si>
   <si>
@@ -486,9 +536,6 @@
   </si>
   <si>
     <t>关键位置是前高__，因为这是最近一次冲高回落的位置。</t>
-  </si>
-  <si>
-    <t>前低</t>
   </si>
   <si>
     <t>找最近一次下跌后反弹的最低价，优先看近5-20日内明显低点。</t>
@@ -1091,9 +1138,6 @@
     <t>一般</t>
   </si>
   <si>
-    <t>中</t>
-  </si>
-  <si>
     <t>5日</t>
   </si>
   <si>
@@ -1122,9 +1166,6 @@
   </si>
   <si>
     <t>首日异动</t>
-  </si>
-  <si>
-    <t>跌破</t>
   </si>
   <si>
     <t>不清晰</t>
@@ -1199,12 +1240,6 @@
     <t>20日线</t>
   </si>
   <si>
-    <t>跌破后收回</t>
-  </si>
-  <si>
-    <t>退潮转弱</t>
-  </si>
-  <si>
     <t>继续转弱</t>
   </si>
   <si>
@@ -1244,7 +1279,7 @@
     <numFmt numFmtId="176" formatCode="0.0%"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1272,13 +1307,6 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1432,7 +1460,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="43">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1508,12 +1536,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1849,13 +1871,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1864,37 +1889,37 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1909,73 +1934,70 @@
     <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2049,10 +2071,10 @@
     <xf numFmtId="9" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2064,7 +2086,7 @@
     <xf numFmtId="9" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3374,47 +3396,85 @@
         <v>无效</v>
       </c>
     </row>
-    <row r="10" ht="17" spans="1:31">
+    <row r="10" ht="118" spans="1:31">
       <c r="A10" s="8" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="19"/>
-      <c r="R10" s="19"/>
-      <c r="S10" s="19"/>
-      <c r="T10" s="19"/>
+        <v>20260717-009</v>
+      </c>
+      <c r="B10" s="22">
+        <v>46220</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="I10" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="J10" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="M10" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="N10" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="O10" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="P10" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q10" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="R10" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="S10" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="T10" s="19" t="s">
+        <v>138</v>
+      </c>
       <c r="U10" s="20"/>
       <c r="V10" s="20"/>
-      <c r="W10" s="23" t="str">
+      <c r="W10" s="23">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="X10" s="23" t="str">
+        <v>46223</v>
+      </c>
+      <c r="X10" s="23">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="Y10" s="23" t="str">
+        <v>46225</v>
+      </c>
+      <c r="Y10" s="23">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Z10" s="24" t="str">
+        <v>46230</v>
+      </c>
+      <c r="Z10" s="24">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AA10" s="14"/>
       <c r="AB10" s="14"/>
@@ -3422,50 +3482,86 @@
       <c r="AD10" s="14"/>
       <c r="AE10" s="8" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="17" spans="1:31">
+        <v>无效</v>
+      </c>
+    </row>
+    <row r="11" ht="101" spans="1:31">
       <c r="A11" s="8" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
+        <v>20260718-010</v>
+      </c>
+      <c r="B11" s="22">
+        <v>46221</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>140</v>
+      </c>
       <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="19"/>
-      <c r="T11" s="19"/>
+      <c r="K11" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="M11" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="N11" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="O11" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="P11" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q11" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="R11" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="S11" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="T11" s="19" t="s">
+        <v>147</v>
+      </c>
       <c r="U11" s="20"/>
       <c r="V11" s="20"/>
-      <c r="W11" s="23" t="str">
+      <c r="W11" s="23">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="X11" s="23" t="str">
+        <v>46224</v>
+      </c>
+      <c r="X11" s="23">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="Y11" s="23" t="str">
+        <v>46226</v>
+      </c>
+      <c r="Y11" s="23">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Z11" s="24" t="str">
+        <v>46231</v>
+      </c>
+      <c r="Z11" s="24">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.947368421052632</v>
       </c>
       <c r="AA11" s="14"/>
       <c r="AB11" s="14"/>
@@ -3473,7 +3569,7 @@
       <c r="AD11" s="14"/>
       <c r="AE11" s="8" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>无效</v>
       </c>
     </row>
     <row r="12" ht="17" spans="1:31">
@@ -28487,50 +28583,50 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" ht="78" customHeight="1" spans="1:5">
       <c r="A2" s="19" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" ht="78" customHeight="1" spans="1:5">
       <c r="A3" s="19" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" ht="78" customHeight="1" spans="1:5">
@@ -28538,16 +28634,16 @@
         <v>57</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" ht="78" customHeight="1" spans="1:5">
@@ -28555,118 +28651,118 @@
         <v>98</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" ht="78" customHeight="1" spans="1:5">
       <c r="A6" s="19" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" ht="78" customHeight="1" spans="1:5">
       <c r="A7" s="19" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" ht="78" customHeight="1" spans="1:5">
       <c r="A8" s="19" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" ht="78" customHeight="1" spans="1:5">
       <c r="A9" s="19" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" ht="78" customHeight="1" spans="1:5">
       <c r="A10" s="19" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" ht="78" customHeight="1" spans="1:5">
       <c r="A11" s="19" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -28694,25 +28790,25 @@
   <sheetData>
     <row r="1" ht="17" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" ht="90" customHeight="1" spans="1:7">
@@ -28720,22 +28816,22 @@
         <v>102</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" ht="90" customHeight="1" spans="1:7">
@@ -28743,22 +28839,22 @@
         <v>107</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" ht="90" customHeight="1" spans="1:7">
@@ -28766,45 +28862,45 @@
         <v>73</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" ht="90" customHeight="1" spans="1:7">
       <c r="A5" s="19" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1" spans="1:7">
@@ -28812,22 +28908,22 @@
         <v>124</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" ht="90" customHeight="1" spans="1:7">
@@ -28835,45 +28931,45 @@
         <v>89</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1" spans="1:7">
       <c r="A8" s="19" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1" spans="1:7">
@@ -28881,91 +28977,91 @@
         <v>114</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" ht="90" customHeight="1" spans="1:7">
       <c r="A10" s="19" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" ht="90" customHeight="1" spans="1:7">
       <c r="A11" s="19" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" ht="90" customHeight="1" spans="1:7">
       <c r="A12" s="19" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -29004,76 +29100,76 @@
   <sheetData>
     <row r="1" ht="34" spans="1:24">
       <c r="A1" s="11" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="D1" s="11" t="s">
         <v>23</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="O1" s="11" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="T1" s="11" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="U1" s="11" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="V1" s="12" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="W1" s="11" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="X1" s="11" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:24">
@@ -45103,236 +45199,236 @@
   <sheetData>
     <row r="1" ht="20.4" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="5"/>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:3">
       <c r="A3" s="7" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="B3" s="8">
         <f>COUNTA(每日观察!B2:B500)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:3">
       <c r="A4" s="7" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="B4" s="8">
         <f>COUNTIF(每日观察!Z2:Z500,1)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:3">
       <c r="A5" s="7" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="B5" s="10">
         <f>IFERROR(B4/B3,"")</f>
         <v>0.5</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:3">
       <c r="A6" s="7" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="B6" s="8">
         <f>COUNTIF(每日观察!AE2:AE500,"有效")</f>
         <v>0</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:3">
       <c r="A7" s="7" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="B7" s="10">
         <f>IFERROR(B6/B3,"")</f>
         <v>0</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:3">
       <c r="A8" s="7" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="B8" s="8">
         <f>COUNTIF(每日观察!AA2:AA500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:3">
       <c r="A9" s="7" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="B9" s="8">
         <f>COUNTIF(每日观察!AB2:AB500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:3">
       <c r="A10" s="7" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="B10" s="8">
         <f>COUNTIF(每日观察!AC2:AC500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:3">
       <c r="A11" s="7" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(每日观察!AD2:AD500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:3">
       <c r="A12" s="7" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="B12" s="8">
         <f>COUNTIF(每日观察!H2:H500,"无清晰位置")</f>
         <v>0</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:3">
       <c r="A13" s="7" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="B13" s="8">
         <f>COUNTIF(每日观察!L2:L500,"不清晰")</f>
         <v>0</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:3">
       <c r="A14" s="7" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="B14" s="8">
         <f>COUNTIF(每日观察!R2:R500,"高")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:3">
       <c r="A15" s="7" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="B15" s="8">
         <f>COUNTA(事后验证!B2:B500)</f>
         <v>0</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:3">
       <c r="A16" s="7" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="B16" s="8">
         <f>COUNTIF(事后验证!R2:R500,"关键位置找错")</f>
         <v>0</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:3">
       <c r="A17" s="7" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="B17" s="8">
         <f>COUNTIF(事后验证!R2:R500,"理由链断裂")</f>
         <v>0</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="B18" s="8">
         <f>COUNTIF(事后验证!R2:R500,"漏掉反证")</f>
         <v>0</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="B19" s="8">
         <f>COUNTIF(事后验证!R2:R500,"过度确定")</f>
         <v>0</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="B20" s="8">
         <f>COUNTIF(事后验证!R2:R500,"概率失败")</f>
         <v>0</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -45376,31 +45472,31 @@
         <v>33</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>17</v>
@@ -45414,16 +45510,16 @@
         <v>54</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>61</v>
@@ -45432,42 +45528,42 @@
         <v>102</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>67</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:18">
       <c r="A3" s="2" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>55</v>
@@ -45476,13 +45572,13 @@
         <v>56</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>107</v>
@@ -45491,42 +45587,42 @@
         <v>75</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>342</v>
+        <v>136</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:18">
       <c r="A4" s="2" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>104</v>
@@ -45535,48 +45631,48 @@
         <v>57</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>353</v>
+        <v>141</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>73</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>78</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>73</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:18">
       <c r="A5" s="2" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>81</v>
@@ -45588,31 +45684,31 @@
         <v>60</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>116</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:18">
@@ -45623,7 +45719,7 @@
         <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>101</v>
@@ -45635,13 +45731,13 @@
         <v>109</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:18">
@@ -45652,7 +45748,7 @@
         <v>81</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>82</v>
@@ -45664,44 +45760,44 @@
         <v>126</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8" ht="34" spans="1:18">
       <c r="D8" s="2" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>378</v>
+        <v>132</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>379</v>
+        <v>143</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9" ht="34" spans="1:18">
       <c r="D9" s="2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>114</v>
@@ -45713,46 +45809,46 @@
         <v>116</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:18">
       <c r="D10" s="2" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>81</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:18">
       <c r="D11" s="2" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" ht="17" spans="1:18">
       <c r="D12" s="2" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>116</v>
@@ -45760,7 +45856,7 @@
     </row>
     <row r="13" ht="17" spans="1:18">
       <c r="D13" s="2" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>62</v>
@@ -45768,7 +45864,7 @@
     </row>
     <row r="14" ht="17" spans="1:18">
       <c r="D14" s="2" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" ht="17" spans="1:18">

--- a/stock_review_template.xlsx
+++ b/stock_review_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12740" activeTab="1"/>
+    <workbookView windowWidth="29400" windowHeight="12700" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="417">
   <si>
     <t>股票观察训练模板</t>
   </si>
@@ -511,6 +511,69 @@
     <t>是否会V型反转，冲破箱体上沿80～82</t>
   </si>
   <si>
+    <t>低位反弹</t>
+  </si>
+  <si>
+    <t>跟随着板块走出了一个超级大V，整个板块，从底部直接拉涨停，能量非常大，个股跟谁板块</t>
+  </si>
+  <si>
+    <t>震荡整理</t>
+  </si>
+  <si>
+    <t>板块也跌了很久，应该开始震荡整理</t>
+  </si>
+  <si>
+    <t>动能很大，一天振幅20%</t>
+  </si>
+  <si>
+    <t>跟谁着板块，个股的情况不明朗</t>
+  </si>
+  <si>
+    <t>个股是否会走出自己独立的趋势，板块的回调是否结束</t>
+  </si>
+  <si>
+    <t>机构可能抄底，然后慢慢又出货跑掉，早盘继续涨，然后尾盘跑掉，吸引散户接盘</t>
+  </si>
+  <si>
+    <t>震荡</t>
+  </si>
+  <si>
+    <t>箱体的上沿是之前的箱体的下沿，现在成了压力位</t>
+  </si>
+  <si>
+    <t>今天的走势强于板块，强的不是太多，早盘跟着板块冲击箱体上沿，后回落，交易量5日均线即将下穿50日均线</t>
+  </si>
+  <si>
+    <t>如果不是大盘已经跌破了70，同时跌破了50日均线，不是很好的势头，看多的是散户卖出的是机构，交易量不低但是价格没怎么往上走，说明是有人在出货，机构在有序撤退</t>
+  </si>
+  <si>
+    <t>强于板块，冲击箱体上沿，可能调整结束开始反冲</t>
+  </si>
+  <si>
+    <t>震荡时期不太好判断，多空继续博弈，空方略微占优</t>
+  </si>
+  <si>
+    <t>后续是冲击箱体上沿，还是跌破箱体下沿</t>
+  </si>
+  <si>
+    <t>震荡偏弱</t>
+  </si>
+  <si>
+    <t>今天走势弱于板块，板块早层冲高，个股没跟，跌破了MA50，缩了不少量，</t>
+  </si>
+  <si>
+    <t>板块走弱，个股走势弱于板块，空方明显更强，全天没有组织什么有效攻势，个股接近箱体下沿</t>
+  </si>
+  <si>
+    <t>可能是回调，资金在吸筹</t>
+  </si>
+  <si>
+    <t>情绪面，技术分析层面，都不太好</t>
+  </si>
+  <si>
+    <t>后续是继续冲击前期低点，还是在箱体震荡</t>
+  </si>
+  <si>
     <t>怎么找</t>
   </si>
   <si>
@@ -856,9 +919,6 @@
     <t>当前阶段只训练识别，不训练追涨。</t>
   </si>
   <si>
-    <t>低位反弹</t>
-  </si>
-  <si>
     <t>下降趋势中的前高/20日线/箱体上沿。</t>
   </si>
   <si>
@@ -1162,9 +1222,6 @@
     <t>无效</t>
   </si>
   <si>
-    <t>震荡</t>
-  </si>
-  <si>
     <t>首日异动</t>
   </si>
   <si>
@@ -1187,9 +1244,6 @@
   </si>
   <si>
     <t>把退潮当回调</t>
-  </si>
-  <si>
-    <t>震荡偏弱</t>
   </si>
   <si>
     <t>主升延续</t>
@@ -1262,9 +1316,6 @@
   </si>
   <si>
     <t>大阴线高点</t>
-  </si>
-  <si>
-    <t>震荡整理</t>
   </si>
 </sst>
 </file>
@@ -3572,47 +3623,85 @@
         <v>无效</v>
       </c>
     </row>
-    <row r="12" ht="17" spans="1:31">
+    <row r="12" ht="51" spans="1:31">
       <c r="A12" s="8" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
+        <v>20260720-011</v>
+      </c>
+      <c r="B12" s="27">
+        <v>46223</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>140</v>
+      </c>
       <c r="J12" s="19"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="19"/>
-      <c r="R12" s="7"/>
-      <c r="S12" s="19"/>
-      <c r="T12" s="19"/>
+      <c r="K12" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="N12" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="P12" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q12" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="R12" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="S12" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="T12" s="19" t="s">
+        <v>154</v>
+      </c>
       <c r="U12" s="20"/>
-      <c r="V12" s="20"/>
-      <c r="W12" s="28" t="str">
+      <c r="V12" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="W12" s="28">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="X12" s="28" t="str">
+        <v>46226</v>
+      </c>
+      <c r="X12" s="28">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="Y12" s="28" t="str">
+        <v>46228</v>
+      </c>
+      <c r="Y12" s="28">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Z12" s="29" t="str">
+        <v>46233</v>
+      </c>
+      <c r="Z12" s="29">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.947368421052632</v>
       </c>
       <c r="AA12" s="17"/>
       <c r="AB12" s="17"/>
@@ -3620,50 +3709,88 @@
       <c r="AD12" s="17"/>
       <c r="AE12" s="8" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="17" spans="1:31">
+        <v>无效</v>
+      </c>
+    </row>
+    <row r="13" ht="68" spans="1:31">
       <c r="A13" s="8" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="19"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="19"/>
-      <c r="T13" s="19"/>
+        <v>20260721-012</v>
+      </c>
+      <c r="B13" s="27">
+        <v>46224</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I13" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="J13" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="N13" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="P13" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q13" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="R13" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="S13" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="T13" s="19" t="s">
+        <v>162</v>
+      </c>
       <c r="U13" s="20"/>
       <c r="V13" s="20"/>
-      <c r="W13" s="28" t="str">
+      <c r="W13" s="28">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="X13" s="28" t="str">
+        <v>46227</v>
+      </c>
+      <c r="X13" s="28">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="Y13" s="28" t="str">
+        <v>46229</v>
+      </c>
+      <c r="Y13" s="28">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Z13" s="29" t="str">
+        <v>46234</v>
+      </c>
+      <c r="Z13" s="29">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AA13" s="17"/>
       <c r="AB13" s="17"/>
@@ -3671,50 +3798,86 @@
       <c r="AD13" s="17"/>
       <c r="AE13" s="8" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="17" spans="1:31">
+        <v>无效</v>
+      </c>
+    </row>
+    <row r="14" ht="51" spans="1:31">
       <c r="A14" s="8" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B14" s="27"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
+        <v>20260722-013</v>
+      </c>
+      <c r="B14" s="27">
+        <v>46225</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>140</v>
+      </c>
       <c r="J14" s="19"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="19"/>
-      <c r="R14" s="7"/>
-      <c r="S14" s="19"/>
-      <c r="T14" s="19"/>
+      <c r="K14" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="N14" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="P14" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q14" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="R14" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="S14" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="T14" s="19" t="s">
+        <v>168</v>
+      </c>
       <c r="U14" s="20"/>
       <c r="V14" s="20"/>
-      <c r="W14" s="28" t="str">
+      <c r="W14" s="28">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="X14" s="28" t="str">
+        <v>46228</v>
+      </c>
+      <c r="X14" s="28">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="Y14" s="28" t="str">
+        <v>46230</v>
+      </c>
+      <c r="Y14" s="28">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Z14" s="29" t="str">
+        <v>46235</v>
+      </c>
+      <c r="Z14" s="29">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.947368421052632</v>
       </c>
       <c r="AA14" s="17"/>
       <c r="AB14" s="17"/>
@@ -3722,7 +3885,7 @@
       <c r="AD14" s="17"/>
       <c r="AE14" s="8" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>无效</v>
       </c>
     </row>
     <row r="15" ht="17" spans="1:31">
@@ -28583,33 +28746,33 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" ht="78" customHeight="1" spans="1:5">
       <c r="A2" s="19" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" ht="78" customHeight="1" spans="1:5">
@@ -28617,16 +28780,16 @@
         <v>139</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" ht="78" customHeight="1" spans="1:5">
@@ -28634,16 +28797,16 @@
         <v>57</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" ht="78" customHeight="1" spans="1:5">
@@ -28651,118 +28814,118 @@
         <v>98</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" ht="78" customHeight="1" spans="1:5">
       <c r="A6" s="19" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" ht="78" customHeight="1" spans="1:5">
       <c r="A7" s="19" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" ht="78" customHeight="1" spans="1:5">
       <c r="A8" s="19" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" ht="78" customHeight="1" spans="1:5">
       <c r="A9" s="19" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" ht="78" customHeight="1" spans="1:5">
       <c r="A10" s="19" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" ht="78" customHeight="1" spans="1:5">
       <c r="A11" s="19" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -28790,25 +28953,25 @@
   <sheetData>
     <row r="1" ht="17" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" ht="90" customHeight="1" spans="1:7">
@@ -28816,22 +28979,22 @@
         <v>102</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" ht="90" customHeight="1" spans="1:7">
@@ -28839,22 +29002,22 @@
         <v>107</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" ht="90" customHeight="1" spans="1:7">
@@ -28862,45 +29025,45 @@
         <v>73</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" ht="90" customHeight="1" spans="1:7">
       <c r="A5" s="19" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1" spans="1:7">
@@ -28908,22 +29071,22 @@
         <v>124</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" ht="90" customHeight="1" spans="1:7">
@@ -28931,45 +29094,45 @@
         <v>89</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1" spans="1:7">
       <c r="A8" s="19" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1" spans="1:7">
@@ -28977,91 +29140,91 @@
         <v>114</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" ht="90" customHeight="1" spans="1:7">
       <c r="A10" s="19" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11" ht="90" customHeight="1" spans="1:7">
       <c r="A11" s="19" t="s">
-        <v>263</v>
+        <v>148</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12" ht="90" customHeight="1" spans="1:7">
       <c r="A12" s="19" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -29100,76 +29263,76 @@
   <sheetData>
     <row r="1" ht="34" spans="1:24">
       <c r="A1" s="11" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="D1" s="11" t="s">
         <v>23</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="O1" s="11" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="T1" s="11" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="U1" s="11" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="V1" s="12" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="W1" s="11" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="X1" s="11" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:24">
@@ -45199,236 +45362,236 @@
   <sheetData>
     <row r="1" ht="20.4" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="5"/>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:3">
       <c r="A3" s="7" t="s">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="B3" s="8">
         <f>COUNTA(每日观察!B2:B500)</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:3">
       <c r="A4" s="7" t="s">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="B4" s="8">
         <f>COUNTIF(每日观察!Z2:Z500,1)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:3">
       <c r="A5" s="7" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="B5" s="10">
         <f>IFERROR(B4/B3,"")</f>
-        <v>0.5</v>
+        <v>0.461538461538462</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:3">
       <c r="A6" s="7" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="B6" s="8">
         <f>COUNTIF(每日观察!AE2:AE500,"有效")</f>
         <v>0</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:3">
       <c r="A7" s="7" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="B7" s="10">
         <f>IFERROR(B6/B3,"")</f>
         <v>0</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:3">
       <c r="A8" s="7" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="B8" s="8">
         <f>COUNTIF(每日观察!AA2:AA500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:3">
       <c r="A9" s="7" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="B9" s="8">
         <f>COUNTIF(每日观察!AB2:AB500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>317</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:3">
       <c r="A10" s="7" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="B10" s="8">
         <f>COUNTIF(每日观察!AC2:AC500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>319</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:3">
       <c r="A11" s="7" t="s">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(每日观察!AD2:AD500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:3">
       <c r="A12" s="7" t="s">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="B12" s="8">
         <f>COUNTIF(每日观察!H2:H500,"无清晰位置")</f>
         <v>0</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>323</v>
+        <v>343</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:3">
       <c r="A13" s="7" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="B13" s="8">
         <f>COUNTIF(每日观察!L2:L500,"不清晰")</f>
         <v>0</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>325</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:3">
       <c r="A14" s="7" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="B14" s="8">
         <f>COUNTIF(每日观察!R2:R500,"高")</f>
         <v>2</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:3">
       <c r="A15" s="7" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="B15" s="8">
         <f>COUNTA(事后验证!B2:B500)</f>
         <v>0</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:3">
       <c r="A16" s="7" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="B16" s="8">
         <f>COUNTIF(事后验证!R2:R500,"关键位置找错")</f>
         <v>0</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:3">
       <c r="A17" s="7" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="B17" s="8">
         <f>COUNTIF(事后验证!R2:R500,"理由链断裂")</f>
         <v>0</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="B18" s="8">
         <f>COUNTIF(事后验证!R2:R500,"漏掉反证")</f>
         <v>0</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="B19" s="8">
         <f>COUNTIF(事后验证!R2:R500,"过度确定")</f>
         <v>0</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="B20" s="8">
         <f>COUNTIF(事后验证!R2:R500,"概率失败")</f>
         <v>0</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -45472,31 +45635,31 @@
         <v>33</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>17</v>
@@ -45510,16 +45673,16 @@
         <v>54</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>61</v>
@@ -45528,42 +45691,42 @@
         <v>102</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>67</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>353</v>
+        <v>373</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:18">
       <c r="A3" s="2" t="s">
-        <v>354</v>
+        <v>374</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>55</v>
@@ -45575,10 +45738,10 @@
         <v>139</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>107</v>
@@ -45590,39 +45753,39 @@
         <v>136</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:18">
       <c r="A4" s="2" t="s">
-        <v>365</v>
+        <v>156</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>104</v>
@@ -45634,45 +45797,45 @@
         <v>141</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>73</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>78</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>73</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:18">
       <c r="A5" s="2" t="s">
-        <v>374</v>
+        <v>163</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>365</v>
+        <v>156</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>81</v>
@@ -45684,31 +45847,31 @@
         <v>60</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>116</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:18">
@@ -45719,7 +45882,7 @@
         <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>101</v>
@@ -45731,13 +45894,13 @@
         <v>109</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:18">
@@ -45748,7 +45911,7 @@
         <v>81</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>82</v>
@@ -45760,44 +45923,44 @@
         <v>126</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
     </row>
     <row r="8" ht="34" spans="1:18">
       <c r="D8" s="2" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>132</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>143</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9" ht="34" spans="1:18">
       <c r="D9" s="2" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>114</v>
@@ -45809,46 +45972,46 @@
         <v>116</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:18">
       <c r="D10" s="2" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>81</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:18">
       <c r="D11" s="2" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>263</v>
+        <v>148</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>399</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" ht="17" spans="1:18">
       <c r="D12" s="2" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>116</v>
@@ -45856,7 +46019,7 @@
     </row>
     <row r="13" ht="17" spans="1:18">
       <c r="D13" s="2" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>62</v>
@@ -45864,7 +46027,7 @@
     </row>
     <row r="14" ht="17" spans="1:18">
       <c r="D14" s="2" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" ht="17" spans="1:18">

--- a/stock_review_template.xlsx
+++ b/stock_review_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12700" activeTab="1"/>
+    <workbookView windowWidth="29400" windowHeight="14060" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="454">
   <si>
     <t>股票观察训练模板</t>
   </si>
@@ -574,6 +574,121 @@
     <t>后续是继续冲击前期低点，还是在箱体震荡</t>
   </si>
   <si>
+    <t>横盘震荡</t>
+  </si>
+  <si>
+    <t>今天走势强于板块，成交量，换手率都变低，没有太多情绪，最近两天波动也相对较小</t>
+  </si>
+  <si>
+    <t>个股进入了平淡期，但是通常横盘整理会延续之前的趋势，之前是下降趋势</t>
+  </si>
+  <si>
+    <t>震荡时期不太好判断</t>
+  </si>
+  <si>
+    <t>看后续是跌破80，还是在80 左右不停的震荡</t>
+  </si>
+  <si>
+    <t>之前跳空的压力位，转变为第一之支撑位，第二支撑位70，上方压力位90</t>
+  </si>
+  <si>
+    <t>接近支撑位，前一个小锤子并没有起到夯实底部的作用，尤其昨天大盘涨的厉害，现在处于一个横向振荡期，今天试探了75后拉回</t>
+  </si>
+  <si>
+    <t>目前是横盘震荡，波动，以及成交量都在减小，当前实体不算大，处于休整时期，还看不到趋势</t>
+  </si>
+  <si>
+    <t>后后续是否跌破75，这个串口的支撑线已经还行，虽然之前已经试探过了，</t>
+  </si>
+  <si>
+    <t>如果75是支撑位，那此时买入的风险收入比还可以2.6.如果是70只有0.5问题就是没有反转信号啊</t>
+  </si>
+  <si>
+    <t>PCB</t>
+  </si>
+  <si>
+    <t>100～102</t>
+  </si>
+  <si>
+    <t>之前的低点，也是超级整数点</t>
+  </si>
+  <si>
+    <t>出现了分手线，跌破了之前的跳空的窗口115的支撑，大阴线，空方力量强劲</t>
+  </si>
+  <si>
+    <t>目前没有反转的迹象</t>
+  </si>
+  <si>
+    <t>后续是否能突破跳空的压力位115</t>
+  </si>
+  <si>
+    <t>突破了之前75的跳空支撑位，第二次试探了70的支撑位</t>
+  </si>
+  <si>
+    <t>阴线，然后实体也不小，</t>
+  </si>
+  <si>
+    <t>触碰了前期低点，然后回升了，没有跌破
+板块出现了一个锤子线，有可能企稳</t>
+  </si>
+  <si>
+    <t>形势很明确，空方占据很大的优势</t>
+  </si>
+  <si>
+    <t>是否跌破70，但是75变成了压力位，是否能站稳现在的低点，板块是否会企稳</t>
+  </si>
+  <si>
+    <t>下影线触碰了100的支撑位到达97，然后收回了，回到了收盘位置上面一点，出现了一个锤子线</t>
+  </si>
+  <si>
+    <t>可能触底回稳了，成交量也小幅扩大，是很好的信号，空方控制不了局势，板块也有一个十字星</t>
+  </si>
+  <si>
+    <t>第一次试探了支撑位，前面是一个分手线</t>
+  </si>
+  <si>
+    <t>是否企稳</t>
+  </si>
+  <si>
+    <t>整数位</t>
+  </si>
+  <si>
+    <t>第一支撑位60，第二支撑位50</t>
+  </si>
+  <si>
+    <t>大阴线，而且一直收在低点，跌破了前低70，没有回稳的迹象</t>
+  </si>
+  <si>
+    <t>没有反转的信号，持续下跌</t>
+  </si>
+  <si>
+    <t>第一天突破70，不知道是否能收回</t>
+  </si>
+  <si>
+    <t>没有小实体，持续下跌，3只乌鸦，3连跌</t>
+  </si>
+  <si>
+    <t>是否明天继续收在70之下，则70变成阻力位</t>
+  </si>
+  <si>
+    <t>之前跳空的支撑位</t>
+  </si>
+  <si>
+    <t>大阴线，之前锤子线的低点被突破，跌破了100整数位</t>
+  </si>
+  <si>
+    <t>100的整数位，还有前低，都跌破了</t>
+  </si>
+  <si>
+    <t>第一天突破100，不知道是否收回</t>
+  </si>
+  <si>
+    <t>锤子线没守住</t>
+  </si>
+  <si>
+    <t>是否明天继续收在100之下，则100变成阻力位，另外90是一个比较强力的支撑不知道能否守住</t>
+  </si>
+  <si>
     <t>怎么找</t>
   </si>
   <si>
@@ -650,9 +765,6 @@
   </si>
   <si>
     <t>关键位置是__日线，因为近期价格一直围绕它运行。</t>
-  </si>
-  <si>
-    <t>整数位</t>
   </si>
   <si>
     <t>看10、20、50、100等整数，或个股常见心理价位。</t>
@@ -935,9 +1047,6 @@
   </si>
   <si>
     <t>低位不等于低风险。</t>
-  </si>
-  <si>
-    <t>横盘震荡</t>
   </si>
   <si>
     <t>箱体上沿/下沿。</t>
@@ -1316,6 +1425,9 @@
   </si>
   <si>
     <t>大阴线高点</t>
+  </si>
+  <si>
+    <t>放量下跌</t>
   </si>
 </sst>
 </file>
@@ -3724,7 +3836,7 @@
         <v>52</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>156</v>
@@ -3813,7 +3925,7 @@
         <v>52</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>163</v>
@@ -3888,47 +4000,83 @@
         <v>无效</v>
       </c>
     </row>
-    <row r="15" ht="17" spans="1:31">
+    <row r="15" ht="51" spans="1:31">
       <c r="A15" s="8" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B15" s="27"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
+        <v>20260723-014</v>
+      </c>
+      <c r="B15" s="27">
+        <v>46226</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="I15" s="19" t="s">
+        <v>140</v>
+      </c>
       <c r="J15" s="19"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="19"/>
-      <c r="Q15" s="19"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="19"/>
-      <c r="T15" s="19"/>
+      <c r="K15" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="N15" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="P15" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q15" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="R15" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="S15" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="T15" s="19" t="s">
+        <v>173</v>
+      </c>
       <c r="U15" s="20"/>
       <c r="V15" s="20"/>
-      <c r="W15" s="28" t="str">
+      <c r="W15" s="28">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="X15" s="28" t="str">
+        <v>46229</v>
+      </c>
+      <c r="X15" s="28">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="Y15" s="28" t="str">
+        <v>46231</v>
+      </c>
+      <c r="Y15" s="28">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Z15" s="29" t="str">
+        <v>46236</v>
+      </c>
+      <c r="Z15" s="29">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.947368421052632</v>
       </c>
       <c r="AA15" s="17"/>
       <c r="AB15" s="17"/>
@@ -3936,50 +4084,88 @@
       <c r="AD15" s="17"/>
       <c r="AE15" s="8" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="17" spans="1:31">
+        <v>无效</v>
+      </c>
+    </row>
+    <row r="16" ht="51" spans="1:31">
       <c r="A16" s="8" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="19"/>
+        <v>20260728-015</v>
+      </c>
+      <c r="B16" s="27">
+        <v>46231</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="I16" s="7">
+        <v>75</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="N16" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="P16" s="19" t="s">
+        <v>176</v>
+      </c>
       <c r="Q16" s="19"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="19"/>
+      <c r="R16" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="S16" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="T16" s="19" t="s">
+        <v>177</v>
+      </c>
       <c r="U16" s="20"/>
-      <c r="V16" s="20"/>
-      <c r="W16" s="28" t="str">
+      <c r="V16" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="W16" s="28">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="X16" s="28" t="str">
+        <v>46234</v>
+      </c>
+      <c r="X16" s="28">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="Y16" s="28" t="str">
+        <v>46236</v>
+      </c>
+      <c r="Y16" s="28">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Z16" s="29" t="str">
+        <v>46241</v>
+      </c>
+      <c r="Z16" s="29">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.947368421052632</v>
       </c>
       <c r="AA16" s="17"/>
       <c r="AB16" s="17"/>
@@ -3987,50 +4173,84 @@
       <c r="AD16" s="17"/>
       <c r="AE16" s="8" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="17" spans="1:31">
+        <v>无效</v>
+      </c>
+    </row>
+    <row r="17" ht="34" spans="1:31">
       <c r="A17" s="8" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B17" s="27"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="7"/>
+        <v>20260728-016</v>
+      </c>
+      <c r="B17" s="27">
+        <v>46231</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="J17" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="N17" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>143</v>
+      </c>
       <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="7"/>
+      <c r="Q17" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="R17" s="7" t="s">
+        <v>78</v>
+      </c>
       <c r="S17" s="19"/>
-      <c r="T17" s="19"/>
+      <c r="T17" s="19" t="s">
+        <v>184</v>
+      </c>
       <c r="U17" s="20"/>
       <c r="V17" s="20"/>
-      <c r="W17" s="28" t="str">
+      <c r="W17" s="28">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="X17" s="28" t="str">
+        <v>46234</v>
+      </c>
+      <c r="X17" s="28">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="Y17" s="28" t="str">
+        <v>46236</v>
+      </c>
+      <c r="Y17" s="28">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Z17" s="29" t="str">
+        <v>46241</v>
+      </c>
+      <c r="Z17" s="29">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.894736842105263</v>
       </c>
       <c r="AA17" s="17"/>
       <c r="AB17" s="17"/>
@@ -4038,50 +4258,78 @@
       <c r="AD17" s="17"/>
       <c r="AE17" s="8" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="17" spans="1:31">
+        <v>无效</v>
+      </c>
+    </row>
+    <row r="18" ht="34" spans="1:31">
       <c r="A18" s="8" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B18" s="27"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
+        <v>20260729-017</v>
+      </c>
+      <c r="B18" s="27">
+        <v>46232</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>53</v>
+      </c>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
+      <c r="I18" s="7">
+        <v>70</v>
+      </c>
+      <c r="J18" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>61</v>
+      </c>
       <c r="M18" s="7"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
+      <c r="N18" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="P18" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q18" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="R18" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="S18" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="T18" s="19" t="s">
+        <v>189</v>
+      </c>
       <c r="U18" s="20"/>
       <c r="V18" s="20"/>
-      <c r="W18" s="28" t="str">
+      <c r="W18" s="28">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="X18" s="28" t="str">
+        <v>46235</v>
+      </c>
+      <c r="X18" s="28">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="Y18" s="28" t="str">
+        <v>46237</v>
+      </c>
+      <c r="Y18" s="28">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Z18" s="29" t="str">
+        <v>46242</v>
+      </c>
+      <c r="Z18" s="29">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.736842105263158</v>
       </c>
       <c r="AA18" s="17"/>
       <c r="AB18" s="17"/>
@@ -4089,50 +4337,70 @@
       <c r="AD18" s="17"/>
       <c r="AE18" s="8" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="17" spans="1:31">
+        <v>无效</v>
+      </c>
+    </row>
+    <row r="19" ht="51" spans="1:31">
       <c r="A19" s="8" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B19" s="27"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
+        <v>20260729-018</v>
+      </c>
+      <c r="B19" s="27">
+        <v>46232</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>179</v>
+      </c>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
+      <c r="I19" s="7" t="s">
+        <v>180</v>
+      </c>
       <c r="J19" s="19"/>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
       <c r="M19" s="7"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="19"/>
-      <c r="Q19" s="19"/>
-      <c r="R19" s="7"/>
+      <c r="N19" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="P19" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q19" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="R19" s="7" t="s">
+        <v>78</v>
+      </c>
       <c r="S19" s="19"/>
-      <c r="T19" s="19"/>
+      <c r="T19" s="19" t="s">
+        <v>193</v>
+      </c>
       <c r="U19" s="20"/>
       <c r="V19" s="20"/>
-      <c r="W19" s="28" t="str">
+      <c r="W19" s="28">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="X19" s="28" t="str">
+        <v>46235</v>
+      </c>
+      <c r="X19" s="28">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="Y19" s="28" t="str">
+        <v>46237</v>
+      </c>
+      <c r="Y19" s="28">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Z19" s="29" t="str">
+        <v>46242</v>
+      </c>
+      <c r="Z19" s="29">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.526315789473684</v>
       </c>
       <c r="AA19" s="17"/>
       <c r="AB19" s="17"/>
@@ -4140,50 +4408,88 @@
       <c r="AD19" s="17"/>
       <c r="AE19" s="8" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="17" spans="1:31">
+        <v>无效</v>
+      </c>
+    </row>
+    <row r="20" ht="34" spans="1:31">
       <c r="A20" s="8" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="7"/>
-      <c r="S20" s="19"/>
-      <c r="T20" s="19"/>
+        <v>20260730-019</v>
+      </c>
+      <c r="B20" s="27">
+        <v>46233</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="I20" s="7">
+        <v>60</v>
+      </c>
+      <c r="J20" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="N20" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="O20" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="P20" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q20" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="R20" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="S20" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="T20" s="19" t="s">
+        <v>200</v>
+      </c>
       <c r="U20" s="20"/>
       <c r="V20" s="20"/>
-      <c r="W20" s="28" t="str">
+      <c r="W20" s="28">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="X20" s="28" t="str">
+        <v>46236</v>
+      </c>
+      <c r="X20" s="28">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="Y20" s="28" t="str">
+        <v>46238</v>
+      </c>
+      <c r="Y20" s="28">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Z20" s="29" t="str">
+        <v>46243</v>
+      </c>
+      <c r="Z20" s="29">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AA20" s="17"/>
       <c r="AB20" s="17"/>
@@ -4191,50 +4497,88 @@
       <c r="AD20" s="17"/>
       <c r="AE20" s="8" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="17" spans="1:31">
+        <v>无效</v>
+      </c>
+    </row>
+    <row r="21" ht="34" spans="1:31">
       <c r="A21" s="8" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B21" s="27"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="7"/>
-      <c r="S21" s="19"/>
-      <c r="T21" s="19"/>
+        <v>20260730-020</v>
+      </c>
+      <c r="B21" s="27">
+        <v>46233</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="I21" s="7">
+        <v>90</v>
+      </c>
+      <c r="J21" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="N21" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="P21" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q21" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="R21" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="S21" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="T21" s="19" t="s">
+        <v>206</v>
+      </c>
       <c r="U21" s="20"/>
       <c r="V21" s="20"/>
-      <c r="W21" s="28" t="str">
+      <c r="W21" s="28">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="X21" s="28" t="str">
+        <v>46236</v>
+      </c>
+      <c r="X21" s="28">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="Y21" s="28" t="str">
+        <v>46238</v>
+      </c>
+      <c r="Y21" s="28">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Z21" s="29" t="str">
+        <v>46243</v>
+      </c>
+      <c r="Z21" s="29">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AA21" s="17"/>
       <c r="AB21" s="17"/>
@@ -4242,7 +4586,7 @@
       <c r="AD21" s="17"/>
       <c r="AE21" s="8" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>无效</v>
       </c>
     </row>
     <row r="22" ht="17" spans="1:31">
@@ -28695,13 +29039,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" sqref="E2:E500">
+    <dataValidation type="list" allowBlank="1" sqref="E16 E21 E2:E15 E17:E20 E22:E500">
       <formula1>选项!$A$2:$A$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F500">
+    <dataValidation type="list" allowBlank="1" sqref="F21 F2:F20 F22:F500">
       <formula1>选项!$B$2:$B$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G500">
+    <dataValidation type="list" allowBlank="1" sqref="G21 G2:G20 G22:G500">
       <formula1>选项!$C$2:$C$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="H2:H500">
@@ -28746,33 +29090,33 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>169</v>
+        <v>207</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>170</v>
+        <v>208</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>171</v>
+        <v>209</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>172</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" ht="78" customHeight="1" spans="1:5">
       <c r="A2" s="19" t="s">
-        <v>173</v>
+        <v>211</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>175</v>
+        <v>213</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>176</v>
+        <v>214</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>177</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" ht="78" customHeight="1" spans="1:5">
@@ -28780,16 +29124,16 @@
         <v>139</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>178</v>
+        <v>216</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>181</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" ht="78" customHeight="1" spans="1:5">
@@ -28797,16 +29141,16 @@
         <v>57</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>182</v>
+        <v>220</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>183</v>
+        <v>221</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>184</v>
+        <v>222</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>185</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" ht="78" customHeight="1" spans="1:5">
@@ -28814,118 +29158,118 @@
         <v>98</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>186</v>
+        <v>224</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>187</v>
+        <v>225</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>188</v>
+        <v>226</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" ht="78" customHeight="1" spans="1:5">
       <c r="A6" s="19" t="s">
-        <v>190</v>
+        <v>228</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>191</v>
+        <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>194</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" ht="78" customHeight="1" spans="1:5">
       <c r="A7" s="19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>196</v>
+        <v>233</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>197</v>
+        <v>234</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>198</v>
+        <v>235</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>199</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" ht="78" customHeight="1" spans="1:5">
       <c r="A8" s="19" t="s">
-        <v>200</v>
+        <v>237</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>201</v>
+        <v>238</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>202</v>
+        <v>239</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>203</v>
+        <v>240</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>204</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" ht="78" customHeight="1" spans="1:5">
       <c r="A9" s="19" t="s">
-        <v>205</v>
+        <v>242</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>206</v>
+        <v>243</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>207</v>
+        <v>244</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>208</v>
+        <v>245</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" ht="78" customHeight="1" spans="1:5">
       <c r="A10" s="19" t="s">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>211</v>
+        <v>248</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>213</v>
+        <v>250</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>214</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" ht="78" customHeight="1" spans="1:5">
       <c r="A11" s="19" t="s">
-        <v>215</v>
+        <v>252</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>216</v>
+        <v>253</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>217</v>
+        <v>254</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>218</v>
+        <v>255</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>219</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -28953,25 +29297,25 @@
   <sheetData>
     <row r="1" ht="17" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>257</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>221</v>
+        <v>258</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>222</v>
+        <v>259</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>223</v>
+        <v>260</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>224</v>
+        <v>261</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>225</v>
+        <v>262</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>226</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" ht="90" customHeight="1" spans="1:7">
@@ -28979,22 +29323,22 @@
         <v>102</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>227</v>
+        <v>264</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>229</v>
+        <v>266</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>230</v>
+        <v>267</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>231</v>
+        <v>268</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>232</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" ht="90" customHeight="1" spans="1:7">
@@ -29002,22 +29346,22 @@
         <v>107</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>233</v>
+        <v>270</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>234</v>
+        <v>271</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>235</v>
+        <v>272</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>236</v>
+        <v>273</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>237</v>
+        <v>274</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>238</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4" ht="90" customHeight="1" spans="1:7">
@@ -29025,45 +29369,45 @@
         <v>73</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>239</v>
+        <v>276</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>241</v>
+        <v>278</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>242</v>
+        <v>279</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>243</v>
+        <v>280</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>244</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" ht="90" customHeight="1" spans="1:7">
       <c r="A5" s="19" t="s">
-        <v>245</v>
+        <v>282</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>246</v>
+        <v>283</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>247</v>
+        <v>284</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>248</v>
+        <v>285</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>249</v>
+        <v>286</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>250</v>
+        <v>287</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>251</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1" spans="1:7">
@@ -29071,22 +29415,22 @@
         <v>124</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>252</v>
+        <v>289</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>253</v>
+        <v>290</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>254</v>
+        <v>291</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>256</v>
+        <v>293</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>257</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" ht="90" customHeight="1" spans="1:7">
@@ -29094,45 +29438,45 @@
         <v>89</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>258</v>
+        <v>295</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>259</v>
+        <v>296</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>260</v>
+        <v>297</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>262</v>
+        <v>299</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>263</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1" spans="1:7">
       <c r="A8" s="19" t="s">
-        <v>264</v>
+        <v>301</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>265</v>
+        <v>302</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>266</v>
+        <v>303</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>268</v>
+        <v>305</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>269</v>
+        <v>306</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1" spans="1:7">
@@ -29140,45 +29484,45 @@
         <v>114</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>271</v>
+        <v>308</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>272</v>
+        <v>309</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>273</v>
+        <v>310</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>275</v>
+        <v>312</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>276</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10" ht="90" customHeight="1" spans="1:7">
       <c r="A10" s="19" t="s">
-        <v>277</v>
+        <v>314</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>278</v>
+        <v>315</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>279</v>
+        <v>316</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>280</v>
+        <v>317</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>281</v>
+        <v>318</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>282</v>
+        <v>319</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>283</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11" ht="90" customHeight="1" spans="1:7">
@@ -29186,45 +29530,45 @@
         <v>148</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>284</v>
+        <v>321</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>285</v>
+        <v>322</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>286</v>
+        <v>323</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>287</v>
+        <v>324</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>288</v>
+        <v>325</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>289</v>
+        <v>326</v>
       </c>
     </row>
     <row r="12" ht="90" customHeight="1" spans="1:7">
       <c r="A12" s="19" t="s">
-        <v>290</v>
+        <v>169</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>291</v>
+        <v>327</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>293</v>
+        <v>329</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>294</v>
+        <v>330</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -29263,76 +29607,76 @@
   <sheetData>
     <row r="1" ht="34" spans="1:24">
       <c r="A1" s="11" t="s">
-        <v>297</v>
+        <v>333</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>299</v>
+        <v>335</v>
       </c>
       <c r="D1" s="11" t="s">
         <v>23</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>300</v>
+        <v>336</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>302</v>
+        <v>338</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>303</v>
+        <v>339</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>304</v>
+        <v>340</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>306</v>
+        <v>342</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>307</v>
+        <v>343</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>309</v>
+        <v>345</v>
       </c>
       <c r="O1" s="11" t="s">
-        <v>310</v>
+        <v>346</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>311</v>
+        <v>347</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>312</v>
+        <v>348</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>313</v>
+        <v>349</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="T1" s="11" t="s">
-        <v>315</v>
+        <v>351</v>
       </c>
       <c r="U1" s="11" t="s">
-        <v>316</v>
+        <v>352</v>
       </c>
       <c r="V1" s="12" t="s">
-        <v>317</v>
+        <v>353</v>
       </c>
       <c r="W1" s="11" t="s">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="X1" s="11" t="s">
-        <v>319</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:24">
@@ -45362,236 +45706,236 @@
   <sheetData>
     <row r="1" ht="20.4" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>320</v>
+        <v>356</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="5"/>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>323</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:3">
       <c r="A3" s="7" t="s">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="B3" s="8">
         <f>COUNTA(每日观察!B2:B500)</f>
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:3">
       <c r="A4" s="7" t="s">
-        <v>326</v>
+        <v>362</v>
       </c>
       <c r="B4" s="8">
         <f>COUNTIF(每日观察!Z2:Z500,1)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>327</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:3">
       <c r="A5" s="7" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="B5" s="10">
         <f>IFERROR(B4/B3,"")</f>
-        <v>0.461538461538462</v>
+        <v>0.4</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>329</v>
+        <v>365</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:3">
       <c r="A6" s="7" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="B6" s="8">
         <f>COUNTIF(每日观察!AE2:AE500,"有效")</f>
         <v>0</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>331</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:3">
       <c r="A7" s="7" t="s">
-        <v>332</v>
+        <v>368</v>
       </c>
       <c r="B7" s="10">
         <f>IFERROR(B6/B3,"")</f>
         <v>0</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>333</v>
+        <v>369</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:3">
       <c r="A8" s="7" t="s">
-        <v>334</v>
+        <v>370</v>
       </c>
       <c r="B8" s="8">
         <f>COUNTIF(每日观察!AA2:AA500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:3">
       <c r="A9" s="7" t="s">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="B9" s="8">
         <f>COUNTIF(每日观察!AB2:AB500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>337</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:3">
       <c r="A10" s="7" t="s">
-        <v>338</v>
+        <v>374</v>
       </c>
       <c r="B10" s="8">
         <f>COUNTIF(每日观察!AC2:AC500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>339</v>
+        <v>375</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:3">
       <c r="A11" s="7" t="s">
-        <v>340</v>
+        <v>376</v>
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(每日观察!AD2:AD500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>341</v>
+        <v>377</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:3">
       <c r="A12" s="7" t="s">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="B12" s="8">
         <f>COUNTIF(每日观察!H2:H500,"无清晰位置")</f>
         <v>0</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>343</v>
+        <v>379</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:3">
       <c r="A13" s="7" t="s">
-        <v>344</v>
+        <v>380</v>
       </c>
       <c r="B13" s="8">
         <f>COUNTIF(每日观察!L2:L500,"不清晰")</f>
         <v>0</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>345</v>
+        <v>381</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:3">
       <c r="A14" s="7" t="s">
-        <v>346</v>
+        <v>382</v>
       </c>
       <c r="B14" s="8">
         <f>COUNTIF(每日观察!R2:R500,"高")</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>347</v>
+        <v>383</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:3">
       <c r="A15" s="7" t="s">
-        <v>348</v>
+        <v>384</v>
       </c>
       <c r="B15" s="8">
         <f>COUNTA(事后验证!B2:B500)</f>
         <v>0</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>349</v>
+        <v>385</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:3">
       <c r="A16" s="7" t="s">
-        <v>350</v>
+        <v>386</v>
       </c>
       <c r="B16" s="8">
         <f>COUNTIF(事后验证!R2:R500,"关键位置找错")</f>
         <v>0</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:3">
       <c r="A17" s="7" t="s">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="B17" s="8">
         <f>COUNTIF(事后验证!R2:R500,"理由链断裂")</f>
         <v>0</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>353</v>
+        <v>389</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="B18" s="8">
         <f>COUNTIF(事后验证!R2:R500,"漏掉反证")</f>
         <v>0</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>355</v>
+        <v>391</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>356</v>
+        <v>392</v>
       </c>
       <c r="B19" s="8">
         <f>COUNTIF(事后验证!R2:R500,"过度确定")</f>
         <v>0</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>357</v>
+        <v>393</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>358</v>
+        <v>394</v>
       </c>
       <c r="B20" s="8">
         <f>COUNTIF(事后验证!R2:R500,"概率失败")</f>
         <v>0</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
@@ -45635,31 +45979,31 @@
         <v>33</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>360</v>
+        <v>396</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>361</v>
+        <v>397</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>306</v>
+        <v>342</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>309</v>
+        <v>345</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>362</v>
+        <v>398</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>311</v>
+        <v>347</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>312</v>
+        <v>348</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>313</v>
+        <v>349</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>17</v>
@@ -45673,16 +46017,16 @@
         <v>54</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>363</v>
+        <v>399</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>173</v>
+        <v>211</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>364</v>
+        <v>400</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>61</v>
@@ -45691,42 +46035,42 @@
         <v>102</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>365</v>
+        <v>401</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>67</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>366</v>
+        <v>402</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>367</v>
+        <v>403</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>368</v>
+        <v>404</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>369</v>
+        <v>405</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>370</v>
+        <v>406</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>371</v>
+        <v>407</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>372</v>
+        <v>408</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>373</v>
+        <v>409</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>368</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:18">
       <c r="A3" s="2" t="s">
-        <v>374</v>
+        <v>410</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>55</v>
@@ -45738,10 +46082,10 @@
         <v>139</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>375</v>
+        <v>411</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>376</v>
+        <v>412</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>107</v>
@@ -45753,31 +46097,31 @@
         <v>136</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>377</v>
+        <v>413</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>378</v>
+        <v>414</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>376</v>
+        <v>412</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>379</v>
+        <v>415</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>380</v>
+        <v>416</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>381</v>
+        <v>417</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>382</v>
+        <v>418</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>383</v>
+        <v>419</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>384</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:18">
@@ -45785,7 +46129,7 @@
         <v>156</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>385</v>
+        <v>421</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>104</v>
@@ -45797,37 +46141,37 @@
         <v>141</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>386</v>
+        <v>422</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>73</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>78</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>388</v>
+        <v>424</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>73</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>384</v>
+        <v>420</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>390</v>
+        <v>426</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>391</v>
+        <v>427</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>392</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:18">
@@ -45847,31 +46191,31 @@
         <v>60</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>245</v>
+        <v>282</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>393</v>
+        <v>429</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>394</v>
+        <v>430</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>395</v>
+        <v>431</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>116</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>396</v>
+        <v>432</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>397</v>
+        <v>433</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>398</v>
+        <v>434</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>399</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:18">
@@ -45882,7 +46226,7 @@
         <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>400</v>
+        <v>436</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>101</v>
@@ -45894,13 +46238,13 @@
         <v>109</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>402</v>
+        <v>438</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>403</v>
+        <v>439</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:18">
@@ -45911,7 +46255,7 @@
         <v>81</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>404</v>
+        <v>440</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>82</v>
@@ -45923,44 +46267,44 @@
         <v>126</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>405</v>
+        <v>441</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>406</v>
+        <v>442</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>407</v>
+        <v>443</v>
       </c>
     </row>
     <row r="8" ht="34" spans="1:18">
       <c r="D8" s="2" t="s">
-        <v>408</v>
+        <v>444</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>132</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>264</v>
+        <v>301</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>143</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>409</v>
+        <v>445</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>411</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9" ht="34" spans="1:18">
       <c r="D9" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>396</v>
+        <v>432</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>114</v>
@@ -45972,32 +46316,32 @@
         <v>116</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>412</v>
+        <v>448</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>413</v>
+        <v>449</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:18">
       <c r="D10" s="2" t="s">
-        <v>200</v>
+        <v>237</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>81</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>277</v>
+        <v>314</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>414</v>
+        <v>450</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>415</v>
+        <v>451</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:18">
       <c r="D11" s="2" t="s">
-        <v>416</v>
+        <v>452</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>148</v>
@@ -46008,10 +46352,10 @@
     </row>
     <row r="12" ht="17" spans="1:18">
       <c r="D12" s="2" t="s">
-        <v>205</v>
+        <v>242</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>290</v>
+        <v>169</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>116</v>
@@ -46019,7 +46363,7 @@
     </row>
     <row r="13" ht="17" spans="1:18">
       <c r="D13" s="2" t="s">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>62</v>
@@ -46027,7 +46371,10 @@
     </row>
     <row r="14" ht="17" spans="1:18">
       <c r="D14" s="2" t="s">
-        <v>215</v>
+        <v>252</v>
+      </c>
+      <c r="G14" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="15" ht="17" spans="1:18">

--- a/stock_review_template.xlsx
+++ b/stock_review_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="14060" activeTab="1"/>
+    <workbookView windowWidth="15980" windowHeight="12660" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="466">
   <si>
     <t>股票观察训练模板</t>
   </si>
@@ -689,6 +689,48 @@
     <t>是否明天继续收在100之下，则100变成阻力位，另外90是一个比较强力的支撑不知道能否守住</t>
   </si>
   <si>
+    <t>首日异动</t>
+  </si>
+  <si>
+    <t>上方的压力位</t>
+  </si>
+  <si>
+    <t>早盘情绪很高，直接压力位高开，随后低走，开于最高点，收于最低点，空方占优</t>
+  </si>
+  <si>
+    <t>没有反转的信号，持续下跌，今天这么强势高开，但是几乎没有守住，没有收回70</t>
+  </si>
+  <si>
+    <t>找不到，可能就是今天还是收盘高于昨天</t>
+  </si>
+  <si>
+    <t>高开低走，开在最高点收在最低点</t>
+  </si>
+  <si>
+    <t>是否去试探60的支撑位</t>
+  </si>
+  <si>
+    <t>下方支撑位</t>
+  </si>
+  <si>
+    <t>高位放量震荡</t>
+  </si>
+  <si>
+    <t>回到了100支撑位之上，实体很小，早盘盘中涨停，代表空方力量没有那么强大</t>
+  </si>
+  <si>
+    <t>小实体，空方可能动摇了</t>
+  </si>
+  <si>
+    <t>100支撑位是否足够坚挺，交易量没有放大，也没有强反转信号，毕竟开始高开低走受在最低处</t>
+  </si>
+  <si>
+    <t>小实体，大盘整体高开，有情绪，</t>
+  </si>
+  <si>
+    <t>是否守住100支撑位</t>
+  </si>
+  <si>
     <t>怎么找</t>
   </si>
   <si>
@@ -912,9 +954,6 @@
   </si>
   <si>
     <t>重点不是当天红绿，而是冲高后有没有资金继续接。</t>
-  </si>
-  <si>
-    <t>高位放量震荡</t>
   </si>
   <si>
     <t>放量分歧区/前高/短期均线。</t>
@@ -1329,9 +1368,6 @@
   </si>
   <si>
     <t>无效</t>
-  </si>
-  <si>
-    <t>首日异动</t>
   </si>
   <si>
     <t>不清晰</t>
@@ -4589,47 +4625,85 @@
         <v>无效</v>
       </c>
     </row>
-    <row r="22" ht="17" spans="1:31">
+    <row r="22" ht="34" spans="1:31">
       <c r="A22" s="8" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B22" s="27"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="7"/>
-      <c r="S22" s="19"/>
-      <c r="T22" s="19"/>
+        <v>20260731-021</v>
+      </c>
+      <c r="B22" s="27">
+        <v>46234</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="I22" s="7">
+        <v>70</v>
+      </c>
+      <c r="J22" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="N22" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="O22" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="P22" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q22" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="R22" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="S22" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="T22" s="19" t="s">
+        <v>213</v>
+      </c>
       <c r="U22" s="20"/>
       <c r="V22" s="20"/>
-      <c r="W22" s="28" t="str">
+      <c r="W22" s="28">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="X22" s="28" t="str">
+        <v>46237</v>
+      </c>
+      <c r="X22" s="28">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="Y22" s="28" t="str">
+        <v>46239</v>
+      </c>
+      <c r="Y22" s="28">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Z22" s="29" t="str">
+        <v>46244</v>
+      </c>
+      <c r="Z22" s="29">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AA22" s="17"/>
       <c r="AB22" s="17"/>
@@ -4637,50 +4711,88 @@
       <c r="AD22" s="17"/>
       <c r="AE22" s="8" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="17" spans="1:31">
+        <v>无效</v>
+      </c>
+    </row>
+    <row r="23" ht="51" spans="1:31">
       <c r="A23" s="8" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="7"/>
-      <c r="S23" s="19"/>
-      <c r="T23" s="19"/>
+        <v>20260731-022</v>
+      </c>
+      <c r="B23" s="27">
+        <v>46234</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="I23" s="7">
+        <v>100</v>
+      </c>
+      <c r="J23" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="N23" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="P23" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q23" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="R23" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="S23" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="T23" s="19" t="s">
+        <v>220</v>
+      </c>
       <c r="U23" s="20"/>
       <c r="V23" s="20"/>
-      <c r="W23" s="28" t="str">
+      <c r="W23" s="28">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="X23" s="28" t="str">
+        <v>46237</v>
+      </c>
+      <c r="X23" s="28">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="Y23" s="28" t="str">
+        <v>46239</v>
+      </c>
+      <c r="Y23" s="28">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Z23" s="29" t="str">
+        <v>46244</v>
+      </c>
+      <c r="Z23" s="29">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AA23" s="17"/>
       <c r="AB23" s="17"/>
@@ -4688,7 +4800,7 @@
       <c r="AD23" s="17"/>
       <c r="AE23" s="8" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>无效</v>
       </c>
     </row>
     <row r="24" ht="17" spans="1:31">
@@ -29039,23 +29151,23 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" sqref="E16 E21 E2:E15 E17:E20 E22:E500">
+    <dataValidation type="list" allowBlank="1" sqref="E16 E21 E22 E23 E2:E15 E17:E20 E24:E500">
       <formula1>选项!$A$2:$A$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F21 F2:F20 F22:F500">
+    <dataValidation type="list" allowBlank="1" sqref="F21 F22 F23 F2:F20 F24:F500">
       <formula1>选项!$B$2:$B$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G21 G2:G20 G22:G500">
+    <dataValidation type="list" allowBlank="1" sqref="G21 G22 G2:G20 G23:G500">
       <formula1>选项!$C$2:$C$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H500">
+    <dataValidation type="list" allowBlank="1" sqref="H22 H23 H2:H21 H24:H500">
       <formula1>选项!$D$2:$D$15</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="L22 L2:L21 L23:L500">
+      <formula1>选项!$F$2:$F$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="K2:K500">
       <formula1>选项!$E$2:$E$10</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="L2:L500">
-      <formula1>选项!$F$2:$F$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="M2:M500">
       <formula1>选项!$G$2:$G$13</formula1>
@@ -29090,33 +29202,33 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" ht="78" customHeight="1" spans="1:5">
       <c r="A2" s="19" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" ht="78" customHeight="1" spans="1:5">
@@ -29124,16 +29236,16 @@
         <v>139</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" ht="78" customHeight="1" spans="1:5">
@@ -29141,16 +29253,16 @@
         <v>57</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" ht="78" customHeight="1" spans="1:5">
@@ -29158,33 +29270,33 @@
         <v>98</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" ht="78" customHeight="1" spans="1:5">
       <c r="A6" s="19" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" ht="78" customHeight="1" spans="1:5">
@@ -29192,84 +29304,84 @@
         <v>194</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" ht="78" customHeight="1" spans="1:5">
       <c r="A8" s="19" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" ht="78" customHeight="1" spans="1:5">
       <c r="A9" s="19" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10" ht="78" customHeight="1" spans="1:5">
       <c r="A10" s="19" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" ht="78" customHeight="1" spans="1:5">
       <c r="A11" s="19" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -29297,25 +29409,25 @@
   <sheetData>
     <row r="1" ht="17" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
     </row>
     <row r="2" ht="90" customHeight="1" spans="1:7">
@@ -29323,22 +29435,22 @@
         <v>102</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3" ht="90" customHeight="1" spans="1:7">
@@ -29346,22 +29458,22 @@
         <v>107</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" ht="90" customHeight="1" spans="1:7">
@@ -29369,45 +29481,45 @@
         <v>73</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" ht="90" customHeight="1" spans="1:7">
       <c r="A5" s="19" t="s">
-        <v>282</v>
+        <v>215</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1" spans="1:7">
@@ -29415,22 +29527,22 @@
         <v>124</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" ht="90" customHeight="1" spans="1:7">
@@ -29438,45 +29550,45 @@
         <v>89</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1" spans="1:7">
       <c r="A8" s="19" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1" spans="1:7">
@@ -29484,45 +29596,45 @@
         <v>114</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10" ht="90" customHeight="1" spans="1:7">
       <c r="A10" s="19" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11" ht="90" customHeight="1" spans="1:7">
@@ -29530,22 +29642,22 @@
         <v>148</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" ht="90" customHeight="1" spans="1:7">
@@ -29553,22 +29665,22 @@
         <v>169</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -29607,76 +29719,76 @@
   <sheetData>
     <row r="1" ht="34" spans="1:24">
       <c r="A1" s="11" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="D1" s="11" t="s">
         <v>23</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="O1" s="11" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="T1" s="11" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="U1" s="11" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="V1" s="12" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="W1" s="11" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="X1" s="11" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:24">
@@ -45706,236 +45818,236 @@
   <sheetData>
     <row r="1" ht="20.4" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="5"/>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:3">
       <c r="A3" s="7" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="B3" s="8">
         <f>COUNTA(每日观察!B2:B500)</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:3">
       <c r="A4" s="7" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B4" s="8">
         <f>COUNTIF(每日观察!Z2:Z500,1)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:3">
       <c r="A5" s="7" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="B5" s="10">
         <f>IFERROR(B4/B3,"")</f>
-        <v>0.4</v>
+        <v>0.454545454545455</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:3">
       <c r="A6" s="7" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="B6" s="8">
         <f>COUNTIF(每日观察!AE2:AE500,"有效")</f>
         <v>0</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:3">
       <c r="A7" s="7" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="B7" s="10">
         <f>IFERROR(B6/B3,"")</f>
         <v>0</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:3">
       <c r="A8" s="7" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="B8" s="8">
         <f>COUNTIF(每日观察!AA2:AA500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:3">
       <c r="A9" s="7" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="B9" s="8">
         <f>COUNTIF(每日观察!AB2:AB500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:3">
       <c r="A10" s="7" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="B10" s="8">
         <f>COUNTIF(每日观察!AC2:AC500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:3">
       <c r="A11" s="7" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(每日观察!AD2:AD500,"不合格")</f>
         <v>0</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:3">
       <c r="A12" s="7" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="B12" s="8">
         <f>COUNTIF(每日观察!H2:H500,"无清晰位置")</f>
         <v>0</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:3">
       <c r="A13" s="7" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="B13" s="8">
         <f>COUNTIF(每日观察!L2:L500,"不清晰")</f>
         <v>0</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:3">
       <c r="A14" s="7" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="B14" s="8">
         <f>COUNTIF(每日观察!R2:R500,"高")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:3">
       <c r="A15" s="7" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="B15" s="8">
         <f>COUNTA(事后验证!B2:B500)</f>
         <v>0</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:3">
       <c r="A16" s="7" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="B16" s="8">
         <f>COUNTIF(事后验证!R2:R500,"关键位置找错")</f>
         <v>0</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:3">
       <c r="A17" s="7" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="B17" s="8">
         <f>COUNTIF(事后验证!R2:R500,"理由链断裂")</f>
         <v>0</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="B18" s="8">
         <f>COUNTIF(事后验证!R2:R500,"漏掉反证")</f>
         <v>0</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="B19" s="8">
         <f>COUNTIF(事后验证!R2:R500,"过度确定")</f>
         <v>0</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="B20" s="8">
         <f>COUNTIF(事后验证!R2:R500,"概率失败")</f>
         <v>0</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -45979,31 +46091,31 @@
         <v>33</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>17</v>
@@ -46017,16 +46129,16 @@
         <v>54</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>61</v>
@@ -46035,42 +46147,42 @@
         <v>102</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>67</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:18">
       <c r="A3" s="2" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>55</v>
@@ -46082,10 +46194,10 @@
         <v>139</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>107</v>
@@ -46097,31 +46209,31 @@
         <v>136</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:18">
@@ -46129,7 +46241,7 @@
         <v>156</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>421</v>
+        <v>207</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>104</v>
@@ -46141,37 +46253,37 @@
         <v>141</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>73</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>78</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>73</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:18">
@@ -46191,31 +46303,31 @@
         <v>60</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>282</v>
+        <v>215</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>116</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:18">
@@ -46226,7 +46338,7 @@
         <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>101</v>
@@ -46238,13 +46350,13 @@
         <v>109</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:18">
@@ -46255,7 +46367,7 @@
         <v>81</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>82</v>
@@ -46267,36 +46379,36 @@
         <v>126</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
     </row>
     <row r="8" ht="34" spans="1:18">
       <c r="D8" s="2" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>132</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>143</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9" ht="34" spans="1:18">
@@ -46304,7 +46416,7 @@
         <v>194</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>114</v>
@@ -46316,32 +46428,32 @@
         <v>116</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:18">
       <c r="D10" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>81</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:18">
       <c r="D11" s="2" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>148</v>
@@ -46352,7 +46464,7 @@
     </row>
     <row r="12" ht="17" spans="1:18">
       <c r="D12" s="2" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>169</v>
@@ -46363,7 +46475,7 @@
     </row>
     <row r="13" ht="17" spans="1:18">
       <c r="D13" s="2" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>62</v>
@@ -46371,10 +46483,10 @@
     </row>
     <row r="14" ht="17" spans="1:18">
       <c r="D14" s="2" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="G14" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
     </row>
     <row r="15" ht="17" spans="1:18">
